--- a/research/traditional_assets/database/data/netherlands/netherlands_diversified.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_diversified.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -596,40 +596,40 @@
         <v>0.407</v>
       </c>
       <c r="G2">
-        <v>0.206598412794572</v>
+        <v>0.2065820434171691</v>
       </c>
       <c r="H2">
-        <v>0.1721184951838614</v>
+        <v>0.1721048577479897</v>
       </c>
       <c r="I2">
-        <v>0.4614842188162597</v>
+        <v>0.4614583396432875</v>
       </c>
       <c r="J2">
-        <v>0.4487100364730116</v>
+        <v>0.427771590371199</v>
       </c>
       <c r="K2">
-        <v>17927.8</v>
+        <v>17928.262</v>
       </c>
       <c r="L2">
-        <v>0.4344290301084388</v>
+        <v>0.4344058034294005</v>
       </c>
       <c r="M2">
         <v>1072.5</v>
       </c>
       <c r="N2">
-        <v>0.05444853407792867</v>
+        <v>0.05443264436070192</v>
       </c>
       <c r="O2">
-        <v>0.0598232912013744</v>
+        <v>0.05982174959290533</v>
       </c>
       <c r="P2">
         <v>135</v>
       </c>
       <c r="Q2">
-        <v>0.006853661632186826</v>
+        <v>0.006851661527920521</v>
       </c>
       <c r="R2">
-        <v>0.007530204486886289</v>
+        <v>0.007530010438267803</v>
       </c>
       <c r="S2">
         <v>937.5</v>
@@ -638,55 +638,55 @@
         <v>0.8741258741258742</v>
       </c>
       <c r="U2">
-        <v>870</v>
+        <v>870.009</v>
       </c>
       <c r="V2">
-        <v>0.04416804162964844</v>
+        <v>0.04415560884625633</v>
       </c>
       <c r="W2">
-        <v>0.739824615702053</v>
+        <v>0.4002272684809478</v>
       </c>
       <c r="X2">
-        <v>0.08335620371859218</v>
+        <v>0.08529580976581787</v>
       </c>
       <c r="Y2">
-        <v>0.6564684119834608</v>
+        <v>0.31493145871513</v>
       </c>
       <c r="Z2">
-        <v>0.8296792664121385</v>
+        <v>0.8295468085616156</v>
       </c>
       <c r="AA2">
-        <v>0.3722854138926923</v>
+        <v>0.2025017026837672</v>
       </c>
       <c r="AB2">
-        <v>0.07471688389450169</v>
+        <v>0.07436887150645186</v>
       </c>
       <c r="AC2">
-        <v>0.2975685299981906</v>
+        <v>0.1281328311773153</v>
       </c>
       <c r="AD2">
-        <v>5052</v>
+        <v>5054.44</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5052</v>
+        <v>5054.44</v>
       </c>
       <c r="AG2">
-        <v>4182</v>
+        <v>4184.431</v>
       </c>
       <c r="AH2">
-        <v>0.204125335865371</v>
+        <v>0.2041563651536149</v>
       </c>
       <c r="AI2">
-        <v>0.109504002358281</v>
+        <v>0.1095292321594385</v>
       </c>
       <c r="AJ2">
-        <v>0.1751292950019891</v>
+        <v>0.1751710850458862</v>
       </c>
       <c r="AK2">
-        <v>0.09238865090919533</v>
+        <v>0.09241858896783685</v>
       </c>
       <c r="AL2">
         <v>1610.4</v>
@@ -695,16 +695,16 @@
         <v>16.10000000000014</v>
       </c>
       <c r="AN2">
-        <v>0.2545498518652881</v>
+        <v>0.2546727935989681</v>
       </c>
       <c r="AO2">
-        <v>11.82581967213115</v>
+        <v>11.8260935171386</v>
       </c>
       <c r="AP2">
-        <v>0.2107140697744725</v>
+        <v>0.2108365580345446</v>
       </c>
       <c r="AQ2">
-        <v>1182.875776397505</v>
+        <v>1182.903167701853</v>
       </c>
     </row>
     <row r="3">
@@ -781,10 +781,10 @@
         <v>0.739824615702053</v>
       </c>
       <c r="X3">
-        <v>0.08335620371859218</v>
+        <v>0.08333205841874314</v>
       </c>
       <c r="Y3">
-        <v>0.6564684119834608</v>
+        <v>0.6564925572833099</v>
       </c>
       <c r="Z3">
         <v>0.8296792664121385</v>
@@ -793,10 +793,10 @@
         <v>0.3722854138926923</v>
       </c>
       <c r="AB3">
-        <v>0.07471688389450169</v>
+        <v>0.07469766726209391</v>
       </c>
       <c r="AC3">
-        <v>0.2975685299981906</v>
+        <v>0.2975877466305983</v>
       </c>
       <c r="AD3">
         <v>5052</v>
@@ -839,6 +839,119 @@
       </c>
       <c r="AQ3">
         <v>1182.875776397505</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Readen Holding Corp. (OTCPK:RHCO)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Diversified</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0.1348623853211009</v>
+      </c>
+      <c r="J4">
+        <v>0.1189053855311997</v>
+      </c>
+      <c r="K4">
+        <v>0.462</v>
+      </c>
+      <c r="L4">
+        <v>0.1412844036697248</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="V4">
+        <v>0.001565217391304348</v>
+      </c>
+      <c r="W4">
+        <v>0.06062992125984252</v>
+      </c>
+      <c r="X4">
+        <v>0.0872595611128926</v>
+      </c>
+      <c r="Y4">
+        <v>-0.02662963985305008</v>
+      </c>
+      <c r="Z4">
+        <v>0.2751598788286772</v>
+      </c>
+      <c r="AA4">
+        <v>0.03271799147484205</v>
+      </c>
+      <c r="AB4">
+        <v>0.07404007575080981</v>
+      </c>
+      <c r="AC4">
+        <v>-0.04132208427596776</v>
+      </c>
+      <c r="AD4">
+        <v>2.44</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>2.44</v>
+      </c>
+      <c r="AG4">
+        <v>2.431</v>
+      </c>
+      <c r="AH4">
+        <v>0.2979242979242979</v>
+      </c>
+      <c r="AI4">
+        <v>0.2094420600858369</v>
+      </c>
+      <c r="AJ4">
+        <v>0.2971519374159638</v>
+      </c>
+      <c r="AK4">
+        <v>0.2088308564556309</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1133,7 +1246,7 @@
         <v>11.8258196721311</v>
       </c>
       <c r="F2">
-        <v>15.0339411867584</v>
+        <v>15.452380901698</v>
       </c>
       <c r="G2">
         <v>0.254549851865288</v>
@@ -1151,13 +1264,13 @@
         <v>19697.5</v>
       </c>
       <c r="L2">
-        <v>1117.67688727263</v>
+        <v>1190.14404528158</v>
       </c>
       <c r="M2">
         <v>23879.5</v>
       </c>
       <c r="N2">
-        <v>24749.6818872726</v>
+        <v>24822.1490452816</v>
       </c>
       <c r="O2">
         <v>5052</v>
@@ -1166,16 +1279,16 @@
         <v>24502.005</v>
       </c>
       <c r="Q2">
-        <v>0.07471688389450171</v>
+        <v>0.0746976672620939</v>
       </c>
       <c r="R2">
-        <v>0.0619285353585257</v>
+        <v>0.0608850196094409</v>
       </c>
       <c r="S2">
         <v>0.0410326</v>
       </c>
       <c r="T2">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,10 +1301,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0833562037185922</v>
+        <v>0.0833320584187431</v>
       </c>
       <c r="X2">
-        <v>2.39507493585256</v>
+        <v>2.39356456094409</v>
       </c>
       <c r="Y2">
         <v>0.866791187499842</v>
@@ -1230,7 +1343,7 @@
         <v>19697.5</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.04329999999999999</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1531,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.07735167928029983</v>
+        <v>0.07733139435579917</v>
       </c>
       <c r="C2">
-        <v>24577.76317545685</v>
+        <v>24577.82925899202</v>
       </c>
       <c r="D2">
-        <v>23707.76317545685</v>
+        <v>23707.82925899202</v>
       </c>
       <c r="E2">
         <v>-5052</v>
@@ -1469,19 +1582,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.07735167928029983</v>
+        <v>0.07733139435579917</v>
       </c>
       <c r="T2">
         <v>0.7282077218429368</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.258</v>
       </c>
       <c r="W2">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1613,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07719588994775665</v>
+        <v>0.07716526935836121</v>
       </c>
       <c r="C3">
-        <v>24340.35383534252</v>
+        <v>24341.08959635497</v>
       </c>
       <c r="D3">
-        <v>23717.84883534252</v>
+        <v>23718.58459635497</v>
       </c>
       <c r="E3">
         <v>-4804.505</v>
@@ -1533,37 +1646,37 @@
         <v>19044.3</v>
       </c>
       <c r="M3">
-        <v>12.7954915</v>
+        <v>12.4489985</v>
       </c>
       <c r="N3">
-        <v>19031.5045085</v>
+        <v>19031.8510015</v>
       </c>
       <c r="O3">
-        <v>4910.128163193</v>
+        <v>4910.217558387</v>
       </c>
       <c r="P3">
-        <v>14121.376345307</v>
+        <v>14121.633443113</v>
       </c>
       <c r="Q3">
-        <v>14923.876345307</v>
+        <v>14924.133443113</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07758815752298652</v>
+        <v>0.07756772056400121</v>
       </c>
       <c r="T3">
         <v>0.7336656019399818</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.258</v>
       </c>
       <c r="W3">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1684,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>1488.360177489079</v>
+        <v>1529.785709268099</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1695,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07704010061521349</v>
+        <v>0.07699914436092323</v>
       </c>
       <c r="C4">
-        <v>24102.95308008088</v>
+        <v>24104.35969671923</v>
       </c>
       <c r="D4">
-        <v>23727.94308008088</v>
+        <v>23729.34969671923</v>
       </c>
       <c r="E4">
         <v>-4557.01</v>
@@ -1615,37 +1728,37 @@
         <v>19044.3</v>
       </c>
       <c r="M4">
-        <v>25.590983</v>
+        <v>24.897997</v>
       </c>
       <c r="N4">
-        <v>19018.709017</v>
+        <v>19019.402003</v>
       </c>
       <c r="O4">
-        <v>4906.826926386</v>
+        <v>4907.005716774</v>
       </c>
       <c r="P4">
-        <v>14111.882090614</v>
+        <v>14112.396286226</v>
       </c>
       <c r="Q4">
-        <v>14914.382090614</v>
+        <v>14914.896286226</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07782946185225867</v>
+        <v>0.07780886975604412</v>
       </c>
       <c r="T4">
         <v>0.7392348673451299</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.258</v>
       </c>
       <c r="W4">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1766,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>744.1800887445395</v>
+        <v>764.8928546340494</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1777,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.0768843112826703</v>
+        <v>0.07683301936348526</v>
       </c>
       <c r="C5">
-        <v>23865.56092063766</v>
+        <v>23867.63957338416</v>
       </c>
       <c r="D5">
-        <v>23738.04592063767</v>
+        <v>23740.12457338416</v>
       </c>
       <c r="E5">
         <v>-4309.515</v>
@@ -1697,37 +1810,37 @@
         <v>19044.3</v>
       </c>
       <c r="M5">
-        <v>38.38647450000001</v>
+        <v>37.3469955</v>
       </c>
       <c r="N5">
-        <v>19005.9135255</v>
+        <v>19006.9530045</v>
       </c>
       <c r="O5">
-        <v>4903.525689579</v>
+        <v>4903.793875161</v>
       </c>
       <c r="P5">
-        <v>14102.387835921</v>
+        <v>14103.159129339</v>
       </c>
       <c r="Q5">
-        <v>14904.887835921</v>
+        <v>14905.659129339</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07807574152852609</v>
+        <v>0.07805499109637656</v>
       </c>
       <c r="T5">
         <v>0.744918962964817</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.258</v>
       </c>
       <c r="W5">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1848,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>496.1200591630262</v>
+        <v>509.928569756033</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1859,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07672852195012714</v>
+        <v>0.07666689436604732</v>
       </c>
       <c r="C6">
-        <v>23628.17736799729</v>
+        <v>23630.92923967331</v>
       </c>
       <c r="D6">
-        <v>23748.15736799729</v>
+        <v>23750.90923967331</v>
       </c>
       <c r="E6">
         <v>-4062.02</v>
@@ -1779,37 +1892,37 @@
         <v>19044.3</v>
       </c>
       <c r="M6">
-        <v>51.181966</v>
+        <v>49.795994</v>
       </c>
       <c r="N6">
-        <v>18993.118034</v>
+        <v>18994.504006</v>
       </c>
       <c r="O6">
-        <v>4900.224452771999</v>
+        <v>4900.582033548</v>
       </c>
       <c r="P6">
-        <v>14092.893581228</v>
+        <v>14093.921972452</v>
       </c>
       <c r="Q6">
-        <v>14895.393581228</v>
+        <v>14896.421972452</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07832715203138244</v>
+        <v>0.07830623996463262</v>
       </c>
       <c r="T6">
         <v>0.7507214772432477</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.258</v>
       </c>
       <c r="W6">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1930,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>372.0900443722697</v>
+        <v>382.4464273170247</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1941,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07657273261758396</v>
+        <v>0.07650076936860935</v>
       </c>
       <c r="C7">
-        <v>23390.80243316288</v>
+        <v>23394.22870893442</v>
       </c>
       <c r="D7">
-        <v>23758.27743316288</v>
+        <v>23761.70370893442</v>
       </c>
       <c r="E7">
         <v>-3814.525</v>
@@ -1861,37 +1974,37 @@
         <v>19044.3</v>
       </c>
       <c r="M7">
-        <v>63.97745750000001</v>
+        <v>62.2449925</v>
       </c>
       <c r="N7">
-        <v>18980.3225425</v>
+        <v>18982.0550075</v>
       </c>
       <c r="O7">
-        <v>4896.923215965</v>
+        <v>4897.370191935</v>
       </c>
       <c r="P7">
-        <v>14083.399326535</v>
+        <v>14084.684815565</v>
       </c>
       <c r="Q7">
-        <v>14885.899326535</v>
+        <v>14887.184815565</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.0785838553869305</v>
+        <v>0.07856277828274669</v>
       </c>
       <c r="T7">
         <v>0.7566461497170136</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.258</v>
       </c>
       <c r="W7">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +2012,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>297.6720354978157</v>
+        <v>305.9571418536198</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +2023,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07641694328504078</v>
+        <v>0.07633464437117138</v>
       </c>
       <c r="C8">
-        <v>23153.43612715635</v>
+        <v>23157.53799453953</v>
       </c>
       <c r="D8">
-        <v>23768.40612715635</v>
+        <v>23772.50799453953</v>
       </c>
       <c r="E8">
         <v>-3567.03</v>
@@ -1943,37 +2056,37 @@
         <v>19044.3</v>
       </c>
       <c r="M8">
-        <v>76.77294900000001</v>
+        <v>74.693991</v>
       </c>
       <c r="N8">
-        <v>18967.527051</v>
+        <v>18969.606009</v>
       </c>
       <c r="O8">
-        <v>4893.621979158001</v>
+        <v>4894.158350322</v>
       </c>
       <c r="P8">
-        <v>14073.905071842</v>
+        <v>14075.447658678</v>
       </c>
       <c r="Q8">
-        <v>14876.405071842</v>
+        <v>14877.947658678</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07884602051600084</v>
+        <v>0.07882477486294828</v>
       </c>
       <c r="T8">
         <v>0.7626968790519235</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.258</v>
       </c>
       <c r="W8">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +2094,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>248.0600295815131</v>
+        <v>254.9642848780165</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +2105,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07626115395249762</v>
+        <v>0.07616851937373341</v>
       </c>
       <c r="C9">
-        <v>22916.07846101839</v>
+        <v>22920.85710988502</v>
       </c>
       <c r="D9">
-        <v>23778.54346101839</v>
+        <v>23783.32210988502</v>
       </c>
       <c r="E9">
         <v>-3319.535</v>
@@ -2025,37 +2138,37 @@
         <v>19044.3</v>
       </c>
       <c r="M9">
-        <v>89.56844050000001</v>
+        <v>87.1429895</v>
       </c>
       <c r="N9">
-        <v>18954.7315595</v>
+        <v>18957.1570105</v>
       </c>
       <c r="O9">
-        <v>4890.320742351</v>
+        <v>4890.946508709</v>
       </c>
       <c r="P9">
-        <v>14064.410817149</v>
+        <v>14066.210501791</v>
       </c>
       <c r="Q9">
-        <v>14866.910817149</v>
+        <v>14868.710501791</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07911382360483615</v>
+        <v>0.07909240577820797</v>
       </c>
       <c r="T9">
         <v>0.7688777315983369</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.258</v>
       </c>
       <c r="W9">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2176,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>212.6228824984398</v>
+        <v>218.5408156097284</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2187,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07610536461995446</v>
+        <v>0.07600239437629547</v>
       </c>
       <c r="C10">
-        <v>22678.72944580856</v>
+        <v>22684.18606839162</v>
       </c>
       <c r="D10">
-        <v>23788.68944580856</v>
+        <v>23794.14606839162</v>
       </c>
       <c r="E10">
         <v>-3072.04</v>
@@ -2107,37 +2220,37 @@
         <v>19044.3</v>
       </c>
       <c r="M10">
-        <v>102.363932</v>
+        <v>99.591988</v>
       </c>
       <c r="N10">
-        <v>18941.936068</v>
+        <v>18944.708012</v>
       </c>
       <c r="O10">
-        <v>4887.019505544</v>
+        <v>4887.734667096</v>
       </c>
       <c r="P10">
-        <v>14054.916562456</v>
+        <v>14056.973344904</v>
       </c>
       <c r="Q10">
-        <v>14857.416562456</v>
+        <v>14859.473344904</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07938744849995048</v>
+        <v>0.07936585475684289</v>
       </c>
       <c r="T10">
         <v>0.7751929505044549</v>
       </c>
       <c r="U10">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.258</v>
       </c>
       <c r="W10">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2258,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>186.0450221861348</v>
+        <v>191.2232136585123</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2269,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07594957528741127</v>
+        <v>0.0758362693788575</v>
       </c>
       <c r="C11">
-        <v>22441.38909260528</v>
+        <v>22447.52488350455</v>
       </c>
       <c r="D11">
-        <v>23798.84409260528</v>
+        <v>23804.97988350455</v>
       </c>
       <c r="E11">
         <v>-2824.545</v>
@@ -2189,37 +2302,37 @@
         <v>19044.3</v>
       </c>
       <c r="M11">
-        <v>115.1594235</v>
+        <v>112.0409865</v>
       </c>
       <c r="N11">
-        <v>18929.1405765</v>
+        <v>18932.2590135</v>
       </c>
       <c r="O11">
-        <v>4883.718268737</v>
+        <v>4884.522825483</v>
       </c>
       <c r="P11">
-        <v>14045.422307763</v>
+        <v>14047.736188017</v>
       </c>
       <c r="Q11">
-        <v>14847.922307763</v>
+        <v>14850.236188017</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07966708712902337</v>
+        <v>0.07964531360314012</v>
       </c>
       <c r="T11">
         <v>0.7816469654304877</v>
       </c>
       <c r="U11">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.258</v>
       </c>
       <c r="W11">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2340,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>165.3733530543421</v>
+        <v>169.9761899186777</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2351,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.0757937859548681</v>
+        <v>0.07567014438141956</v>
       </c>
       <c r="C12">
-        <v>22204.05741250591</v>
+        <v>22210.87356869349</v>
       </c>
       <c r="D12">
-        <v>23809.00741250591</v>
+        <v>23815.82356869349</v>
       </c>
       <c r="E12">
         <v>-2577.05</v>
@@ -2271,37 +2384,37 @@
         <v>19044.3</v>
       </c>
       <c r="M12">
-        <v>127.954915</v>
+        <v>124.489985</v>
       </c>
       <c r="N12">
-        <v>18916.345085</v>
+        <v>18919.810015</v>
       </c>
       <c r="O12">
-        <v>4880.41703193</v>
+        <v>4881.31098387</v>
       </c>
       <c r="P12">
-        <v>14035.92805307</v>
+        <v>14038.49903113</v>
       </c>
       <c r="Q12">
-        <v>14838.42805307</v>
+        <v>14840.99903113</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07995293994985345</v>
+        <v>0.07993098264602172</v>
       </c>
       <c r="T12">
         <v>0.7882444029104323</v>
       </c>
       <c r="U12">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.258</v>
       </c>
       <c r="W12">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2422,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>148.8360177489079</v>
+        <v>152.9785709268099</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2433,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07563799662232494</v>
+        <v>0.07550401938398159</v>
       </c>
       <c r="C13">
-        <v>21966.73441662677</v>
+        <v>21974.23213745269</v>
       </c>
       <c r="D13">
-        <v>23819.17941662677</v>
+        <v>23826.67713745269</v>
       </c>
       <c r="E13">
         <v>-2329.555</v>
@@ -2353,37 +2466,37 @@
         <v>19044.3</v>
       </c>
       <c r="M13">
-        <v>140.7504065</v>
+        <v>136.9389835</v>
       </c>
       <c r="N13">
-        <v>18903.5495935</v>
+        <v>18907.3610165</v>
       </c>
       <c r="O13">
-        <v>4877.115795123</v>
+        <v>4878.099142257</v>
       </c>
       <c r="P13">
-        <v>14026.433798377</v>
+        <v>14029.261874243</v>
       </c>
       <c r="Q13">
-        <v>14828.933798377</v>
+        <v>14831.761874243</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.08024521642957858</v>
+        <v>0.08022307121795683</v>
       </c>
       <c r="T13">
         <v>0.794990097412398</v>
       </c>
       <c r="U13">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.258</v>
       </c>
       <c r="W13">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2504,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>135.3054706808253</v>
+        <v>139.0714281152817</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2515,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07548220728978175</v>
+        <v>0.07533789438654362</v>
       </c>
       <c r="C14">
-        <v>21729.42011610318</v>
+        <v>21737.60060330102</v>
       </c>
       <c r="D14">
-        <v>23829.36011610318</v>
+        <v>23837.54060330101</v>
       </c>
       <c r="E14">
         <v>-2082.06</v>
@@ -2435,37 +2548,37 @@
         <v>19044.3</v>
       </c>
       <c r="M14">
-        <v>153.545898</v>
+        <v>149.387982</v>
       </c>
       <c r="N14">
-        <v>18890.754102</v>
+        <v>18894.912018</v>
       </c>
       <c r="O14">
-        <v>4873.814558315999</v>
+        <v>4874.887300644</v>
       </c>
       <c r="P14">
-        <v>14016.939543684</v>
+        <v>14020.024717356</v>
       </c>
       <c r="Q14">
-        <v>14819.439543684</v>
+        <v>14822.524717356</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08054413555657017</v>
+        <v>0.08052179816652684</v>
       </c>
       <c r="T14">
         <v>0.801889103153045</v>
       </c>
       <c r="U14">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.258</v>
       </c>
       <c r="W14">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2586,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>124.0300147907566</v>
+        <v>127.4821424390082</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2597,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07532641795723859</v>
+        <v>0.07517176938910566</v>
       </c>
       <c r="C15">
-        <v>21492.11452208952</v>
+        <v>21500.97897978198</v>
       </c>
       <c r="D15">
-        <v>23839.54952208952</v>
+        <v>23848.41397978198</v>
       </c>
       <c r="E15">
         <v>-1834.565</v>
@@ -2517,37 +2630,37 @@
         <v>19044.3</v>
       </c>
       <c r="M15">
-        <v>166.3413895</v>
+        <v>161.8369805</v>
       </c>
       <c r="N15">
-        <v>18877.9586105</v>
+        <v>18882.4630195</v>
       </c>
       <c r="O15">
-        <v>4870.513321509</v>
+        <v>4871.675459031</v>
       </c>
       <c r="P15">
-        <v>14007.445288991</v>
+        <v>14010.787560469</v>
       </c>
       <c r="Q15">
-        <v>14809.945288991</v>
+        <v>14813.287560469</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08084992638763056</v>
+        <v>0.08082739240127088</v>
       </c>
       <c r="T15">
         <v>0.80894670672681</v>
       </c>
       <c r="U15">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V15">
         <v>0.258</v>
       </c>
       <c r="W15">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2668,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>114.4892444222368</v>
+        <v>117.6758237898538</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2679,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07517062862469541</v>
+        <v>0.07500564439166769</v>
       </c>
       <c r="C16">
-        <v>21254.81764575925</v>
+        <v>21264.36728046385</v>
       </c>
       <c r="D16">
-        <v>23849.74764575925</v>
+        <v>23859.29728046385</v>
       </c>
       <c r="E16">
         <v>-1587.07</v>
@@ -2599,37 +2712,37 @@
         <v>19044.3</v>
       </c>
       <c r="M16">
-        <v>179.136881</v>
+        <v>174.285979</v>
       </c>
       <c r="N16">
-        <v>18865.163119</v>
+        <v>18870.014021</v>
       </c>
       <c r="O16">
-        <v>4867.212084702001</v>
+        <v>4868.463617418</v>
       </c>
       <c r="P16">
-        <v>13997.951034298</v>
+        <v>14001.550403582</v>
       </c>
       <c r="Q16">
-        <v>14800.451034298</v>
+        <v>14804.050403582</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.08116282863336675</v>
+        <v>0.08114009347868337</v>
       </c>
       <c r="T16">
         <v>0.8161684406162442</v>
       </c>
       <c r="U16">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V16">
         <v>0.258</v>
       </c>
       <c r="W16">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2750,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>106.3114412492199</v>
+        <v>109.2704078048642</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2761,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07501483929215223</v>
+        <v>0.07483951939422973</v>
       </c>
       <c r="C17">
-        <v>21017.52949830494</v>
+        <v>21027.76551893963</v>
       </c>
       <c r="D17">
-        <v>23859.95449830494</v>
+        <v>23870.19051893963</v>
       </c>
       <c r="E17">
         <v>-1339.575</v>
@@ -2681,37 +2794,37 @@
         <v>19044.3</v>
       </c>
       <c r="M17">
-        <v>191.9323725</v>
+        <v>186.7349775</v>
       </c>
       <c r="N17">
-        <v>18852.3676275</v>
+        <v>18857.5650225</v>
       </c>
       <c r="O17">
-        <v>4863.910847895</v>
+        <v>4865.251775805</v>
       </c>
       <c r="P17">
-        <v>13988.456779605</v>
+        <v>13992.313246695</v>
       </c>
       <c r="Q17">
-        <v>14790.956779605</v>
+        <v>14794.813246695</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08148309328488498</v>
+        <v>0.08146015222850557</v>
       </c>
       <c r="T17">
         <v>0.8235600976560179</v>
       </c>
       <c r="U17">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V17">
         <v>0.258</v>
       </c>
       <c r="W17">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2832,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>99.22401183260527</v>
+        <v>101.9857139512066</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2843,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07485904995960906</v>
+        <v>0.07467339439679176</v>
       </c>
       <c r="C18">
-        <v>20780.25009093835</v>
+        <v>20791.17370882721</v>
       </c>
       <c r="D18">
-        <v>23870.17009093835</v>
+        <v>23881.0937088272</v>
       </c>
       <c r="E18">
         <v>-1092.08</v>
@@ -2763,37 +2876,37 @@
         <v>19044.3</v>
       </c>
       <c r="M18">
-        <v>204.727864</v>
+        <v>199.183976</v>
       </c>
       <c r="N18">
-        <v>18839.572136</v>
+        <v>18845.116024</v>
       </c>
       <c r="O18">
-        <v>4860.609611088</v>
+        <v>4862.039934192</v>
       </c>
       <c r="P18">
-        <v>13978.962524912</v>
+        <v>13983.076089808</v>
       </c>
       <c r="Q18">
-        <v>14781.462524912</v>
+        <v>14785.576089808</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.08181098328524888</v>
+        <v>0.0817878314247521</v>
       </c>
       <c r="T18">
         <v>0.8311277465300718</v>
       </c>
       <c r="U18">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V18">
         <v>0.258</v>
       </c>
       <c r="W18">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2914,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>93.02251109306742</v>
+        <v>95.61160682925617</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2925,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07470326062706589</v>
+        <v>0.0745072693993538</v>
       </c>
       <c r="C19">
-        <v>20542.97943489045</v>
+        <v>20554.59186376931</v>
       </c>
       <c r="D19">
-        <v>23880.39443489045</v>
+        <v>23892.00686376931</v>
       </c>
       <c r="E19">
         <v>-844.585</v>
@@ -2845,37 +2958,37 @@
         <v>19044.3</v>
       </c>
       <c r="M19">
-        <v>217.5233555</v>
+        <v>211.6329745</v>
       </c>
       <c r="N19">
-        <v>18826.7766445</v>
+        <v>18832.6670255</v>
       </c>
       <c r="O19">
-        <v>4857.308374280999</v>
+        <v>4858.828092579</v>
       </c>
       <c r="P19">
-        <v>13969.468270219</v>
+        <v>13973.838932921</v>
       </c>
       <c r="Q19">
-        <v>14771.968270219</v>
+        <v>14776.338932921</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08214677424947697</v>
+        <v>0.08212340650524555</v>
       </c>
       <c r="T19">
         <v>0.8388777483890429</v>
       </c>
       <c r="U19">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V19">
         <v>0.258</v>
       </c>
       <c r="W19">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2996,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>87.55059867582816</v>
+        <v>89.98739466282935</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +3007,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07454747129452272</v>
+        <v>0.07434114440191583</v>
       </c>
       <c r="C20">
-        <v>20305.71754141145</v>
+        <v>20318.01999743365</v>
       </c>
       <c r="D20">
-        <v>23890.62754141145</v>
+        <v>23902.92999743365</v>
       </c>
       <c r="E20">
         <v>-597.0900000000001</v>
@@ -2927,37 +3040,37 @@
         <v>19044.3</v>
       </c>
       <c r="M20">
-        <v>230.318847</v>
+        <v>224.081973</v>
       </c>
       <c r="N20">
-        <v>18813.981153</v>
+        <v>18820.218027</v>
       </c>
       <c r="O20">
-        <v>4854.007137474</v>
+        <v>4855.616250966</v>
       </c>
       <c r="P20">
-        <v>13959.974015526</v>
+        <v>13964.601776034</v>
       </c>
       <c r="Q20">
-        <v>14762.474015526</v>
+        <v>14767.101776034</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.08249075523722282</v>
+        <v>0.0824671663437998</v>
       </c>
       <c r="T20">
         <v>0.8468167746835985</v>
       </c>
       <c r="U20">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V20">
         <v>0.258</v>
       </c>
       <c r="W20">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +3078,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>82.68667652717104</v>
+        <v>84.98809495933884</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +3089,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07439168196197954</v>
+        <v>0.07417501940447789</v>
       </c>
       <c r="C21">
-        <v>20068.46442177085</v>
+        <v>20081.45812351294</v>
       </c>
       <c r="D21">
-        <v>23900.86942177085</v>
+        <v>23913.86312351294</v>
       </c>
       <c r="E21">
         <v>-349.5950000000003</v>
@@ -3009,37 +3122,37 @@
         <v>19044.3</v>
       </c>
       <c r="M21">
-        <v>243.1143385</v>
+        <v>236.5309715</v>
       </c>
       <c r="N21">
-        <v>18801.1856615</v>
+        <v>18807.7690285</v>
       </c>
       <c r="O21">
-        <v>4850.705900667</v>
+        <v>4852.404409353</v>
       </c>
       <c r="P21">
-        <v>13950.479760833</v>
+        <v>13955.364619147</v>
       </c>
       <c r="Q21">
-        <v>14752.979760833</v>
+        <v>14757.864619147</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.08284322958269079</v>
+        <v>0.08281941407960233</v>
       </c>
       <c r="T21">
         <v>0.8549518263187605</v>
       </c>
       <c r="U21">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V21">
         <v>0.258</v>
       </c>
       <c r="W21">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3160,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>78.33474618363573</v>
+        <v>80.51503732989995</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3171,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07423589262943638</v>
+        <v>0.07400889440703992</v>
       </c>
       <c r="C22">
-        <v>19831.22008725748</v>
+        <v>19844.90625572496</v>
       </c>
       <c r="D22">
-        <v>23911.12008725748</v>
+        <v>23924.80625572497</v>
       </c>
       <c r="E22">
         <v>-102.0999999999995</v>
@@ -3091,37 +3204,37 @@
         <v>19044.3</v>
       </c>
       <c r="M22">
-        <v>255.9098300000001</v>
+        <v>248.97997</v>
       </c>
       <c r="N22">
-        <v>18788.39017</v>
+        <v>18795.32003</v>
       </c>
       <c r="O22">
-        <v>4847.40466386</v>
+        <v>4849.19256774</v>
       </c>
       <c r="P22">
-        <v>13940.98550614</v>
+        <v>13946.12746226</v>
       </c>
       <c r="Q22">
-        <v>14743.48550614</v>
+        <v>14748.62746226</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08320451578679545</v>
+        <v>0.0831804680087999</v>
       </c>
       <c r="T22">
         <v>0.8632902542448015</v>
       </c>
       <c r="U22">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V22">
         <v>0.258</v>
       </c>
       <c r="W22">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3242,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>74.41800887445392</v>
+        <v>76.48928546340494</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3253,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07408010329689318</v>
+        <v>0.07384276940960197</v>
       </c>
       <c r="C23">
-        <v>19593.98454917958</v>
+        <v>19608.3644078126</v>
       </c>
       <c r="D23">
-        <v>23921.37954917958</v>
+        <v>23935.7594078126</v>
       </c>
       <c r="E23">
         <v>145.3949999999995</v>
@@ -3173,37 +3286,37 @@
         <v>19044.3</v>
       </c>
       <c r="M23">
-        <v>268.7053215</v>
+        <v>261.4289684999999</v>
       </c>
       <c r="N23">
-        <v>18775.5946785</v>
+        <v>18782.8710315</v>
       </c>
       <c r="O23">
-        <v>4844.103427053</v>
+        <v>4845.980726127</v>
       </c>
       <c r="P23">
-        <v>13931.491251447</v>
+        <v>13936.890305373</v>
       </c>
       <c r="Q23">
-        <v>14733.991251447</v>
+        <v>14739.390305373</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.08357494847707998</v>
+        <v>0.08355066254379995</v>
       </c>
       <c r="T23">
         <v>0.8718397816120081</v>
       </c>
       <c r="U23">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V23">
         <v>0.258</v>
       </c>
       <c r="W23">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3324,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>70.87429416614661</v>
+        <v>72.84693853657615</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3335,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07392431396435002</v>
+        <v>0.073676644412164</v>
       </c>
       <c r="C24">
-        <v>19356.75781886476</v>
+        <v>19371.83259354393</v>
       </c>
       <c r="D24">
-        <v>23931.64781886476</v>
+        <v>23946.72259354393</v>
       </c>
       <c r="E24">
         <v>392.8900000000003</v>
@@ -3255,37 +3368,37 @@
         <v>19044.3</v>
       </c>
       <c r="M24">
-        <v>281.5008130000001</v>
+        <v>273.877967</v>
       </c>
       <c r="N24">
-        <v>18762.799187</v>
+        <v>18770.422033</v>
       </c>
       <c r="O24">
-        <v>4840.802190246</v>
+        <v>4842.768884514</v>
       </c>
       <c r="P24">
-        <v>13921.996996754</v>
+        <v>13927.653148486</v>
       </c>
       <c r="Q24">
-        <v>14724.496996754</v>
+        <v>14730.153148486</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.08395487944147438</v>
+        <v>0.0839303492463641</v>
       </c>
       <c r="T24">
         <v>0.880608527629656</v>
       </c>
       <c r="U24">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V24">
         <v>0.258</v>
       </c>
       <c r="W24">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3406,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>67.65273534041266</v>
+        <v>69.53571405764086</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3417,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07376852463180684</v>
+        <v>0.07351051941472604</v>
       </c>
       <c r="C25">
-        <v>19119.5399076601</v>
+        <v>19135.31082671225</v>
       </c>
       <c r="D25">
-        <v>23941.9249076601</v>
+        <v>23957.69582671225</v>
       </c>
       <c r="E25">
         <v>640.3850000000002</v>
@@ -3337,37 +3450,37 @@
         <v>19044.3</v>
       </c>
       <c r="M25">
-        <v>294.2963045</v>
+        <v>286.3269655</v>
       </c>
       <c r="N25">
-        <v>18750.0036955</v>
+        <v>18757.9730345</v>
       </c>
       <c r="O25">
-        <v>4837.500953439</v>
+        <v>4839.557042900999</v>
       </c>
       <c r="P25">
-        <v>13912.502742061</v>
+        <v>13918.415991599</v>
       </c>
       <c r="Q25">
-        <v>14715.002742061</v>
+        <v>14720.915991599</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.08434467874260629</v>
+        <v>0.08431989794120265</v>
       </c>
       <c r="T25">
         <v>0.8896050332841259</v>
       </c>
       <c r="U25">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V25">
         <v>0.258</v>
       </c>
       <c r="W25">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3488,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>64.71131206474256</v>
+        <v>66.51242214209127</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3499,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07361273529926368</v>
+        <v>0.07334439441728807</v>
       </c>
       <c r="C26">
-        <v>18882.3308269322</v>
+        <v>18898.79912113618</v>
       </c>
       <c r="D26">
-        <v>23952.21082693221</v>
+        <v>23968.67912113618</v>
       </c>
       <c r="E26">
         <v>887.8800000000001</v>
@@ -3419,37 +3532,37 @@
         <v>19044.3</v>
       </c>
       <c r="M26">
-        <v>307.091796</v>
+        <v>298.775964</v>
       </c>
       <c r="N26">
-        <v>18737.208204</v>
+        <v>18745.524036</v>
       </c>
       <c r="O26">
-        <v>4834.199716632</v>
+        <v>4836.345201288</v>
       </c>
       <c r="P26">
-        <v>13903.008487368</v>
+        <v>13909.178834712</v>
       </c>
       <c r="Q26">
-        <v>14705.508487368</v>
+        <v>14711.678834712</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.08474473592008377</v>
+        <v>0.08471969791748431</v>
       </c>
       <c r="T26">
         <v>0.8988382890873976</v>
       </c>
       <c r="U26">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V26">
         <v>0.258</v>
       </c>
       <c r="W26">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3570,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>62.01500739537827</v>
+        <v>63.74107121950412</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3581,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07345694596672049</v>
+        <v>0.07317826941985012</v>
       </c>
       <c r="C27">
-        <v>18645.13058806719</v>
+        <v>18662.29749065967</v>
       </c>
       <c r="D27">
-        <v>23962.50558806719</v>
+        <v>23979.67249065967</v>
       </c>
       <c r="E27">
         <v>1135.375</v>
@@ -3501,37 +3614,37 @@
         <v>19044.3</v>
       </c>
       <c r="M27">
-        <v>319.8872875</v>
+        <v>311.2249625</v>
       </c>
       <c r="N27">
-        <v>18724.4127125</v>
+        <v>18733.0750375</v>
       </c>
       <c r="O27">
-        <v>4830.898479824999</v>
+        <v>4833.133359675</v>
       </c>
       <c r="P27">
-        <v>13893.514232675</v>
+        <v>13899.941677825</v>
       </c>
       <c r="Q27">
-        <v>14696.014232675</v>
+        <v>14702.441677825</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.08515546128896066</v>
+        <v>0.08513015922646683</v>
       </c>
       <c r="T27">
         <v>0.9083177650454233</v>
       </c>
       <c r="U27">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V27">
         <v>0.258</v>
       </c>
       <c r="W27">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3652,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>59.53440709956315</v>
+        <v>61.19142837072395</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3663,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07330115663417733</v>
+        <v>0.07301214442241215</v>
       </c>
       <c r="C28">
-        <v>18407.93920247078</v>
+        <v>18425.80594915208</v>
       </c>
       <c r="D28">
-        <v>23972.80920247078</v>
+        <v>23990.67594915208</v>
       </c>
       <c r="E28">
         <v>1382.87</v>
@@ -3583,37 +3696,37 @@
         <v>19044.3</v>
       </c>
       <c r="M28">
-        <v>332.682779</v>
+        <v>323.673961</v>
       </c>
       <c r="N28">
-        <v>18711.617221</v>
+        <v>18720.626039</v>
       </c>
       <c r="O28">
-        <v>4827.597243018</v>
+        <v>4829.921518061999</v>
       </c>
       <c r="P28">
-        <v>13884.019977982</v>
+        <v>13890.704520938</v>
       </c>
       <c r="Q28">
-        <v>14686.519977982</v>
+        <v>14693.204520938</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.08557728734348287</v>
+        <v>0.08555171408434074</v>
       </c>
       <c r="T28">
         <v>0.9180534430563684</v>
       </c>
       <c r="U28">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V28">
         <v>0.258</v>
       </c>
       <c r="W28">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3734,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>57.24462221111841</v>
+        <v>58.83791189492688</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3745,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07314536730163415</v>
+        <v>0.07284601942497419</v>
       </c>
       <c r="C29">
-        <v>18170.75668156829</v>
+        <v>18189.32451050824</v>
       </c>
       <c r="D29">
-        <v>23983.12168156829</v>
+        <v>24001.68951050824</v>
       </c>
       <c r="E29">
         <v>1630.365000000001</v>
@@ -3665,37 +3778,37 @@
         <v>19044.3</v>
       </c>
       <c r="M29">
-        <v>345.4782705000001</v>
+        <v>336.1229595</v>
       </c>
       <c r="N29">
-        <v>18698.8217295</v>
+        <v>18708.1770405</v>
       </c>
       <c r="O29">
-        <v>4824.296006211</v>
+        <v>4826.709676449</v>
       </c>
       <c r="P29">
-        <v>13874.525723289</v>
+        <v>13881.467364051</v>
       </c>
       <c r="Q29">
-        <v>14677.025723289</v>
+        <v>14683.967364051</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.08601067027621116</v>
+        <v>0.08598481839037561</v>
       </c>
       <c r="T29">
         <v>0.9280558519717231</v>
       </c>
       <c r="U29">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V29">
         <v>0.258</v>
       </c>
       <c r="W29">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3816,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>55.12445101811402</v>
+        <v>56.65872997289254</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3827,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07298957796909097</v>
+        <v>0.07267989442753624</v>
       </c>
       <c r="C30">
-        <v>17933.58303680475</v>
+        <v>17952.8531886485</v>
       </c>
       <c r="D30">
-        <v>23993.44303680475</v>
+        <v>24012.7131886485</v>
       </c>
       <c r="E30">
         <v>1877.860000000001</v>
@@ -3747,37 +3860,37 @@
         <v>19044.3</v>
       </c>
       <c r="M30">
-        <v>358.273762</v>
+        <v>348.571958</v>
       </c>
       <c r="N30">
-        <v>18686.026238</v>
+        <v>18695.728042</v>
       </c>
       <c r="O30">
-        <v>4820.994769404</v>
+        <v>4823.497834836</v>
       </c>
       <c r="P30">
-        <v>13865.031468596</v>
+        <v>13872.230207164</v>
       </c>
       <c r="Q30">
-        <v>14667.531468596</v>
+        <v>14674.730207164</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.08645609162373746</v>
+        <v>0.08642995337157811</v>
       </c>
       <c r="T30">
         <v>0.938336105579171</v>
       </c>
       <c r="U30">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V30">
         <v>0.258</v>
       </c>
       <c r="W30">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3898,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>53.15572062460995</v>
+        <v>54.6352039024321</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3909,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.0728337886365478</v>
+        <v>0.07251376943009827</v>
       </c>
       <c r="C31">
-        <v>17696.41827964487</v>
+        <v>17716.39199751884</v>
       </c>
       <c r="D31">
-        <v>24003.77327964487</v>
+        <v>24023.74699751884</v>
       </c>
       <c r="E31">
         <v>2125.355</v>
@@ -3829,37 +3942,37 @@
         <v>19044.3</v>
       </c>
       <c r="M31">
-        <v>371.0692535</v>
+        <v>361.0209565</v>
       </c>
       <c r="N31">
-        <v>18673.2307465</v>
+        <v>18683.2790435</v>
       </c>
       <c r="O31">
-        <v>4817.693532597</v>
+        <v>4820.285993222999</v>
       </c>
       <c r="P31">
-        <v>13855.537213903</v>
+        <v>13862.993050277</v>
       </c>
       <c r="Q31">
-        <v>14658.037213903</v>
+        <v>14665.493050277</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.08691406005147578</v>
+        <v>0.08688762736633558</v>
       </c>
       <c r="T31">
         <v>0.9489059437952793</v>
       </c>
       <c r="U31">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V31">
         <v>0.258</v>
       </c>
       <c r="W31">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3980,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>51.32276474100271</v>
+        <v>52.75123135407238</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3991,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.07267799930400462</v>
+        <v>0.0723476444326603</v>
       </c>
       <c r="C32">
-        <v>17459.26242157311</v>
+        <v>17479.94095109082</v>
       </c>
       <c r="D32">
-        <v>24014.11242157311</v>
+        <v>24034.79095109082</v>
       </c>
       <c r="E32">
         <v>2372.849999999999</v>
@@ -3911,37 +4024,37 @@
         <v>19044.3</v>
       </c>
       <c r="M32">
-        <v>383.864745</v>
+        <v>373.469955</v>
       </c>
       <c r="N32">
-        <v>18660.435255</v>
+        <v>18670.830045</v>
       </c>
       <c r="O32">
-        <v>4814.39229579</v>
+        <v>4817.07415161</v>
       </c>
       <c r="P32">
-        <v>13846.04295921</v>
+        <v>13853.75589339</v>
       </c>
       <c r="Q32">
-        <v>14648.54295921</v>
+        <v>14656.25589339</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.08738511329143518</v>
+        <v>0.0873583777609433</v>
       </c>
       <c r="T32">
         <v>0.9597777773889907</v>
       </c>
       <c r="U32">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V32">
         <v>0.258</v>
       </c>
       <c r="W32">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +4062,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>49.61200591630264</v>
+        <v>50.9928569756033</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +4073,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.07252220997146146</v>
+        <v>0.07218151943522234</v>
       </c>
       <c r="C33">
-        <v>17222.11547409374</v>
+        <v>17243.50006336174</v>
       </c>
       <c r="D33">
-        <v>24024.46047409374</v>
+        <v>24045.84506336174</v>
       </c>
       <c r="E33">
         <v>2620.345</v>
@@ -3993,37 +4106,37 @@
         <v>19044.3</v>
       </c>
       <c r="M33">
-        <v>396.6602365000001</v>
+        <v>385.9189535</v>
       </c>
       <c r="N33">
-        <v>18647.6397635</v>
+        <v>18658.3810465</v>
       </c>
       <c r="O33">
-        <v>4811.091058983</v>
+        <v>4813.862309997</v>
       </c>
       <c r="P33">
-        <v>13836.548704517</v>
+        <v>13844.518736503</v>
       </c>
       <c r="Q33">
-        <v>14639.048704517</v>
+        <v>14647.018736503</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.08786982024849486</v>
+        <v>0.08784277309452514</v>
       </c>
       <c r="T33">
         <v>0.9709647365941142</v>
       </c>
       <c r="U33">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V33">
         <v>0.258</v>
       </c>
       <c r="W33">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4144,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>48.01161862867995</v>
+        <v>49.34792610542254</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4155,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07236642063891828</v>
+        <v>0.07201539443778437</v>
       </c>
       <c r="C34">
-        <v>16984.97744873086</v>
+        <v>17007.06934835466</v>
       </c>
       <c r="D34">
-        <v>24034.81744873086</v>
+        <v>24056.90934835466</v>
       </c>
       <c r="E34">
         <v>2867.84</v>
@@ -4075,37 +4188,37 @@
         <v>19044.3</v>
       </c>
       <c r="M34">
-        <v>409.455728</v>
+        <v>398.367952</v>
       </c>
       <c r="N34">
-        <v>18634.844272</v>
+        <v>18645.932048</v>
       </c>
       <c r="O34">
-        <v>4807.789822176</v>
+        <v>4810.650468383999</v>
       </c>
       <c r="P34">
-        <v>13827.054449824</v>
+        <v>13835.281579616</v>
       </c>
       <c r="Q34">
-        <v>14629.554449824</v>
+        <v>14637.781579616</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.08836878329252688</v>
+        <v>0.08834141534968291</v>
       </c>
       <c r="T34">
         <v>0.9824807240111529</v>
       </c>
       <c r="U34">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V34">
         <v>0.258</v>
       </c>
       <c r="W34">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4226,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>46.51125554653371</v>
+        <v>47.80580341462809</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4237,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.0722106313063751</v>
+        <v>0.07184926944034642</v>
       </c>
       <c r="C35">
-        <v>16747.84835702846</v>
+        <v>16770.64882011846</v>
       </c>
       <c r="D35">
-        <v>24045.18335702845</v>
+        <v>24067.98382011846</v>
       </c>
       <c r="E35">
         <v>3115.335</v>
@@ -4157,37 +4270,37 @@
         <v>19044.3</v>
       </c>
       <c r="M35">
-        <v>422.2512195</v>
+        <v>410.8169505</v>
       </c>
       <c r="N35">
-        <v>18622.0487805</v>
+        <v>18633.4830495</v>
       </c>
       <c r="O35">
-        <v>4804.488585368999</v>
+        <v>4807.438626771</v>
       </c>
       <c r="P35">
-        <v>13817.560195131</v>
+        <v>13826.044422729</v>
       </c>
       <c r="Q35">
-        <v>14620.060195131</v>
+        <v>14628.544422729</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.08888264075578374</v>
+        <v>0.08885494244827824</v>
       </c>
       <c r="T35">
         <v>0.9943404722466107</v>
       </c>
       <c r="U35">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V35">
         <v>0.258</v>
       </c>
       <c r="W35">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4308,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>45.10182356027511</v>
+        <v>46.35714270509391</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4319,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.07205484197383193</v>
+        <v>0.07168314444290844</v>
       </c>
       <c r="C36">
-        <v>16510.72821055043</v>
+        <v>16534.23849272788</v>
       </c>
       <c r="D36">
-        <v>24055.55821055043</v>
+        <v>24079.06849272788</v>
       </c>
       <c r="E36">
         <v>3362.83</v>
@@ -4239,37 +4352,37 @@
         <v>19044.3</v>
       </c>
       <c r="M36">
-        <v>435.046711</v>
+        <v>423.265949</v>
       </c>
       <c r="N36">
-        <v>18609.253289</v>
+        <v>18621.034051</v>
       </c>
       <c r="O36">
-        <v>4801.187348562</v>
+        <v>4804.226785158</v>
       </c>
       <c r="P36">
-        <v>13808.065940438</v>
+        <v>13816.807265842</v>
       </c>
       <c r="Q36">
-        <v>14610.565940438</v>
+        <v>14619.307265842</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.08941206965732111</v>
+        <v>0.08938403097410372</v>
       </c>
       <c r="T36">
         <v>1.006559606792234</v>
       </c>
       <c r="U36">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V36">
         <v>0.258</v>
       </c>
       <c r="W36">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4390,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>43.77529933791408</v>
+        <v>44.99369733141467</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4401,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.07189905264128876</v>
+        <v>0.07151701944547049</v>
       </c>
       <c r="C37">
-        <v>16273.61702088067</v>
+        <v>16297.83838028364</v>
       </c>
       <c r="D37">
-        <v>24065.94202088067</v>
+        <v>24090.16338028364</v>
       </c>
       <c r="E37">
         <v>3610.325000000001</v>
@@ -4321,37 +4434,37 @@
         <v>19044.3</v>
       </c>
       <c r="M37">
-        <v>447.8422025</v>
+        <v>435.7149475</v>
       </c>
       <c r="N37">
-        <v>18596.4577975</v>
+        <v>18608.5850525</v>
       </c>
       <c r="O37">
-        <v>4797.886111755</v>
+        <v>4801.014943544999</v>
       </c>
       <c r="P37">
-        <v>13798.571685745</v>
+        <v>13807.570108955</v>
       </c>
       <c r="Q37">
-        <v>14601.071685745</v>
+        <v>14610.070108955</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.08995778867890579</v>
+        <v>0.0899293991468777</v>
       </c>
       <c r="T37">
         <v>1.019154714708492</v>
       </c>
       <c r="U37">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V37">
         <v>0.258</v>
       </c>
       <c r="W37">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4472,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>42.52457649968796</v>
+        <v>43.70816312194568</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4483,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.0717432633087456</v>
+        <v>0.07135089444803253</v>
       </c>
       <c r="C38">
-        <v>16036.51479962304</v>
+        <v>16061.44849691243</v>
       </c>
       <c r="D38">
-        <v>24076.33479962304</v>
+        <v>24101.26849691243</v>
       </c>
       <c r="E38">
         <v>3857.82</v>
@@ -4403,37 +4516,37 @@
         <v>19044.3</v>
       </c>
       <c r="M38">
-        <v>460.637694</v>
+        <v>448.163946</v>
       </c>
       <c r="N38">
-        <v>18583.662306</v>
+        <v>18596.136054</v>
       </c>
       <c r="O38">
-        <v>4794.584874948</v>
+        <v>4797.803101932</v>
       </c>
       <c r="P38">
-        <v>13789.077431052</v>
+        <v>13798.332952068</v>
       </c>
       <c r="Q38">
-        <v>14591.577431052</v>
+        <v>14600.832952068</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.09052056141991499</v>
+        <v>0.09049181007505083</v>
       </c>
       <c r="T38">
         <v>1.032143419747133</v>
       </c>
       <c r="U38">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V38">
         <v>0.258</v>
       </c>
       <c r="W38">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4554,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>41.34333826358552</v>
+        <v>42.49404747966942</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4565,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.07158747397620241</v>
+        <v>0.07118476945059457</v>
       </c>
       <c r="C39">
-        <v>15799.42155840148</v>
+        <v>15825.06885676702</v>
       </c>
       <c r="D39">
-        <v>24086.73655840148</v>
+        <v>24112.38385676702</v>
       </c>
       <c r="E39">
         <v>4105.315000000001</v>
@@ -4485,37 +4598,37 @@
         <v>19044.3</v>
       </c>
       <c r="M39">
-        <v>473.4331855</v>
+        <v>460.6129445</v>
       </c>
       <c r="N39">
-        <v>18570.8668145</v>
+        <v>18583.6870555</v>
       </c>
       <c r="O39">
-        <v>4791.283638141</v>
+        <v>4794.591260319</v>
       </c>
       <c r="P39">
-        <v>13779.583176359</v>
+        <v>13789.095795181</v>
       </c>
       <c r="Q39">
-        <v>14582.083176359</v>
+        <v>14591.595795181</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.09110119996222604</v>
+        <v>0.09107207531840408</v>
       </c>
       <c r="T39">
         <v>1.04554446462827</v>
       </c>
       <c r="U39">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V39">
         <v>0.258</v>
       </c>
       <c r="W39">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4636,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>40.22595074294807</v>
+        <v>41.34555970994862</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4647,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.07143168464365925</v>
+        <v>0.0710186444531566</v>
       </c>
       <c r="C40">
-        <v>15562.33730886003</v>
+        <v>15588.69947402628</v>
       </c>
       <c r="D40">
-        <v>24097.14730886003</v>
+        <v>24123.50947402628</v>
       </c>
       <c r="E40">
         <v>4352.809999999999</v>
@@ -4567,37 +4680,37 @@
         <v>19044.3</v>
       </c>
       <c r="M40">
-        <v>486.228677</v>
+        <v>473.0619429999999</v>
       </c>
       <c r="N40">
-        <v>18558.071323</v>
+        <v>18571.238057</v>
       </c>
       <c r="O40">
-        <v>4787.982401334</v>
+        <v>4791.379418705999</v>
       </c>
       <c r="P40">
-        <v>13770.088921666</v>
+        <v>13779.858638294</v>
       </c>
       <c r="Q40">
-        <v>14572.588921666</v>
+        <v>14582.358638294</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.09170056878009555</v>
+        <v>0.09167105879541387</v>
       </c>
       <c r="T40">
         <v>1.059377801279767</v>
       </c>
       <c r="U40">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V40">
         <v>0.258</v>
       </c>
       <c r="W40">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4718,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>39.16737309181786</v>
+        <v>40.25751866494998</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4729,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.07127589531111608</v>
+        <v>0.07085251945571866</v>
       </c>
       <c r="C41">
-        <v>15325.26206266286</v>
+        <v>15352.34036289527</v>
       </c>
       <c r="D41">
-        <v>24107.56706266286</v>
+        <v>24134.64536289527</v>
       </c>
       <c r="E41">
         <v>4600.305</v>
@@ -4649,37 +4762,37 @@
         <v>19044.3</v>
       </c>
       <c r="M41">
-        <v>499.0241685</v>
+        <v>485.5109415</v>
       </c>
       <c r="N41">
-        <v>18545.2758315</v>
+        <v>18558.7890585</v>
       </c>
       <c r="O41">
-        <v>4784.681164527</v>
+        <v>4788.167577093</v>
       </c>
       <c r="P41">
-        <v>13760.594666973</v>
+        <v>13770.621481407</v>
       </c>
       <c r="Q41">
-        <v>14563.094666973</v>
+        <v>14573.121481407</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.09231958903461651</v>
+        <v>0.09228968107494862</v>
       </c>
       <c r="T41">
         <v>1.073664689952624</v>
       </c>
       <c r="U41">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V41">
         <v>0.258</v>
       </c>
       <c r="W41">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4800,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>38.16308147407894</v>
+        <v>39.22527459661792</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4811,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.07112010597857289</v>
+        <v>0.07068639445828069</v>
       </c>
       <c r="C42">
-        <v>15088.19583149433</v>
+        <v>15115.9915376053</v>
       </c>
       <c r="D42">
-        <v>24117.99583149433</v>
+        <v>24145.79153760531</v>
       </c>
       <c r="E42">
         <v>4847.800000000001</v>
@@ -4731,37 +4844,37 @@
         <v>19044.3</v>
       </c>
       <c r="M42">
-        <v>511.8196600000001</v>
+        <v>497.95994</v>
       </c>
       <c r="N42">
-        <v>18532.48034</v>
+        <v>18546.34006</v>
       </c>
       <c r="O42">
-        <v>4781.37992772</v>
+        <v>4784.95573548</v>
       </c>
       <c r="P42">
-        <v>13751.10041228</v>
+        <v>13761.38432452</v>
       </c>
       <c r="Q42">
-        <v>14553.60041228</v>
+        <v>14563.88432452</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.09295924329762149</v>
+        <v>0.09292892409713449</v>
       </c>
       <c r="T42">
         <v>1.08842780824791</v>
       </c>
       <c r="U42">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V42">
         <v>0.258</v>
       </c>
       <c r="W42">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4882,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>37.20900443722696</v>
+        <v>38.24464273170247</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4893,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.07096431664602972</v>
+        <v>0.07052026946084272</v>
       </c>
       <c r="C43">
-        <v>14851.13862705901</v>
+        <v>14879.65301241399</v>
       </c>
       <c r="D43">
-        <v>24128.43362705901</v>
+        <v>24156.94801241399</v>
       </c>
       <c r="E43">
         <v>5095.295</v>
@@ -4813,37 +4926,37 @@
         <v>19044.3</v>
       </c>
       <c r="M43">
-        <v>524.6151515</v>
+        <v>510.4089385</v>
       </c>
       <c r="N43">
-        <v>18519.6848485</v>
+        <v>18533.8910615</v>
       </c>
       <c r="O43">
-        <v>4778.078690913</v>
+        <v>4781.743893867</v>
       </c>
       <c r="P43">
-        <v>13741.606157587</v>
+        <v>13752.147167633</v>
       </c>
       <c r="Q43">
-        <v>14544.106157587</v>
+        <v>14554.647167633</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.09362058075598256</v>
+        <v>0.0935898363743097</v>
       </c>
       <c r="T43">
         <v>1.103691371231171</v>
       </c>
       <c r="U43">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V43">
         <v>0.258</v>
       </c>
       <c r="W43">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4964,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>36.30146774363607</v>
+        <v>37.31184656751461</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4975,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.07080852731348655</v>
+        <v>0.07035414446340477</v>
       </c>
       <c r="C44">
-        <v>14614.09046108176</v>
+        <v>14643.32480160529</v>
       </c>
       <c r="D44">
-        <v>24138.88046108176</v>
+        <v>24168.11480160529</v>
       </c>
       <c r="E44">
         <v>5342.789999999999</v>
@@ -4895,37 +5008,37 @@
         <v>19044.3</v>
       </c>
       <c r="M44">
-        <v>537.4106429999999</v>
+        <v>522.8579369999999</v>
       </c>
       <c r="N44">
-        <v>18506.889357</v>
+        <v>18521.442063</v>
       </c>
       <c r="O44">
-        <v>4774.777454106</v>
+        <v>4778.532052254</v>
       </c>
       <c r="P44">
-        <v>13732.111902894</v>
+        <v>13742.910010746</v>
       </c>
       <c r="Q44">
-        <v>14534.611902894</v>
+        <v>14545.410010746</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.09430472295428716</v>
+        <v>0.09427353873000821</v>
       </c>
       <c r="T44">
         <v>1.119481263972476</v>
       </c>
       <c r="U44">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V44">
         <v>0.258</v>
       </c>
       <c r="W44">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +5046,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>35.43714708307331</v>
+        <v>36.42346926828807</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +5057,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.07065273798094339</v>
+        <v>0.07018801946596681</v>
       </c>
       <c r="C45">
-        <v>14377.05134530775</v>
+        <v>14407.00691948959</v>
       </c>
       <c r="D45">
-        <v>24149.33634530775</v>
+        <v>24179.29191948959</v>
       </c>
       <c r="E45">
         <v>5590.285</v>
@@ -4977,37 +5090,37 @@
         <v>19044.3</v>
       </c>
       <c r="M45">
-        <v>550.2061345000001</v>
+        <v>535.3069355</v>
       </c>
       <c r="N45">
-        <v>18494.0938655</v>
+        <v>18508.9930645</v>
       </c>
       <c r="O45">
-        <v>4771.476217298999</v>
+        <v>4775.320210641</v>
       </c>
       <c r="P45">
-        <v>13722.617648201</v>
+        <v>13733.672853859</v>
       </c>
       <c r="Q45">
-        <v>14525.117648201</v>
+        <v>14536.172853859</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.09501287014200592</v>
+        <v>0.09498123064204703</v>
       </c>
       <c r="T45">
         <v>1.135825188038038</v>
       </c>
       <c r="U45">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V45">
         <v>0.258</v>
       </c>
       <c r="W45">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5128,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>34.61302738346694</v>
+        <v>35.57641184344416</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5139,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.0704969486484002</v>
+        <v>0.07002189446852884</v>
       </c>
       <c r="C46">
-        <v>14140.02129150251</v>
+        <v>14170.69938040378</v>
       </c>
       <c r="D46">
-        <v>24159.80129150251</v>
+        <v>24190.47938040378</v>
       </c>
       <c r="E46">
         <v>5837.780000000001</v>
@@ -5059,37 +5172,37 @@
         <v>19044.3</v>
       </c>
       <c r="M46">
-        <v>563.0016260000001</v>
+        <v>547.755934</v>
       </c>
       <c r="N46">
-        <v>18481.298374</v>
+        <v>18496.544066</v>
       </c>
       <c r="O46">
-        <v>4768.174980492</v>
+        <v>4772.108369028</v>
       </c>
       <c r="P46">
-        <v>13713.123393508</v>
+        <v>13724.435696972</v>
       </c>
       <c r="Q46">
-        <v>14515.623393508</v>
+        <v>14526.935696972</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.09574630830071464</v>
+        <v>0.09571419726523006</v>
       </c>
       <c r="T46">
         <v>1.152752823677369</v>
       </c>
       <c r="U46">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V46">
         <v>0.258</v>
       </c>
       <c r="W46">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5210,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>33.82636767020633</v>
+        <v>34.76785702882043</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5221,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.07034115931585702</v>
+        <v>0.06985576947109087</v>
       </c>
       <c r="C47">
-        <v>13903.00031145197</v>
+        <v>13934.40219871128</v>
       </c>
       <c r="D47">
-        <v>24170.27531145197</v>
+        <v>24201.67719871128</v>
       </c>
       <c r="E47">
         <v>6085.275</v>
@@ -5141,37 +5254,37 @@
         <v>19044.3</v>
       </c>
       <c r="M47">
-        <v>575.7971175</v>
+        <v>560.2049324999999</v>
       </c>
       <c r="N47">
-        <v>18468.5028825</v>
+        <v>18484.0950675</v>
       </c>
       <c r="O47">
-        <v>4764.873743685001</v>
+        <v>4768.896527415</v>
       </c>
       <c r="P47">
-        <v>13703.629138815</v>
+        <v>13715.198540085</v>
       </c>
       <c r="Q47">
-        <v>14506.129138815</v>
+        <v>14517.698540085</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.09650641693792186</v>
+        <v>0.09647381722016524</v>
       </c>
       <c r="T47">
         <v>1.170296009703585</v>
       </c>
       <c r="U47">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V47">
         <v>0.258</v>
       </c>
       <c r="W47">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5292,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>33.07467061086842</v>
+        <v>33.99523798373554</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5303,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.07018536998331386</v>
+        <v>0.06968964447365292</v>
       </c>
       <c r="C48">
-        <v>13665.98841696249</v>
+        <v>13698.11538880212</v>
       </c>
       <c r="D48">
-        <v>24180.75841696249</v>
+        <v>24212.88538880212</v>
       </c>
       <c r="E48">
         <v>6332.77</v>
@@ -5223,37 +5336,37 @@
         <v>19044.3</v>
       </c>
       <c r="M48">
-        <v>588.592609</v>
+        <v>572.6539309999999</v>
       </c>
       <c r="N48">
-        <v>18455.707391</v>
+        <v>18471.646069</v>
       </c>
       <c r="O48">
-        <v>4761.572506878</v>
+        <v>4765.684685802</v>
       </c>
       <c r="P48">
-        <v>13694.134884122</v>
+        <v>13705.961383198</v>
       </c>
       <c r="Q48">
-        <v>14496.634884122</v>
+        <v>14508.461383198</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.0972946777468775</v>
+        <v>0.0972615712475054</v>
       </c>
       <c r="T48">
         <v>1.188488943360402</v>
       </c>
       <c r="U48">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V48">
         <v>0.258</v>
       </c>
       <c r="W48">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5374,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>32.35565603237128</v>
+        <v>33.25621107104563</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5385,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.07002958065077068</v>
+        <v>0.06952351947621495</v>
       </c>
       <c r="C49">
-        <v>13428.98561986096</v>
+        <v>13461.83896509301</v>
       </c>
       <c r="D49">
-        <v>24191.25061986096</v>
+        <v>24224.10396509301</v>
       </c>
       <c r="E49">
         <v>6580.265000000001</v>
@@ -5305,37 +5418,37 @@
         <v>19044.3</v>
       </c>
       <c r="M49">
-        <v>601.3881005000001</v>
+        <v>585.1029295000001</v>
       </c>
       <c r="N49">
-        <v>18442.9118995</v>
+        <v>18459.1970705</v>
       </c>
       <c r="O49">
-        <v>4758.271270071</v>
+        <v>4762.472844189</v>
       </c>
       <c r="P49">
-        <v>13684.640629429</v>
+        <v>13696.724226311</v>
       </c>
       <c r="Q49">
-        <v>14487.140629429</v>
+        <v>14499.224226311</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.09811268424673712</v>
+        <v>0.098079051841915</v>
       </c>
       <c r="T49">
         <v>1.207368402815589</v>
       </c>
       <c r="U49">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V49">
         <v>0.258</v>
       </c>
       <c r="W49">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5456,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>31.66723781891657</v>
+        <v>32.5486321120872</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5467,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.0698737913182275</v>
+        <v>0.06935739447877698</v>
       </c>
       <c r="C50">
-        <v>13191.99193199477</v>
+        <v>13225.57294202736</v>
       </c>
       <c r="D50">
-        <v>24201.75193199478</v>
+        <v>24235.33294202736</v>
       </c>
       <c r="E50">
         <v>6827.76</v>
@@ -5387,37 +5500,37 @@
         <v>19044.3</v>
       </c>
       <c r="M50">
-        <v>614.1835920000001</v>
+        <v>597.551928</v>
       </c>
       <c r="N50">
-        <v>18430.116408</v>
+        <v>18446.748072</v>
       </c>
       <c r="O50">
-        <v>4754.970033264</v>
+        <v>4759.261002576</v>
       </c>
       <c r="P50">
-        <v>13675.146374736</v>
+        <v>13687.487069424</v>
       </c>
       <c r="Q50">
-        <v>14477.646374736</v>
+        <v>14489.987069424</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.09896215253505289</v>
+        <v>0.09892797399764805</v>
       </c>
       <c r="T50">
         <v>1.226973995326745</v>
       </c>
       <c r="U50">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V50">
         <v>0.258</v>
       </c>
       <c r="W50">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5538,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>31.00750369768913</v>
+        <v>31.87053560975206</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5549,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.06971800198568433</v>
+        <v>0.06919126948133902</v>
       </c>
       <c r="C51">
-        <v>12955.00736523193</v>
+        <v>12989.31733407542</v>
       </c>
       <c r="D51">
-        <v>24212.26236523193</v>
+        <v>24246.57233407542</v>
       </c>
       <c r="E51">
         <v>7075.254999999999</v>
@@ -5469,37 +5582,37 @@
         <v>19044.3</v>
       </c>
       <c r="M51">
-        <v>626.9790835</v>
+        <v>610.0009264999999</v>
       </c>
       <c r="N51">
-        <v>18417.3209165</v>
+        <v>18434.2990735</v>
       </c>
       <c r="O51">
-        <v>4751.668796457</v>
+        <v>4756.049160963</v>
       </c>
       <c r="P51">
-        <v>13665.652120043</v>
+        <v>13678.249912537</v>
       </c>
       <c r="Q51">
-        <v>14468.152120043</v>
+        <v>14480.749912537</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.09984493330526339</v>
+        <v>0.09981018721831182</v>
       </c>
       <c r="T51">
         <v>1.247348434603045</v>
       </c>
       <c r="U51">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V51">
         <v>0.258</v>
       </c>
       <c r="W51">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5620,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>30.37469749977712</v>
+        <v>31.22011651567549</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5631,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.06956221265314116</v>
+        <v>0.06902514448390107</v>
       </c>
       <c r="C52">
-        <v>12718.03193146101</v>
+        <v>12753.07215573425</v>
       </c>
       <c r="D52">
-        <v>24222.78193146101</v>
+        <v>24257.82215573425</v>
       </c>
       <c r="E52">
         <v>7322.75</v>
@@ -5551,37 +5664,37 @@
         <v>19044.3</v>
       </c>
       <c r="M52">
-        <v>639.774575</v>
+        <v>622.449925</v>
       </c>
       <c r="N52">
-        <v>18404.525425</v>
+        <v>18421.850075</v>
       </c>
       <c r="O52">
-        <v>4748.36755965</v>
+        <v>4752.83731935</v>
       </c>
       <c r="P52">
-        <v>13656.15786535</v>
+        <v>13669.01275565</v>
       </c>
       <c r="Q52">
-        <v>14458.65786535</v>
+        <v>14471.51275565</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1007630253062823</v>
+        <v>0.1007276889678021</v>
       </c>
       <c r="T52">
         <v>1.268537851450396</v>
       </c>
       <c r="U52">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V52">
         <v>0.258</v>
       </c>
       <c r="W52">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5702,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>29.76720354978158</v>
+        <v>30.59571418536198</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5713,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.06940642332059799</v>
+        <v>0.0688590194864631</v>
       </c>
       <c r="C53">
-        <v>12481.06564259132</v>
+        <v>12516.83742152786</v>
       </c>
       <c r="D53">
-        <v>24233.31064259132</v>
+        <v>24269.08242152786</v>
       </c>
       <c r="E53">
         <v>7570.245000000001</v>
@@ -5633,37 +5746,37 @@
         <v>19044.3</v>
       </c>
       <c r="M53">
-        <v>652.5700665000001</v>
+        <v>634.8989235</v>
       </c>
       <c r="N53">
-        <v>18391.7299335</v>
+        <v>18409.4010765</v>
       </c>
       <c r="O53">
-        <v>4745.066322842999</v>
+        <v>4749.625477737</v>
       </c>
       <c r="P53">
-        <v>13646.663610657</v>
+        <v>13659.775598763</v>
       </c>
       <c r="Q53">
-        <v>14449.163610657</v>
+        <v>14462.275598763</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1017185904502</v>
+        <v>0.101682639768292</v>
       </c>
       <c r="T53">
         <v>1.290592142454782</v>
       </c>
       <c r="U53">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V53">
         <v>0.258</v>
       </c>
       <c r="W53">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5784,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>29.18353289194272</v>
+        <v>29.99579822094311</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5795,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.06925063398805481</v>
+        <v>0.06869289448902513</v>
       </c>
       <c r="C54">
-        <v>12244.10851055285</v>
+        <v>12280.61314600724</v>
       </c>
       <c r="D54">
-        <v>24243.84851055285</v>
+        <v>24280.35314600724</v>
       </c>
       <c r="E54">
         <v>7817.74</v>
@@ -5715,37 +5828,37 @@
         <v>19044.3</v>
       </c>
       <c r="M54">
-        <v>665.3655580000001</v>
+        <v>647.3479219999999</v>
       </c>
       <c r="N54">
-        <v>18378.934442</v>
+        <v>18396.952078</v>
       </c>
       <c r="O54">
-        <v>4741.765086036</v>
+        <v>4746.413636124</v>
       </c>
       <c r="P54">
-        <v>13637.169355964</v>
+        <v>13650.538441876</v>
       </c>
       <c r="Q54">
-        <v>14439.669355964</v>
+        <v>14453.038441876</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1027139708084475</v>
+        <v>0.102677380185469</v>
       </c>
       <c r="T54">
         <v>1.313565362251017</v>
       </c>
       <c r="U54">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V54">
         <v>0.258</v>
       </c>
       <c r="W54">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5866,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>28.6223111055592</v>
+        <v>29.41895594746344</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5877,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.06909484465551163</v>
+        <v>0.06852676949158718</v>
       </c>
       <c r="C55">
-        <v>12007.16054729635</v>
+        <v>12044.39934375038</v>
       </c>
       <c r="D55">
-        <v>24254.39554729635</v>
+        <v>24291.63434375038</v>
       </c>
       <c r="E55">
         <v>8065.235000000001</v>
@@ -5797,37 +5910,37 @@
         <v>19044.3</v>
       </c>
       <c r="M55">
-        <v>678.1610495000001</v>
+        <v>659.7969204999999</v>
       </c>
       <c r="N55">
-        <v>18366.1389505</v>
+        <v>18384.5030795</v>
       </c>
       <c r="O55">
-        <v>4738.463849229001</v>
+        <v>4743.201794511</v>
       </c>
       <c r="P55">
-        <v>13627.675101271</v>
+        <v>13641.301284989</v>
       </c>
       <c r="Q55">
-        <v>14430.175101271</v>
+        <v>14443.801284989</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1037517077776843</v>
+        <v>0.1037144499821004</v>
       </c>
       <c r="T55">
         <v>1.33751616586837</v>
       </c>
       <c r="U55">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V55">
         <v>0.258</v>
       </c>
       <c r="W55">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5948,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>28.08226749979394</v>
+        <v>28.86388130694526</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5959,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.06893905532296846</v>
+        <v>0.06836064449414922</v>
       </c>
       <c r="C56">
-        <v>11770.22176479338</v>
+        <v>11808.19602936243</v>
       </c>
       <c r="D56">
-        <v>24264.95176479339</v>
+        <v>24302.92602936243</v>
       </c>
       <c r="E56">
         <v>8312.730000000001</v>
@@ -5879,37 +5992,37 @@
         <v>19044.3</v>
       </c>
       <c r="M56">
-        <v>690.9565410000001</v>
+        <v>672.2459190000001</v>
       </c>
       <c r="N56">
-        <v>18353.343459</v>
+        <v>18372.054081</v>
       </c>
       <c r="O56">
-        <v>4735.162612422</v>
+        <v>4739.989952898</v>
       </c>
       <c r="P56">
-        <v>13618.180846578</v>
+        <v>13632.064128102</v>
       </c>
       <c r="Q56">
-        <v>14420.680846578</v>
+        <v>14434.564128102</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1048345637455836</v>
+        <v>0.1047966097698896</v>
       </c>
       <c r="T56">
         <v>1.362508308773432</v>
       </c>
       <c r="U56">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V56">
         <v>0.258</v>
       </c>
       <c r="W56">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +6030,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>27.56222550905701</v>
+        <v>28.32936498644627</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +6041,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.06878326599042529</v>
+        <v>0.06819451949671125</v>
       </c>
       <c r="C57">
-        <v>11533.29217503637</v>
+        <v>11572.00321747569</v>
       </c>
       <c r="D57">
-        <v>24275.51717503637</v>
+        <v>24314.22821747569</v>
       </c>
       <c r="E57">
         <v>8560.225</v>
@@ -5961,37 +6074,37 @@
         <v>19044.3</v>
       </c>
       <c r="M57">
-        <v>703.7520325</v>
+        <v>684.6949175</v>
       </c>
       <c r="N57">
-        <v>18340.5479675</v>
+        <v>18359.6050825</v>
       </c>
       <c r="O57">
-        <v>4731.861375615</v>
+        <v>4736.778111285</v>
       </c>
       <c r="P57">
-        <v>13608.686591885</v>
+        <v>13622.826971215</v>
       </c>
       <c r="Q57">
-        <v>14411.186591885</v>
+        <v>14425.326971215</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1059655466453895</v>
+        <v>0.1059268655482472</v>
       </c>
       <c r="T57">
         <v>1.388611213585387</v>
       </c>
       <c r="U57">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V57">
         <v>0.258</v>
       </c>
       <c r="W57">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +6112,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>27.06109413616507</v>
+        <v>27.81428562305634</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6123,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06862747665788212</v>
+        <v>0.0680283944992733</v>
       </c>
       <c r="C58">
-        <v>11296.3717900386</v>
+        <v>11335.82092274967</v>
       </c>
       <c r="D58">
-        <v>24286.0917900386</v>
+        <v>24325.54092274967</v>
       </c>
       <c r="E58">
         <v>8807.720000000001</v>
@@ -6043,37 +6156,37 @@
         <v>19044.3</v>
       </c>
       <c r="M58">
-        <v>716.5475240000001</v>
+        <v>697.143916</v>
       </c>
       <c r="N58">
-        <v>18327.752476</v>
+        <v>18347.156084</v>
       </c>
       <c r="O58">
-        <v>4728.560138807999</v>
+        <v>4733.566269672</v>
       </c>
       <c r="P58">
-        <v>13599.192337192</v>
+        <v>13613.589814328</v>
       </c>
       <c r="Q58">
-        <v>14401.692337192</v>
+        <v>14416.089814328</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.107147937858823</v>
+        <v>0.1071084965892575</v>
       </c>
       <c r="T58">
         <v>1.415900614070612</v>
       </c>
       <c r="U58">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V58">
         <v>0.258</v>
       </c>
       <c r="W58">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6194,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>26.57786031230497</v>
+        <v>27.31760195121605</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6205,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06847168732533895</v>
+        <v>0.06786226950183533</v>
       </c>
       <c r="C59">
-        <v>11059.46062183433</v>
+        <v>11099.6491598712</v>
       </c>
       <c r="D59">
-        <v>24296.67562183433</v>
+        <v>24336.8641598712</v>
       </c>
       <c r="E59">
         <v>9055.215000000002</v>
@@ -6125,37 +6238,37 @@
         <v>19044.3</v>
       </c>
       <c r="M59">
-        <v>729.3430155000001</v>
+        <v>709.5929145000001</v>
       </c>
       <c r="N59">
-        <v>18314.9569845</v>
+        <v>18334.7070855</v>
       </c>
       <c r="O59">
-        <v>4725.258902001</v>
+        <v>4730.354428058999</v>
       </c>
       <c r="P59">
-        <v>13589.698082499</v>
+        <v>13604.352657441</v>
       </c>
       <c r="Q59">
-        <v>14392.198082499</v>
+        <v>14406.852657441</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1083853240124162</v>
+        <v>0.1083450872135706</v>
       </c>
       <c r="T59">
         <v>1.444459288997011</v>
       </c>
       <c r="U59">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V59">
         <v>0.258</v>
       </c>
       <c r="W59">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6276,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>26.11158206121191</v>
+        <v>26.83834577663331</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6287,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.06831589799279578</v>
+        <v>0.06769614450439737</v>
       </c>
       <c r="C60">
-        <v>10822.5586824788</v>
+        <v>10863.48794355447</v>
       </c>
       <c r="D60">
-        <v>24307.2686824788</v>
+        <v>24348.19794355447</v>
       </c>
       <c r="E60">
         <v>9302.709999999999</v>
@@ -6207,37 +6320,37 @@
         <v>19044.3</v>
       </c>
       <c r="M60">
-        <v>742.138507</v>
+        <v>722.0419129999999</v>
       </c>
       <c r="N60">
-        <v>18302.161493</v>
+        <v>18322.258087</v>
       </c>
       <c r="O60">
-        <v>4721.957665194</v>
+        <v>4727.142586446</v>
       </c>
       <c r="P60">
-        <v>13580.203827806</v>
+        <v>13595.115500554</v>
       </c>
       <c r="Q60">
-        <v>14382.703827806</v>
+        <v>14397.615500554</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1096816333161804</v>
+        <v>0.109640563105708</v>
       </c>
       <c r="T60">
         <v>1.474377900824666</v>
       </c>
       <c r="U60">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V60">
         <v>0.258</v>
       </c>
       <c r="W60">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6358,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>25.66138237050136</v>
+        <v>26.37561567703619</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6369,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.0681601086602526</v>
+        <v>0.0675300195069594</v>
       </c>
       <c r="C61">
-        <v>10585.66598404828</v>
+        <v>10627.33728854107</v>
       </c>
       <c r="D61">
-        <v>24317.87098404828</v>
+        <v>24359.54228854107</v>
       </c>
       <c r="E61">
         <v>9550.205</v>
@@ -6289,37 +6402,37 @@
         <v>19044.3</v>
       </c>
       <c r="M61">
-        <v>754.9339985</v>
+        <v>734.4909114999999</v>
       </c>
       <c r="N61">
-        <v>18289.3660015</v>
+        <v>18309.8090885</v>
       </c>
       <c r="O61">
-        <v>4718.656428387</v>
+        <v>4723.930744833</v>
       </c>
       <c r="P61">
-        <v>13570.709573113</v>
+        <v>13585.878343667</v>
       </c>
       <c r="Q61">
-        <v>14373.209573113</v>
+        <v>14388.378343667</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1110411772201283</v>
+        <v>0.1109992329438034</v>
       </c>
       <c r="T61">
         <v>1.505755957131719</v>
       </c>
       <c r="U61">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V61">
         <v>0.258</v>
       </c>
       <c r="W61">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6440,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>25.22644368625557</v>
+        <v>25.9285713435271</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6451,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.06800431932770941</v>
+        <v>0.06736389450952143</v>
       </c>
       <c r="C62">
-        <v>10348.78253864011</v>
+        <v>10391.19720960011</v>
       </c>
       <c r="D62">
-        <v>24328.48253864011</v>
+        <v>24370.89720960011</v>
       </c>
       <c r="E62">
         <v>9797.699999999999</v>
@@ -6371,37 +6484,37 @@
         <v>19044.3</v>
       </c>
       <c r="M62">
-        <v>767.7294899999999</v>
+        <v>746.9399099999999</v>
       </c>
       <c r="N62">
-        <v>18276.57051</v>
+        <v>18297.36009</v>
       </c>
       <c r="O62">
-        <v>4715.35519158</v>
+        <v>4720.718903219999</v>
       </c>
       <c r="P62">
-        <v>13561.21531842</v>
+        <v>13576.64118678</v>
       </c>
       <c r="Q62">
-        <v>14363.71531842</v>
+        <v>14379.14118678</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1124686983192735</v>
+        <v>0.1124258362738036</v>
       </c>
       <c r="T62">
         <v>1.538702916254125</v>
       </c>
       <c r="U62">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V62">
         <v>0.258</v>
       </c>
       <c r="W62">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6522,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>24.80600295815131</v>
+        <v>25.49642848780165</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6533,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.06784852999516625</v>
+        <v>0.06719776951208348</v>
       </c>
       <c r="C63">
-        <v>10111.90835837276</v>
+        <v>10155.06772152821</v>
       </c>
       <c r="D63">
-        <v>24339.10335837276</v>
+        <v>24382.26272152821</v>
       </c>
       <c r="E63">
         <v>10045.195</v>
@@ -6453,37 +6566,37 @@
         <v>19044.3</v>
       </c>
       <c r="M63">
-        <v>780.5249815000001</v>
+        <v>759.3889085</v>
       </c>
       <c r="N63">
-        <v>18263.7750185</v>
+        <v>18284.9110915</v>
       </c>
       <c r="O63">
-        <v>4712.053954773</v>
+        <v>4717.507061607</v>
       </c>
       <c r="P63">
-        <v>13551.721063727</v>
+        <v>13567.404029893</v>
       </c>
       <c r="Q63">
-        <v>14354.221063727</v>
+        <v>14369.904029893</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1139694256286314</v>
+        <v>0.113925598748932</v>
       </c>
       <c r="T63">
         <v>1.573339463023834</v>
       </c>
       <c r="U63">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V63">
         <v>0.258</v>
       </c>
       <c r="W63">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6604,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>24.39934717195211</v>
+        <v>25.0784542502967</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6615,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.06769274066262308</v>
+        <v>0.06703164451464552</v>
       </c>
       <c r="C64">
-        <v>9875.043455385885</v>
+        <v>9918.948839149643</v>
       </c>
       <c r="D64">
-        <v>24349.73345538589</v>
+        <v>24393.63883914964</v>
       </c>
       <c r="E64">
         <v>10292.69</v>
@@ -6535,37 +6648,37 @@
         <v>19044.3</v>
       </c>
       <c r="M64">
-        <v>793.3204730000001</v>
+        <v>771.837907</v>
       </c>
       <c r="N64">
-        <v>18250.979527</v>
+        <v>18272.462093</v>
       </c>
       <c r="O64">
-        <v>4708.752717966</v>
+        <v>4714.295219994</v>
       </c>
       <c r="P64">
-        <v>13542.226809034</v>
+        <v>13558.166873006</v>
       </c>
       <c r="Q64">
-        <v>14344.726809034</v>
+        <v>14360.666873006</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1155491385858502</v>
+        <v>0.1155042960911724</v>
       </c>
       <c r="T64">
         <v>1.609798985939318</v>
       </c>
       <c r="U64">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V64">
         <v>0.258</v>
       </c>
       <c r="W64">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6686,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>24.00580931433998</v>
+        <v>24.67396305271127</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6697,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.06753695133007991</v>
+        <v>0.06686551951720757</v>
       </c>
       <c r="C65">
-        <v>9638.187841840341</v>
+        <v>9682.840577316338</v>
       </c>
       <c r="D65">
-        <v>24360.37284184034</v>
+        <v>24405.02557731634</v>
       </c>
       <c r="E65">
         <v>10540.185</v>
@@ -6617,37 +6730,37 @@
         <v>19044.3</v>
       </c>
       <c r="M65">
-        <v>806.1159645</v>
+        <v>784.2869055</v>
       </c>
       <c r="N65">
-        <v>18238.1840355</v>
+        <v>18260.0130945</v>
       </c>
       <c r="O65">
-        <v>4705.451481159</v>
+        <v>4711.083378380999</v>
       </c>
       <c r="P65">
-        <v>13532.732554341</v>
+        <v>13548.929716119</v>
       </c>
       <c r="Q65">
-        <v>14335.232554341</v>
+        <v>14351.429716119</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1172142414326484</v>
+        <v>0.1171683284248853</v>
       </c>
       <c r="T65">
         <v>1.648229293877259</v>
       </c>
       <c r="U65">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V65">
         <v>0.258</v>
       </c>
       <c r="W65">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6768,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>23.62476472204887</v>
+        <v>24.28231284552538</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6779,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.06738116199753673</v>
+        <v>0.0666993945197696</v>
       </c>
       <c r="C66">
-        <v>9401.341529918252</v>
+        <v>9446.74295090797</v>
       </c>
       <c r="D66">
-        <v>24371.02152991825</v>
+        <v>24416.42295090797</v>
       </c>
       <c r="E66">
         <v>10787.68</v>
@@ -6699,37 +6812,37 @@
         <v>19044.3</v>
       </c>
       <c r="M66">
-        <v>818.911456</v>
+        <v>796.735904</v>
       </c>
       <c r="N66">
-        <v>18225.388544</v>
+        <v>18247.564096</v>
       </c>
       <c r="O66">
-        <v>4702.150244351999</v>
+        <v>4707.871536768</v>
       </c>
       <c r="P66">
-        <v>13523.238299648</v>
+        <v>13539.692559232</v>
       </c>
       <c r="Q66">
-        <v>14325.738299648</v>
+        <v>14342.192559232</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1189718499931576</v>
+        <v>0.11892480699936</v>
       </c>
       <c r="T66">
         <v>1.688794618922864</v>
       </c>
       <c r="U66">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V66">
         <v>0.258</v>
       </c>
       <c r="W66">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6850,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>23.25562777326685</v>
+        <v>23.90290170731404</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6861,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.06722537266499357</v>
+        <v>0.06653326952233164</v>
       </c>
       <c r="C67">
-        <v>9164.50453182305</v>
+        <v>9210.655974832041</v>
       </c>
       <c r="D67">
-        <v>24381.67953182305</v>
+        <v>24427.83097483204</v>
       </c>
       <c r="E67">
         <v>11035.175</v>
@@ -6781,37 +6894,37 @@
         <v>19044.3</v>
       </c>
       <c r="M67">
-        <v>831.7069475000001</v>
+        <v>809.1849025</v>
       </c>
       <c r="N67">
-        <v>18212.5930525</v>
+        <v>18235.1150975</v>
       </c>
       <c r="O67">
-        <v>4698.849007545</v>
+        <v>4704.659695155</v>
       </c>
       <c r="P67">
-        <v>13513.744044955</v>
+        <v>13530.455402345</v>
       </c>
       <c r="Q67">
-        <v>14316.244044955</v>
+        <v>14332.955402345</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.120829893328553</v>
+        <v>0.1207816557780904</v>
       </c>
       <c r="T67">
         <v>1.731677962542504</v>
       </c>
       <c r="U67">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V67">
         <v>0.258</v>
       </c>
       <c r="W67">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6932,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>22.89784888444737</v>
+        <v>23.53516475797075</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6943,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.06706958333245039</v>
+        <v>0.06636714452489367</v>
       </c>
       <c r="C68">
-        <v>8927.676859779529</v>
+        <v>8974.5796640239</v>
       </c>
       <c r="D68">
-        <v>24392.34685977953</v>
+        <v>24439.2496640239</v>
       </c>
       <c r="E68">
         <v>11282.67</v>
@@ -6863,37 +6976,37 @@
         <v>19044.3</v>
       </c>
       <c r="M68">
-        <v>844.5024390000001</v>
+        <v>821.6339009999999</v>
       </c>
       <c r="N68">
-        <v>18199.797561</v>
+        <v>18222.666099</v>
       </c>
       <c r="O68">
-        <v>4695.547770738</v>
+        <v>4701.447853541999</v>
       </c>
       <c r="P68">
-        <v>13504.249790262</v>
+        <v>13521.218245458</v>
       </c>
       <c r="Q68">
-        <v>14306.749790262</v>
+        <v>14323.718245458</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1227972333307364</v>
+        <v>0.1227477309555697</v>
       </c>
       <c r="T68">
         <v>1.777083855786828</v>
       </c>
       <c r="U68">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V68">
         <v>0.258</v>
       </c>
       <c r="W68">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +7014,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>22.55091178013755</v>
+        <v>23.17857135254695</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +7025,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.06691379399990721</v>
+        <v>0.06620101952745572</v>
       </c>
       <c r="C69">
-        <v>8690.858526033877</v>
+        <v>8738.514033446856</v>
       </c>
       <c r="D69">
-        <v>24403.02352603388</v>
+        <v>24450.67903344686</v>
       </c>
       <c r="E69">
         <v>11530.165</v>
@@ -6945,37 +7058,37 @@
         <v>19044.3</v>
       </c>
       <c r="M69">
-        <v>857.2979305000001</v>
+        <v>834.0828995000001</v>
       </c>
       <c r="N69">
-        <v>18187.0020695</v>
+        <v>18210.2171005</v>
       </c>
       <c r="O69">
-        <v>4692.246533931</v>
+        <v>4698.236011929</v>
       </c>
       <c r="P69">
-        <v>13494.755535569</v>
+        <v>13511.981088571</v>
       </c>
       <c r="Q69">
-        <v>14297.255535569</v>
+        <v>14314.481088571</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1248838060603249</v>
+        <v>0.1248329622044113</v>
       </c>
       <c r="T69">
         <v>1.825241621348991</v>
       </c>
       <c r="U69">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V69">
         <v>0.258</v>
       </c>
       <c r="W69">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +7096,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>22.21433100729968</v>
+        <v>22.83262252638953</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +7107,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.06675800466736403</v>
+        <v>0.06603489453001775</v>
       </c>
       <c r="C70">
-        <v>8454.049542853754</v>
+        <v>8502.459098092218</v>
       </c>
       <c r="D70">
-        <v>24413.70954285375</v>
+        <v>24462.11909809222</v>
       </c>
       <c r="E70">
         <v>11777.66</v>
@@ -7027,37 +7140,37 @@
         <v>19044.3</v>
       </c>
       <c r="M70">
-        <v>870.093422</v>
+        <v>846.531898</v>
       </c>
       <c r="N70">
-        <v>18174.206578</v>
+        <v>18197.768102</v>
       </c>
       <c r="O70">
-        <v>4688.945297124</v>
+        <v>4695.024170316</v>
       </c>
       <c r="P70">
-        <v>13485.261280876</v>
+        <v>13502.743931684</v>
       </c>
       <c r="Q70">
-        <v>14287.761280876</v>
+        <v>14305.243931684</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1271007895855126</v>
+        <v>0.1270485204063055</v>
       </c>
       <c r="T70">
         <v>1.876409247258788</v>
       </c>
       <c r="U70">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V70">
         <v>0.258</v>
       </c>
       <c r="W70">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7178,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>21.88764966895704</v>
+        <v>22.49684866570734</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7189,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.06660221533482086</v>
+        <v>0.06586876953257979</v>
       </c>
       <c r="C71">
-        <v>8217.249922528285</v>
+        <v>8266.414872979349</v>
       </c>
       <c r="D71">
-        <v>24424.40492252829</v>
+        <v>24473.56987297935</v>
       </c>
       <c r="E71">
         <v>12025.155</v>
@@ -7109,37 +7222,37 @@
         <v>19044.3</v>
       </c>
       <c r="M71">
-        <v>882.8889135000002</v>
+        <v>858.9808965000001</v>
       </c>
       <c r="N71">
-        <v>18161.4110865</v>
+        <v>18185.3191035</v>
       </c>
       <c r="O71">
-        <v>4685.644060317</v>
+        <v>4691.812328702999</v>
       </c>
       <c r="P71">
-        <v>13475.767026183</v>
+        <v>13493.506774797</v>
       </c>
       <c r="Q71">
-        <v>14278.267026183</v>
+        <v>14296.006774797</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1294608043058738</v>
+        <v>0.1294070178470316</v>
       </c>
       <c r="T71">
         <v>1.930878010324056</v>
       </c>
       <c r="U71">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V71">
         <v>0.258</v>
       </c>
       <c r="W71">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7260,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>21.57043735491418</v>
+        <v>22.17080738069708</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7271,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.06644642600227768</v>
+        <v>0.06570264453514182</v>
       </c>
       <c r="C72">
-        <v>7980.459677368166</v>
+        <v>8030.381373155768</v>
       </c>
       <c r="D72">
-        <v>24435.10967736817</v>
+        <v>24485.03137315577</v>
       </c>
       <c r="E72">
         <v>12272.65</v>
@@ -7191,37 +7304,37 @@
         <v>19044.3</v>
       </c>
       <c r="M72">
-        <v>895.6844050000001</v>
+        <v>871.429895</v>
       </c>
       <c r="N72">
-        <v>18148.615595</v>
+        <v>18172.870105</v>
       </c>
       <c r="O72">
-        <v>4682.34282351</v>
+        <v>4688.60048709</v>
       </c>
       <c r="P72">
-        <v>13466.27277149</v>
+        <v>13484.26961791</v>
       </c>
       <c r="Q72">
-        <v>14268.77277149</v>
+        <v>14286.76961791</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1319781533409256</v>
+        <v>0.1319227484504728</v>
       </c>
       <c r="T72">
         <v>1.988978024260342</v>
       </c>
       <c r="U72">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V72">
         <v>0.258</v>
       </c>
       <c r="W72">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7342,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>21.26228824984398</v>
+        <v>21.85408156097284</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7353,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.06629063666973452</v>
+        <v>0.06553651953770387</v>
       </c>
       <c r="C73">
-        <v>7743.678819705678</v>
+        <v>7794.35861369719</v>
       </c>
       <c r="D73">
-        <v>24445.82381970568</v>
+        <v>24496.50361369719</v>
       </c>
       <c r="E73">
         <v>12520.145</v>
@@ -7273,37 +7386,37 @@
         <v>19044.3</v>
       </c>
       <c r="M73">
-        <v>908.4798965000001</v>
+        <v>883.8788935</v>
       </c>
       <c r="N73">
-        <v>18135.8201035</v>
+        <v>18160.4211065</v>
       </c>
       <c r="O73">
-        <v>4679.041586703</v>
+        <v>4685.388645477</v>
       </c>
       <c r="P73">
-        <v>13456.778516797</v>
+        <v>13475.032461023</v>
       </c>
       <c r="Q73">
-        <v>14259.278516797</v>
+        <v>14277.532461023</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1346691126542569</v>
+        <v>0.1346119777162202</v>
       </c>
       <c r="T73">
         <v>2.051084935709475</v>
       </c>
       <c r="U73">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V73">
         <v>0.258</v>
       </c>
       <c r="W73">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7424,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>20.96281940125463</v>
+        <v>21.54627759532534</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7435,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.06613484733719133</v>
+        <v>0.06537039454026589</v>
       </c>
       <c r="C74">
-        <v>7506.90736189473</v>
+        <v>7558.346609707591</v>
       </c>
       <c r="D74">
-        <v>24456.54736189473</v>
+        <v>24507.98660970759</v>
       </c>
       <c r="E74">
         <v>12767.64</v>
@@ -7355,37 +7468,37 @@
         <v>19044.3</v>
       </c>
       <c r="M74">
-        <v>921.275388</v>
+        <v>896.3278919999999</v>
       </c>
       <c r="N74">
-        <v>18123.024612</v>
+        <v>18147.972108</v>
       </c>
       <c r="O74">
-        <v>4675.740349896</v>
+        <v>4682.176803863999</v>
       </c>
       <c r="P74">
-        <v>13447.284262104</v>
+        <v>13465.795304136</v>
       </c>
       <c r="Q74">
-        <v>14249.784262104</v>
+        <v>14268.295304136</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1375522833471119</v>
+        <v>0.1374932947866639</v>
       </c>
       <c r="T74">
         <v>2.11762805511926</v>
       </c>
       <c r="U74">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V74">
         <v>0.258</v>
       </c>
       <c r="W74">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7506,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>20.67166913179276</v>
+        <v>21.24702373983471</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7517,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.06597905800464816</v>
+        <v>0.06520426954282794</v>
       </c>
       <c r="C75">
-        <v>7270.145316310929</v>
+        <v>7322.345376319288</v>
       </c>
       <c r="D75">
-        <v>24467.28031631093</v>
+        <v>24519.48037631929</v>
       </c>
       <c r="E75">
         <v>13015.135</v>
@@ -7437,37 +7550,37 @@
         <v>19044.3</v>
       </c>
       <c r="M75">
-        <v>934.0708794999999</v>
+        <v>908.7768904999999</v>
       </c>
       <c r="N75">
-        <v>18110.2291205</v>
+        <v>18135.5231095</v>
       </c>
       <c r="O75">
-        <v>4672.439113089</v>
+        <v>4678.964962251</v>
       </c>
       <c r="P75">
-        <v>13437.790007411</v>
+        <v>13456.558147249</v>
       </c>
       <c r="Q75">
-        <v>14240.290007411</v>
+        <v>14259.058147249</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1406490222394376</v>
+        <v>0.1405880427512146</v>
       </c>
       <c r="T75">
         <v>2.189100294485326</v>
       </c>
       <c r="U75">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V75">
         <v>0.258</v>
       </c>
       <c r="W75">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7588,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>20.38849558204218</v>
+        <v>20.95596862011094</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7599,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.06582326867210499</v>
+        <v>0.06503814454538998</v>
       </c>
       <c r="C76">
-        <v>7033.392695351606</v>
+        <v>7086.354928692988</v>
       </c>
       <c r="D76">
-        <v>24478.02269535161</v>
+        <v>24530.98492869299</v>
       </c>
       <c r="E76">
         <v>13262.63</v>
@@ -7519,37 +7632,37 @@
         <v>19044.3</v>
       </c>
       <c r="M76">
-        <v>946.8663710000001</v>
+        <v>921.2258890000001</v>
       </c>
       <c r="N76">
-        <v>18097.433629</v>
+        <v>18123.074111</v>
       </c>
       <c r="O76">
-        <v>4669.137876282</v>
+        <v>4675.753120638</v>
       </c>
       <c r="P76">
-        <v>13428.295752718</v>
+        <v>13447.320990362</v>
       </c>
       <c r="Q76">
-        <v>14230.795752718</v>
+        <v>14249.820990362</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1439839718157884</v>
+        <v>0.1439208482514999</v>
       </c>
       <c r="T76">
         <v>2.266070398418012</v>
       </c>
       <c r="U76">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V76">
         <v>0.258</v>
       </c>
       <c r="W76">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7670,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>20.11297537147404</v>
+        <v>20.67277985497431</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7681,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.06566747933956182</v>
+        <v>0.06487201954795202</v>
       </c>
       <c r="C77">
-        <v>6796.649511435891</v>
+        <v>6850.375282017878</v>
       </c>
       <c r="D77">
-        <v>24488.77451143589</v>
+        <v>24542.50028201788</v>
       </c>
       <c r="E77">
         <v>13510.125</v>
@@ -7601,37 +7714,37 @@
         <v>19044.3</v>
       </c>
       <c r="M77">
-        <v>959.6618625000001</v>
+        <v>933.6748875</v>
       </c>
       <c r="N77">
-        <v>18084.6381375</v>
+        <v>18110.6251125</v>
       </c>
       <c r="O77">
-        <v>4665.836639475</v>
+        <v>4672.541279024999</v>
       </c>
       <c r="P77">
-        <v>13418.801498025</v>
+        <v>13438.083833475</v>
       </c>
       <c r="Q77">
-        <v>14221.301498025</v>
+        <v>14240.583833475</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1475857173582473</v>
+        <v>0.1475202781918081</v>
       </c>
       <c r="T77">
         <v>2.349198110665314</v>
       </c>
       <c r="U77">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V77">
         <v>0.258</v>
       </c>
       <c r="W77">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7752,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>19.84480236652105</v>
+        <v>20.39714279024132</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7763,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.06551169000701865</v>
+        <v>0.06470589455051406</v>
       </c>
       <c r="C78">
-        <v>6559.915777004728</v>
+        <v>6614.406451511677</v>
       </c>
       <c r="D78">
-        <v>24499.53577700473</v>
+        <v>24554.02645151168</v>
       </c>
       <c r="E78">
         <v>13757.62</v>
@@ -7683,37 +7796,37 @@
         <v>19044.3</v>
       </c>
       <c r="M78">
-        <v>972.457354</v>
+        <v>946.1238859999999</v>
       </c>
       <c r="N78">
-        <v>18071.842646</v>
+        <v>18098.176114</v>
       </c>
       <c r="O78">
-        <v>4662.535402668001</v>
+        <v>4669.329437412</v>
       </c>
       <c r="P78">
-        <v>13409.307243332</v>
+        <v>13428.846676588</v>
       </c>
       <c r="Q78">
-        <v>14211.807243332</v>
+        <v>14231.346676588</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1514876083625777</v>
+        <v>0.1514196606271419</v>
       </c>
       <c r="T78">
         <v>2.439253132266558</v>
       </c>
       <c r="U78">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V78">
         <v>0.258</v>
       </c>
       <c r="W78">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7834,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>19.58368654590893</v>
+        <v>20.12875933247499</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7845,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.06535590067447547</v>
+        <v>0.0645397695530761</v>
       </c>
       <c r="C79">
-        <v>6323.191504520946</v>
+        <v>6378.448452420693</v>
       </c>
       <c r="D79">
-        <v>24510.30650452095</v>
+        <v>24565.56345242069</v>
       </c>
       <c r="E79">
         <v>14005.115</v>
@@ -7765,37 +7878,37 @@
         <v>19044.3</v>
       </c>
       <c r="M79">
-        <v>985.2528455000001</v>
+        <v>958.5728845</v>
       </c>
       <c r="N79">
-        <v>18059.0471545</v>
+        <v>18085.7271155</v>
       </c>
       <c r="O79">
-        <v>4659.234165861</v>
+        <v>4666.117595799</v>
       </c>
       <c r="P79">
-        <v>13399.812988639</v>
+        <v>13419.609519701</v>
       </c>
       <c r="Q79">
-        <v>14202.312988639</v>
+        <v>14222.109519701</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1557287942368499</v>
+        <v>0.155658119795983</v>
       </c>
       <c r="T79">
         <v>2.537139025311387</v>
       </c>
       <c r="U79">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V79">
         <v>0.258</v>
       </c>
       <c r="W79">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7916,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>19.32935295440362</v>
+        <v>19.86734687361167</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7927,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.06520011134193229</v>
+        <v>0.06437364455563814</v>
       </c>
       <c r="C80">
-        <v>6086.476706469293</v>
+        <v>6142.501300019921</v>
       </c>
       <c r="D80">
-        <v>24521.08670646929</v>
+        <v>24577.11130001992</v>
       </c>
       <c r="E80">
         <v>14252.61</v>
@@ -7847,37 +7960,37 @@
         <v>19044.3</v>
       </c>
       <c r="M80">
-        <v>998.0483370000001</v>
+        <v>971.021883</v>
       </c>
       <c r="N80">
-        <v>18046.251663</v>
+        <v>18073.278117</v>
       </c>
       <c r="O80">
-        <v>4655.932929054</v>
+        <v>4662.905754185999</v>
       </c>
       <c r="P80">
-        <v>13390.318733946</v>
+        <v>13410.372362814</v>
       </c>
       <c r="Q80">
-        <v>14192.818733946</v>
+        <v>14212.872362814</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1603555424633286</v>
+        <v>0.1602818934347188</v>
       </c>
       <c r="T80">
         <v>2.643923635905747</v>
       </c>
       <c r="U80">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V80">
         <v>0.258</v>
       </c>
       <c r="W80">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7998,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>19.08154073703947</v>
+        <v>19.61263729830896</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +8009,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.06504432200938913</v>
+        <v>0.06420751955820017</v>
       </c>
       <c r="C81">
-        <v>5849.771395356503</v>
+        <v>5906.56500961307</v>
       </c>
       <c r="D81">
-        <v>24531.8763953565</v>
+        <v>24588.67000961307</v>
       </c>
       <c r="E81">
         <v>14500.105</v>
@@ -7929,37 +8042,37 @@
         <v>19044.3</v>
       </c>
       <c r="M81">
-        <v>1010.8438285</v>
+        <v>983.4708814999999</v>
       </c>
       <c r="N81">
-        <v>18033.4561715</v>
+        <v>18060.8291185</v>
       </c>
       <c r="O81">
-        <v>4652.631692247</v>
+        <v>4659.693912573</v>
       </c>
       <c r="P81">
-        <v>13380.824479253</v>
+        <v>13401.135205927</v>
       </c>
       <c r="Q81">
-        <v>14183.324479253</v>
+        <v>14203.635205927</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1654229333780435</v>
+        <v>0.1653460264676199</v>
       </c>
       <c r="T81">
         <v>2.760878209413855</v>
       </c>
       <c r="U81">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V81">
         <v>0.258</v>
       </c>
       <c r="W81">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +8080,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>18.8400022466972</v>
+        <v>19.3643760666848</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +8091,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.06488853267684595</v>
+        <v>0.06404139456076222</v>
       </c>
       <c r="C82">
-        <v>5613.075583711314</v>
+        <v>5670.639596532666</v>
       </c>
       <c r="D82">
-        <v>24542.67558371132</v>
+        <v>24600.23959653267</v>
       </c>
       <c r="E82">
         <v>14747.6</v>
@@ -8011,37 +8124,37 @@
         <v>19044.3</v>
       </c>
       <c r="M82">
-        <v>1023.63932</v>
+        <v>995.91988</v>
       </c>
       <c r="N82">
-        <v>18020.66068</v>
+        <v>18048.38012</v>
       </c>
       <c r="O82">
-        <v>4649.33045544</v>
+        <v>4656.48207096</v>
       </c>
       <c r="P82">
-        <v>13371.33022456</v>
+        <v>13391.89804904</v>
       </c>
       <c r="Q82">
-        <v>14173.83022456</v>
+        <v>14194.39804904</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1709970633842298</v>
+        <v>0.1709165728038111</v>
       </c>
       <c r="T82">
         <v>2.889528240272774</v>
       </c>
       <c r="U82">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V82">
         <v>0.258</v>
       </c>
       <c r="W82">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8162,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>18.60450221861348</v>
+        <v>19.12232136585123</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8173,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.06473274334430278</v>
+        <v>0.06387526956332425</v>
       </c>
       <c r="C83">
-        <v>5376.389284084558</v>
+        <v>5434.725076140112</v>
       </c>
       <c r="D83">
-        <v>24553.48428408456</v>
+        <v>24611.82007614011</v>
       </c>
       <c r="E83">
         <v>14995.095</v>
@@ -8093,37 +8206,37 @@
         <v>19044.3</v>
       </c>
       <c r="M83">
-        <v>1036.4348115</v>
+        <v>1008.3688785</v>
       </c>
       <c r="N83">
-        <v>18007.8651885</v>
+        <v>18035.9311215</v>
       </c>
       <c r="O83">
-        <v>4646.029218633</v>
+        <v>4653.270229346999</v>
       </c>
       <c r="P83">
-        <v>13361.835969867</v>
+        <v>13382.660892153</v>
       </c>
       <c r="Q83">
-        <v>14164.335969867</v>
+        <v>14185.160892153</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.177157943917383</v>
+        <v>0.1770734924385487</v>
       </c>
       <c r="T83">
         <v>3.031720379643158</v>
       </c>
       <c r="U83">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V83">
         <v>0.258</v>
       </c>
       <c r="W83">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8244,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>18.37481700603801</v>
+        <v>18.88624332429751</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8255,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.06457695401175961</v>
+        <v>0.06370914456588628</v>
       </c>
       <c r="C84">
-        <v>5139.712509049168</v>
+        <v>5198.821463825734</v>
       </c>
       <c r="D84">
-        <v>24564.30250904917</v>
+        <v>24623.41146382573</v>
       </c>
       <c r="E84">
         <v>15242.59</v>
@@ -8175,37 +8288,37 @@
         <v>19044.3</v>
       </c>
       <c r="M84">
-        <v>1049.230303</v>
+        <v>1020.817877</v>
       </c>
       <c r="N84">
-        <v>17995.069697</v>
+        <v>18023.482123</v>
       </c>
       <c r="O84">
-        <v>4642.727981825999</v>
+        <v>4650.058387734</v>
       </c>
       <c r="P84">
-        <v>13352.341715174</v>
+        <v>13373.423735266</v>
       </c>
       <c r="Q84">
-        <v>14154.841715174</v>
+        <v>14175.923735266</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1840033667319978</v>
+        <v>0.1839145142549239</v>
       </c>
       <c r="T84">
         <v>3.189711645610251</v>
       </c>
       <c r="U84">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V84">
         <v>0.258</v>
       </c>
       <c r="W84">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8326,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>18.15073387181803</v>
+        <v>18.6559232837573</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8337,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.06442116467921644</v>
+        <v>0.06354301956844832</v>
       </c>
       <c r="C85">
-        <v>4903.045271200248</v>
+        <v>4962.928775008862</v>
       </c>
       <c r="D85">
-        <v>24575.13027120025</v>
+        <v>24635.01377500887</v>
       </c>
       <c r="E85">
         <v>15490.085</v>
@@ -8257,37 +8370,37 @@
         <v>19044.3</v>
       </c>
       <c r="M85">
-        <v>1062.0257945</v>
+        <v>1033.2668755</v>
       </c>
       <c r="N85">
-        <v>17982.2742055</v>
+        <v>18011.0331245</v>
       </c>
       <c r="O85">
-        <v>4639.426745019</v>
+        <v>4646.846546121</v>
       </c>
       <c r="P85">
-        <v>13342.847460481</v>
+        <v>13364.186578379</v>
       </c>
       <c r="Q85">
-        <v>14145.347460481</v>
+        <v>14166.686578379</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1916541334071555</v>
+        <v>0.1915603621673432</v>
       </c>
       <c r="T85">
         <v>3.36629011933818</v>
       </c>
       <c r="U85">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V85">
         <v>0.258</v>
       </c>
       <c r="W85">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8408,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>17.93205033119371</v>
+        <v>18.43115312371203</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8419,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.06426537534667326</v>
+        <v>0.06337689457101037</v>
       </c>
       <c r="C86">
-        <v>4666.38758315513</v>
+        <v>4727.047025137927</v>
       </c>
       <c r="D86">
-        <v>24585.96758315513</v>
+        <v>24646.62702513792</v>
       </c>
       <c r="E86">
         <v>15737.58</v>
@@ -8339,37 +8452,37 @@
         <v>19044.3</v>
       </c>
       <c r="M86">
-        <v>1074.821286</v>
+        <v>1045.715874</v>
       </c>
       <c r="N86">
-        <v>17969.478714</v>
+        <v>17998.584126</v>
       </c>
       <c r="O86">
-        <v>4636.125508212001</v>
+        <v>4643.634704507999</v>
       </c>
       <c r="P86">
-        <v>13333.353205788</v>
+        <v>13354.949421492</v>
       </c>
       <c r="Q86">
-        <v>14135.853205788</v>
+        <v>14157.449421492</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2002612459167078</v>
+        <v>0.2001619410688148</v>
       </c>
       <c r="T86">
         <v>3.564940902282097</v>
       </c>
       <c r="U86">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V86">
         <v>0.258</v>
       </c>
       <c r="W86">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8490,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>17.71857354153666</v>
+        <v>18.21173463414404</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8501,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.06410958601413008</v>
+        <v>0.06321076957357241</v>
       </c>
       <c r="C87">
-        <v>4429.739457553398</v>
+        <v>4491.176229690478</v>
       </c>
       <c r="D87">
-        <v>24596.8144575534</v>
+        <v>24658.25122969048</v>
       </c>
       <c r="E87">
         <v>15985.075</v>
@@ -8421,37 +8534,37 @@
         <v>19044.3</v>
       </c>
       <c r="M87">
-        <v>1087.6167775</v>
+        <v>1058.1648725</v>
       </c>
       <c r="N87">
-        <v>17956.6832225</v>
+        <v>17986.1351275</v>
       </c>
       <c r="O87">
-        <v>4632.824271405</v>
+        <v>4640.422862895</v>
       </c>
       <c r="P87">
-        <v>13323.858951095</v>
+        <v>13345.712264605</v>
       </c>
       <c r="Q87">
-        <v>14126.358951095</v>
+        <v>14148.212264605</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2100159734275339</v>
+        <v>0.2099103971571493</v>
       </c>
       <c r="T87">
         <v>3.790078456285205</v>
       </c>
       <c r="U87">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V87">
         <v>0.258</v>
       </c>
       <c r="W87">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8572,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>17.51011973516563</v>
+        <v>17.99747893256587</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8583,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.06395379668158691</v>
+        <v>0.06304464457613444</v>
       </c>
       <c r="C88">
-        <v>4193.100907056963</v>
+        <v>4255.3164041733</v>
       </c>
       <c r="D88">
-        <v>24607.67090705696</v>
+        <v>24669.8864041733</v>
       </c>
       <c r="E88">
         <v>16232.57</v>
@@ -8503,37 +8616,37 @@
         <v>19044.3</v>
       </c>
       <c r="M88">
-        <v>1100.412269</v>
+        <v>1070.613871</v>
       </c>
       <c r="N88">
-        <v>17943.887731</v>
+        <v>17973.686129</v>
       </c>
       <c r="O88">
-        <v>4629.523034598</v>
+        <v>4637.211021282</v>
       </c>
       <c r="P88">
-        <v>13314.364696402</v>
+        <v>13336.475107718</v>
       </c>
       <c r="Q88">
-        <v>14116.864696402</v>
+        <v>14138.975107718</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2211642334399065</v>
+        <v>0.2210514898295317</v>
       </c>
       <c r="T88">
         <v>4.047378518003042</v>
       </c>
       <c r="U88">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V88">
         <v>0.258</v>
       </c>
       <c r="W88">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8654,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>17.30651369173347</v>
+        <v>17.78820592172208</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8665,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.06379800734904373</v>
+        <v>0.06287851957869647</v>
       </c>
       <c r="C89">
-        <v>3956.471944350091</v>
+        <v>4019.467564122435</v>
       </c>
       <c r="D89">
-        <v>24618.53694435009</v>
+        <v>24681.53256412243</v>
       </c>
       <c r="E89">
         <v>16480.065</v>
@@ -8585,37 +8698,37 @@
         <v>19044.3</v>
       </c>
       <c r="M89">
-        <v>1113.2077605</v>
+        <v>1083.0628695</v>
       </c>
       <c r="N89">
-        <v>17931.0922395</v>
+        <v>17961.2371305</v>
       </c>
       <c r="O89">
-        <v>4626.221797791</v>
+        <v>4633.999179668999</v>
       </c>
       <c r="P89">
-        <v>13304.870441709</v>
+        <v>13327.237950831</v>
       </c>
       <c r="Q89">
-        <v>14107.370441709</v>
+        <v>14129.737950831</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2340276103772595</v>
+        <v>0.2339065967592036</v>
       </c>
       <c r="T89">
         <v>4.344263204600547</v>
       </c>
       <c r="U89">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V89">
         <v>0.258</v>
       </c>
       <c r="W89">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8736,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>17.1075882470009</v>
+        <v>17.58374378469079</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8747,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.06364221801650057</v>
+        <v>0.06271239458125852</v>
       </c>
       <c r="C90">
-        <v>3719.852582139469</v>
+        <v>3783.629725103288</v>
       </c>
       <c r="D90">
-        <v>24629.41258213947</v>
+        <v>24693.18972510329</v>
       </c>
       <c r="E90">
         <v>16727.56</v>
@@ -8667,37 +8780,37 @@
         <v>19044.3</v>
       </c>
       <c r="M90">
-        <v>1126.003252</v>
+        <v>1095.511868</v>
       </c>
       <c r="N90">
-        <v>17918.296748</v>
+        <v>17948.788132</v>
       </c>
       <c r="O90">
-        <v>4622.920560984</v>
+        <v>4630.787338055999</v>
       </c>
       <c r="P90">
-        <v>13295.376187016</v>
+        <v>13318.000793944</v>
       </c>
       <c r="Q90">
-        <v>14097.876187016</v>
+        <v>14120.500793944</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.249034883470838</v>
+        <v>0.2489042215104877</v>
       </c>
       <c r="T90">
         <v>4.690628672297637</v>
       </c>
       <c r="U90">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V90">
         <v>0.258</v>
       </c>
       <c r="W90">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8818,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>16.91318383510317</v>
+        <v>17.38392851441021</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8829,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.06348642868395739</v>
+        <v>0.06254626958382055</v>
       </c>
       <c r="C91">
-        <v>3483.242833154251</v>
+        <v>3547.802902710686</v>
       </c>
       <c r="D91">
-        <v>24640.29783315425</v>
+        <v>24704.85790271069</v>
       </c>
       <c r="E91">
         <v>16975.055</v>
@@ -8749,37 +8862,37 @@
         <v>19044.3</v>
       </c>
       <c r="M91">
-        <v>1138.7987435</v>
+        <v>1107.9608665</v>
       </c>
       <c r="N91">
-        <v>17905.5012565</v>
+        <v>17936.3391335</v>
       </c>
       <c r="O91">
-        <v>4619.619324177</v>
+        <v>4627.575496443</v>
       </c>
       <c r="P91">
-        <v>13285.881932323</v>
+        <v>13308.763637057</v>
       </c>
       <c r="Q91">
-        <v>14088.381932323</v>
+        <v>14111.263637057</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2667707516723399</v>
+        <v>0.2666286871256414</v>
       </c>
       <c r="T91">
         <v>5.099969679576016</v>
       </c>
       <c r="U91">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V91">
         <v>0.258</v>
       </c>
       <c r="W91">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8900,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>16.72314806167504</v>
+        <v>17.18860347492246</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8911,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.06333063935141421</v>
+        <v>0.06238014458638258</v>
       </c>
       <c r="C92">
-        <v>3246.642710146087</v>
+        <v>3311.98711256895</v>
       </c>
       <c r="D92">
-        <v>24651.19271014609</v>
+        <v>24716.53711256895</v>
       </c>
       <c r="E92">
         <v>17222.55</v>
@@ -8831,37 +8944,37 @@
         <v>19044.3</v>
       </c>
       <c r="M92">
-        <v>1151.594235</v>
+        <v>1120.409865</v>
       </c>
       <c r="N92">
-        <v>17892.705765</v>
+        <v>17923.890135</v>
       </c>
       <c r="O92">
-        <v>4616.318087369999</v>
+        <v>4624.363654829999</v>
       </c>
       <c r="P92">
-        <v>13276.38767763</v>
+        <v>13299.52648017</v>
       </c>
       <c r="Q92">
-        <v>14078.88767763</v>
+        <v>14102.02648017</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2880537935141421</v>
+        <v>0.2878980458638259</v>
       </c>
       <c r="T92">
         <v>5.591178888310069</v>
       </c>
       <c r="U92">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V92">
         <v>0.258</v>
       </c>
       <c r="W92">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8982,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>16.53733530543421</v>
+        <v>16.99761899186777</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8993,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.06317485001887105</v>
+        <v>0.06221401958894463</v>
       </c>
       <c r="C93">
-        <v>3010.052225889205</v>
+        <v>3076.182370331946</v>
       </c>
       <c r="D93">
-        <v>24662.09722588921</v>
+        <v>24728.22737033195</v>
       </c>
       <c r="E93">
         <v>17470.045</v>
@@ -8913,37 +9026,37 @@
         <v>19044.3</v>
       </c>
       <c r="M93">
-        <v>1164.3897265</v>
+        <v>1132.8588635</v>
       </c>
       <c r="N93">
-        <v>17879.9102735</v>
+        <v>17911.4411365</v>
       </c>
       <c r="O93">
-        <v>4613.016850563</v>
+        <v>4621.151813216999</v>
       </c>
       <c r="P93">
-        <v>13266.893422937</v>
+        <v>13290.289323283</v>
       </c>
       <c r="Q93">
-        <v>14069.393422937</v>
+        <v>14092.789323283</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3140664002096783</v>
+        <v>0.3138939287660515</v>
       </c>
       <c r="T93">
         <v>6.191545698985025</v>
       </c>
       <c r="U93">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V93">
         <v>0.258</v>
       </c>
       <c r="W93">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +9064,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>16.35560634603383</v>
+        <v>16.81083196997911</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +9075,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.06301906068632787</v>
+        <v>0.06204789459150667</v>
       </c>
       <c r="C94">
-        <v>2773.47139318044</v>
+        <v>2840.388691683187</v>
       </c>
       <c r="D94">
-        <v>24673.01139318044</v>
+        <v>24739.92869168319</v>
       </c>
       <c r="E94">
         <v>17717.54</v>
@@ -8995,37 +9108,37 @@
         <v>19044.3</v>
       </c>
       <c r="M94">
-        <v>1177.185218</v>
+        <v>1145.307862</v>
       </c>
       <c r="N94">
-        <v>17867.114782</v>
+        <v>17898.992138</v>
       </c>
       <c r="O94">
-        <v>4609.715613756</v>
+        <v>4617.939971604</v>
       </c>
       <c r="P94">
-        <v>13257.399168244</v>
+        <v>13281.052166396</v>
       </c>
       <c r="Q94">
-        <v>14059.899168244</v>
+        <v>14083.552166396</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3465821585790985</v>
+        <v>0.3463887823938335</v>
       </c>
       <c r="T94">
         <v>6.94200421232872</v>
       </c>
       <c r="U94">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V94">
         <v>0.258</v>
       </c>
       <c r="W94">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9146,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>16.17782801618564</v>
+        <v>16.62810553552281</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9157,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.06286327135378469</v>
+        <v>0.06188176959406871</v>
       </c>
       <c r="C95">
-        <v>2536.900224839304</v>
+        <v>2604.606092335871</v>
       </c>
       <c r="D95">
-        <v>24683.9352248393</v>
+        <v>24751.64109233587</v>
       </c>
       <c r="E95">
         <v>17965.035</v>
@@ -9077,37 +9190,37 @@
         <v>19044.3</v>
       </c>
       <c r="M95">
-        <v>1189.9807095</v>
+        <v>1157.7568605</v>
       </c>
       <c r="N95">
-        <v>17854.3192905</v>
+        <v>17886.5431395</v>
       </c>
       <c r="O95">
-        <v>4606.414376949</v>
+        <v>4614.728129990999</v>
       </c>
       <c r="P95">
-        <v>13247.904913551</v>
+        <v>13271.815009509</v>
       </c>
       <c r="Q95">
-        <v>14050.404913551</v>
+        <v>14074.315009509</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.3883881336254958</v>
+        <v>0.3881678799152675</v>
       </c>
       <c r="T95">
         <v>7.906879443770613</v>
       </c>
       <c r="U95">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V95">
         <v>0.258</v>
       </c>
       <c r="W95">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9228,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>16.00387287622665</v>
+        <v>16.44930870180752</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9239,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.06270748202124152</v>
+        <v>0.06171564459663074</v>
       </c>
       <c r="C96">
-        <v>2300.338733707988</v>
+        <v>2368.834588032962</v>
       </c>
       <c r="D96">
-        <v>24694.86873370799</v>
+        <v>24763.36458803296</v>
       </c>
       <c r="E96">
         <v>18212.53</v>
@@ -9159,37 +9272,37 @@
         <v>19044.3</v>
       </c>
       <c r="M96">
-        <v>1202.776201</v>
+        <v>1170.205859</v>
       </c>
       <c r="N96">
-        <v>17841.523799</v>
+        <v>17874.094141</v>
       </c>
       <c r="O96">
-        <v>4603.113140142</v>
+        <v>4611.516288377999</v>
       </c>
       <c r="P96">
-        <v>13238.410658858</v>
+        <v>13262.577852622</v>
       </c>
       <c r="Q96">
-        <v>14040.910658858</v>
+        <v>14065.077852622</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.444129433687359</v>
+        <v>0.4438733432771795</v>
       </c>
       <c r="T96">
         <v>9.193379752359805</v>
       </c>
       <c r="U96">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V96">
         <v>0.258</v>
       </c>
       <c r="W96">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9310,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>15.83361890945828</v>
+        <v>16.2743160560436</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9321,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.06255169268869834</v>
+        <v>0.06154951959919278</v>
       </c>
       <c r="C97">
-        <v>2063.786932651488</v>
+        <v>2133.074194547298</v>
       </c>
       <c r="D97">
-        <v>24705.81193265149</v>
+        <v>24775.0991945473</v>
       </c>
       <c r="E97">
         <v>18460.025</v>
@@ -9241,37 +9354,37 @@
         <v>19044.3</v>
       </c>
       <c r="M97">
-        <v>1215.5716925</v>
+        <v>1182.6548575</v>
       </c>
       <c r="N97">
-        <v>17828.7283075</v>
+        <v>17861.6451425</v>
       </c>
       <c r="O97">
-        <v>4599.811903334999</v>
+        <v>4608.304446765</v>
       </c>
       <c r="P97">
-        <v>13228.916404165</v>
+        <v>13253.340695735</v>
       </c>
       <c r="Q97">
-        <v>14031.416404165</v>
+        <v>14055.840695735</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.5221672537739674</v>
+        <v>0.5218609919838563</v>
       </c>
       <c r="T97">
         <v>10.99448018438467</v>
       </c>
       <c r="U97">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V97">
         <v>0.258</v>
       </c>
       <c r="W97">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9392,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>15.66694923672714</v>
+        <v>16.10300746597999</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9403,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.06239590335615518</v>
+        <v>0.06138339460175482</v>
       </c>
       <c r="C98">
-        <v>1827.244834557583</v>
+        <v>1897.324927681584</v>
       </c>
       <c r="D98">
-        <v>24716.76483455758</v>
+        <v>24786.84492768158</v>
       </c>
       <c r="E98">
         <v>18707.52</v>
@@ -9323,37 +9436,37 @@
         <v>19044.3</v>
       </c>
       <c r="M98">
-        <v>1228.367184</v>
+        <v>1195.103856</v>
       </c>
       <c r="N98">
-        <v>17815.932816</v>
+        <v>17849.196144</v>
       </c>
       <c r="O98">
-        <v>4596.510666528</v>
+        <v>4605.092605151999</v>
       </c>
       <c r="P98">
-        <v>13219.422149472</v>
+        <v>13244.103538848</v>
       </c>
       <c r="Q98">
-        <v>14021.922149472</v>
+        <v>14046.603538848</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.6392239839038788</v>
+        <v>0.63884246504387</v>
       </c>
       <c r="T98">
         <v>13.69613083242194</v>
       </c>
       <c r="U98">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V98">
         <v>0.258</v>
       </c>
       <c r="W98">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9474,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>15.50375184884457</v>
+        <v>15.93526780487603</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9485,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.062240114023612</v>
+        <v>0.06121726960431687</v>
       </c>
       <c r="C99">
-        <v>1590.712452336928</v>
+        <v>1661.586803268532</v>
       </c>
       <c r="D99">
-        <v>24727.72745233693</v>
+        <v>24798.60180326853</v>
       </c>
       <c r="E99">
         <v>18955.015</v>
@@ -9405,37 +9518,37 @@
         <v>19044.3</v>
       </c>
       <c r="M99">
-        <v>1241.1626755</v>
+        <v>1207.5528545</v>
       </c>
       <c r="N99">
-        <v>17803.1373245</v>
+        <v>17836.7471455</v>
       </c>
       <c r="O99">
-        <v>4593.209429721</v>
+        <v>4601.880763538999</v>
       </c>
       <c r="P99">
-        <v>13209.927894779</v>
+        <v>13234.866381961</v>
       </c>
       <c r="Q99">
-        <v>14012.427894779</v>
+        <v>14037.366381961</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.8343185341203992</v>
+        <v>0.8338115868105613</v>
       </c>
       <c r="T99">
         <v>18.1988819124841</v>
       </c>
       <c r="U99">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V99">
         <v>0.258</v>
       </c>
       <c r="W99">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9556,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>15.34391935555751</v>
+        <v>15.77098669348555</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9567,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.06208432469106883</v>
+        <v>0.0610511446068789</v>
       </c>
       <c r="C100">
-        <v>1354.189798923104</v>
+        <v>1425.859837170905</v>
       </c>
       <c r="D100">
-        <v>24738.6997989231</v>
+        <v>24810.3698371709</v>
       </c>
       <c r="E100">
         <v>19202.51</v>
@@ -9487,37 +9600,37 @@
         <v>19044.3</v>
       </c>
       <c r="M100">
-        <v>1253.958167</v>
+        <v>1220.001853</v>
       </c>
       <c r="N100">
-        <v>17790.341833</v>
+        <v>17824.298147</v>
       </c>
       <c r="O100">
-        <v>4589.908192914</v>
+        <v>4598.668921926001</v>
       </c>
       <c r="P100">
-        <v>13200.433640086</v>
+        <v>13225.629225074</v>
       </c>
       <c r="Q100">
-        <v>14002.933640086</v>
+        <v>14028.129225074</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.22450763455344</v>
+        <v>1.223749830343944</v>
       </c>
       <c r="T100">
         <v>27.20438407260841</v>
       </c>
       <c r="U100">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V100">
         <v>0.258</v>
       </c>
       <c r="W100">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9638,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>15.18734874988856</v>
+        <v>15.61005825783775</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9649,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.06192853535852566</v>
+        <v>0.06088501960944094</v>
       </c>
       <c r="C101">
-        <v>1117.676887272628</v>
+        <v>1190.14404528158</v>
       </c>
       <c r="D101">
-        <v>24749.68188727263</v>
+        <v>24822.14904528158</v>
       </c>
       <c r="E101">
         <v>19450.005</v>
@@ -9569,37 +9682,37 @@
         <v>19044.3</v>
       </c>
       <c r="M101">
-        <v>1266.7536585</v>
+        <v>1232.4508515</v>
       </c>
       <c r="N101">
-        <v>17777.5463415</v>
+        <v>17811.8491485</v>
       </c>
       <c r="O101">
-        <v>4586.606956107</v>
+        <v>4595.457080312999</v>
       </c>
       <c r="P101">
-        <v>13190.939385393</v>
+        <v>13216.392068187</v>
       </c>
       <c r="Q101">
-        <v>13993.439385393</v>
+        <v>14018.892068187</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.395074935852563</v>
+        <v>2.393564560944092</v>
       </c>
       <c r="T101">
         <v>54.22089055298134</v>
       </c>
       <c r="U101">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V101">
         <v>0.258</v>
       </c>
       <c r="W101">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9720,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>15.03394118675837</v>
+        <v>15.45238090169797</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/netherlands/netherlands_diversified.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_diversified.xlsx
@@ -1391,7 +1391,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1528,22 +1528,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07733139435579917</v>
+        <v>0.07716526935836121</v>
       </c>
       <c r="C2">
-        <v>24577.82925899202</v>
+        <v>24341.08959635497</v>
       </c>
       <c r="D2">
-        <v>23707.82925899202</v>
+        <v>23718.58459635497</v>
       </c>
       <c r="E2">
-        <v>-5052</v>
+        <v>-4804.505</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>247.495</v>
       </c>
       <c r="G2">
         <v>870</v>
@@ -1564,28 +1564,28 @@
         <v>19044.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>12.4489985</v>
       </c>
       <c r="N2">
-        <v>19044.3</v>
+        <v>19031.8510015</v>
       </c>
       <c r="O2">
-        <v>4913.4294</v>
+        <v>4910.217558387</v>
       </c>
       <c r="P2">
-        <v>14130.8706</v>
+        <v>14121.633443113</v>
       </c>
       <c r="Q2">
-        <v>14933.3706</v>
+        <v>14924.133443113</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07733139435579917</v>
+        <v>0.07756772056400121</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429368</v>
+        <v>0.7336656019399818</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>1529.785709268099</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1610,22 +1610,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07716526935836121</v>
+        <v>0.07699914436092323</v>
       </c>
       <c r="C3">
-        <v>24341.08959635497</v>
+        <v>24104.35969671923</v>
       </c>
       <c r="D3">
-        <v>23718.58459635497</v>
+        <v>23729.34969671923</v>
       </c>
       <c r="E3">
-        <v>-4804.505</v>
+        <v>-4557.01</v>
       </c>
       <c r="F3">
-        <v>247.495</v>
+        <v>494.99</v>
       </c>
       <c r="G3">
         <v>870</v>
@@ -1646,28 +1646,28 @@
         <v>19044.3</v>
       </c>
       <c r="M3">
-        <v>12.4489985</v>
+        <v>24.897997</v>
       </c>
       <c r="N3">
-        <v>19031.8510015</v>
+        <v>19019.402003</v>
       </c>
       <c r="O3">
-        <v>4910.217558387</v>
+        <v>4907.005716774</v>
       </c>
       <c r="P3">
-        <v>14121.633443113</v>
+        <v>14112.396286226</v>
       </c>
       <c r="Q3">
-        <v>14924.133443113</v>
+        <v>14914.896286226</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07756772056400121</v>
+        <v>0.07780886975604412</v>
       </c>
       <c r="T3">
-        <v>0.7336656019399818</v>
+        <v>0.7392348673451299</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>1529.785709268099</v>
+        <v>764.8928546340494</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1692,22 +1692,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07699914436092323</v>
+        <v>0.07683301936348526</v>
       </c>
       <c r="C4">
-        <v>24104.35969671923</v>
+        <v>23867.63957338416</v>
       </c>
       <c r="D4">
-        <v>23729.34969671923</v>
+        <v>23740.12457338416</v>
       </c>
       <c r="E4">
-        <v>-4557.01</v>
+        <v>-4309.515</v>
       </c>
       <c r="F4">
-        <v>494.99</v>
+        <v>742.485</v>
       </c>
       <c r="G4">
         <v>870</v>
@@ -1728,28 +1728,28 @@
         <v>19044.3</v>
       </c>
       <c r="M4">
-        <v>24.897997</v>
+        <v>37.3469955</v>
       </c>
       <c r="N4">
-        <v>19019.402003</v>
+        <v>19006.9530045</v>
       </c>
       <c r="O4">
-        <v>4907.005716774</v>
+        <v>4903.793875161</v>
       </c>
       <c r="P4">
-        <v>14112.396286226</v>
+        <v>14103.159129339</v>
       </c>
       <c r="Q4">
-        <v>14914.896286226</v>
+        <v>14905.659129339</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07780886975604412</v>
+        <v>0.07805499109637656</v>
       </c>
       <c r="T4">
-        <v>0.7392348673451299</v>
+        <v>0.744918962964817</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>764.8928546340494</v>
+        <v>509.928569756033</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1774,22 +1774,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07683301936348526</v>
+        <v>0.07666689436604732</v>
       </c>
       <c r="C5">
-        <v>23867.63957338416</v>
+        <v>23630.92923967331</v>
       </c>
       <c r="D5">
-        <v>23740.12457338416</v>
+        <v>23750.90923967331</v>
       </c>
       <c r="E5">
-        <v>-4309.515</v>
+        <v>-4062.02</v>
       </c>
       <c r="F5">
-        <v>742.485</v>
+        <v>989.98</v>
       </c>
       <c r="G5">
         <v>870</v>
@@ -1810,28 +1810,28 @@
         <v>19044.3</v>
       </c>
       <c r="M5">
-        <v>37.3469955</v>
+        <v>49.795994</v>
       </c>
       <c r="N5">
-        <v>19006.9530045</v>
+        <v>18994.504006</v>
       </c>
       <c r="O5">
-        <v>4903.793875161</v>
+        <v>4900.582033548</v>
       </c>
       <c r="P5">
-        <v>14103.159129339</v>
+        <v>14093.921972452</v>
       </c>
       <c r="Q5">
-        <v>14905.659129339</v>
+        <v>14896.421972452</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07805499109637656</v>
+        <v>0.07830623996463262</v>
       </c>
       <c r="T5">
-        <v>0.744918962964817</v>
+        <v>0.7507214772432477</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>509.928569756033</v>
+        <v>382.4464273170247</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1856,22 +1856,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07666689436604732</v>
+        <v>0.07650076936860935</v>
       </c>
       <c r="C6">
-        <v>23630.92923967331</v>
+        <v>23394.22870893442</v>
       </c>
       <c r="D6">
-        <v>23750.90923967331</v>
+        <v>23761.70370893442</v>
       </c>
       <c r="E6">
-        <v>-4062.02</v>
+        <v>-3814.525</v>
       </c>
       <c r="F6">
-        <v>989.98</v>
+        <v>1237.475</v>
       </c>
       <c r="G6">
         <v>870</v>
@@ -1892,28 +1892,28 @@
         <v>19044.3</v>
       </c>
       <c r="M6">
-        <v>49.795994</v>
+        <v>62.2449925</v>
       </c>
       <c r="N6">
-        <v>18994.504006</v>
+        <v>18982.0550075</v>
       </c>
       <c r="O6">
-        <v>4900.582033548</v>
+        <v>4897.370191935</v>
       </c>
       <c r="P6">
-        <v>14093.921972452</v>
+        <v>14084.684815565</v>
       </c>
       <c r="Q6">
-        <v>14896.421972452</v>
+        <v>14887.184815565</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07830623996463262</v>
+        <v>0.07856277828274669</v>
       </c>
       <c r="T6">
-        <v>0.7507214772432477</v>
+        <v>0.7566461497170136</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>382.4464273170247</v>
+        <v>305.9571418536198</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1938,22 +1938,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07650076936860935</v>
+        <v>0.07633464437117138</v>
       </c>
       <c r="C7">
-        <v>23394.22870893442</v>
+        <v>23157.53799453953</v>
       </c>
       <c r="D7">
-        <v>23761.70370893442</v>
+        <v>23772.50799453953</v>
       </c>
       <c r="E7">
-        <v>-3814.525</v>
+        <v>-3567.03</v>
       </c>
       <c r="F7">
-        <v>1237.475</v>
+        <v>1484.97</v>
       </c>
       <c r="G7">
         <v>870</v>
@@ -1974,28 +1974,28 @@
         <v>19044.3</v>
       </c>
       <c r="M7">
-        <v>62.2449925</v>
+        <v>74.693991</v>
       </c>
       <c r="N7">
-        <v>18982.0550075</v>
+        <v>18969.606009</v>
       </c>
       <c r="O7">
-        <v>4897.370191935</v>
+        <v>4894.158350322</v>
       </c>
       <c r="P7">
-        <v>14084.684815565</v>
+        <v>14075.447658678</v>
       </c>
       <c r="Q7">
-        <v>14887.184815565</v>
+        <v>14877.947658678</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07856277828274669</v>
+        <v>0.07882477486294828</v>
       </c>
       <c r="T7">
-        <v>0.7566461497170136</v>
+        <v>0.7626968790519235</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>305.9571418536198</v>
+        <v>254.9642848780165</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2020,22 +2020,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07633464437117138</v>
+        <v>0.07616851937373342</v>
       </c>
       <c r="C8">
-        <v>23157.53799453953</v>
+        <v>22920.85710988502</v>
       </c>
       <c r="D8">
-        <v>23772.50799453953</v>
+        <v>23783.32210988502</v>
       </c>
       <c r="E8">
-        <v>-3567.03</v>
+        <v>-3319.535</v>
       </c>
       <c r="F8">
-        <v>1484.97</v>
+        <v>1732.465</v>
       </c>
       <c r="G8">
         <v>870</v>
@@ -2056,28 +2056,28 @@
         <v>19044.3</v>
       </c>
       <c r="M8">
-        <v>74.693991</v>
+        <v>87.14298949999998</v>
       </c>
       <c r="N8">
-        <v>18969.606009</v>
+        <v>18957.1570105</v>
       </c>
       <c r="O8">
-        <v>4894.158350322</v>
+        <v>4890.946508709</v>
       </c>
       <c r="P8">
-        <v>14075.447658678</v>
+        <v>14066.210501791</v>
       </c>
       <c r="Q8">
-        <v>14877.947658678</v>
+        <v>14868.710501791</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07882477486294828</v>
+        <v>0.07909240577820797</v>
       </c>
       <c r="T8">
-        <v>0.7626968790519235</v>
+        <v>0.7688777315983369</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>254.9642848780165</v>
+        <v>218.5408156097284</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2102,22 +2102,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07616851937373341</v>
+        <v>0.07600239437629547</v>
       </c>
       <c r="C9">
-        <v>22920.85710988502</v>
+        <v>22684.18606839162</v>
       </c>
       <c r="D9">
-        <v>23783.32210988502</v>
+        <v>23794.14606839162</v>
       </c>
       <c r="E9">
-        <v>-3319.535</v>
+        <v>-3072.04</v>
       </c>
       <c r="F9">
-        <v>1732.465</v>
+        <v>1979.96</v>
       </c>
       <c r="G9">
         <v>870</v>
@@ -2138,28 +2138,28 @@
         <v>19044.3</v>
       </c>
       <c r="M9">
-        <v>87.1429895</v>
+        <v>99.591988</v>
       </c>
       <c r="N9">
-        <v>18957.1570105</v>
+        <v>18944.708012</v>
       </c>
       <c r="O9">
-        <v>4890.946508709</v>
+        <v>4887.734667096</v>
       </c>
       <c r="P9">
-        <v>14066.210501791</v>
+        <v>14056.973344904</v>
       </c>
       <c r="Q9">
-        <v>14868.710501791</v>
+        <v>14859.473344904</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07909240577820797</v>
+        <v>0.07936585475684289</v>
       </c>
       <c r="T9">
-        <v>0.7688777315983369</v>
+        <v>0.7751929505044549</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>218.5408156097284</v>
+        <v>191.2232136585123</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2184,22 +2184,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07600239437629547</v>
+        <v>0.0758362693788575</v>
       </c>
       <c r="C10">
-        <v>22684.18606839162</v>
+        <v>22447.52488350455</v>
       </c>
       <c r="D10">
-        <v>23794.14606839162</v>
+        <v>23804.97988350455</v>
       </c>
       <c r="E10">
-        <v>-3072.04</v>
+        <v>-2824.545</v>
       </c>
       <c r="F10">
-        <v>1979.96</v>
+        <v>2227.455</v>
       </c>
       <c r="G10">
         <v>870</v>
@@ -2220,28 +2220,28 @@
         <v>19044.3</v>
       </c>
       <c r="M10">
-        <v>99.591988</v>
+        <v>112.0409865</v>
       </c>
       <c r="N10">
-        <v>18944.708012</v>
+        <v>18932.2590135</v>
       </c>
       <c r="O10">
-        <v>4887.734667096</v>
+        <v>4884.522825483</v>
       </c>
       <c r="P10">
-        <v>14056.973344904</v>
+        <v>14047.736188017</v>
       </c>
       <c r="Q10">
-        <v>14859.473344904</v>
+        <v>14850.236188017</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07936585475684289</v>
+        <v>0.07964531360314012</v>
       </c>
       <c r="T10">
-        <v>0.7751929505044549</v>
+        <v>0.7816469654304877</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>191.2232136585123</v>
+        <v>169.9761899186777</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2266,22 +2266,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0758362693788575</v>
+        <v>0.07567014438141956</v>
       </c>
       <c r="C11">
-        <v>22447.52488350455</v>
+        <v>22210.87356869349</v>
       </c>
       <c r="D11">
-        <v>23804.97988350455</v>
+        <v>23815.82356869349</v>
       </c>
       <c r="E11">
-        <v>-2824.545</v>
+        <v>-2577.05</v>
       </c>
       <c r="F11">
-        <v>2227.455</v>
+        <v>2474.95</v>
       </c>
       <c r="G11">
         <v>870</v>
@@ -2302,28 +2302,28 @@
         <v>19044.3</v>
       </c>
       <c r="M11">
-        <v>112.0409865</v>
+        <v>124.489985</v>
       </c>
       <c r="N11">
-        <v>18932.2590135</v>
+        <v>18919.810015</v>
       </c>
       <c r="O11">
-        <v>4884.522825483</v>
+        <v>4881.31098387</v>
       </c>
       <c r="P11">
-        <v>14047.736188017</v>
+        <v>14038.49903113</v>
       </c>
       <c r="Q11">
-        <v>14850.236188017</v>
+        <v>14840.99903113</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07964531360314012</v>
+        <v>0.07993098264602172</v>
       </c>
       <c r="T11">
-        <v>0.7816469654304877</v>
+        <v>0.7882444029104323</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>169.9761899186777</v>
+        <v>152.9785709268099</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2348,22 +2348,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07567014438141956</v>
+        <v>0.07550401938398159</v>
       </c>
       <c r="C12">
-        <v>22210.87356869349</v>
+        <v>21974.23213745269</v>
       </c>
       <c r="D12">
-        <v>23815.82356869349</v>
+        <v>23826.67713745269</v>
       </c>
       <c r="E12">
-        <v>-2577.05</v>
+        <v>-2329.555</v>
       </c>
       <c r="F12">
-        <v>2474.95</v>
+        <v>2722.445</v>
       </c>
       <c r="G12">
         <v>870</v>
@@ -2384,28 +2384,28 @@
         <v>19044.3</v>
       </c>
       <c r="M12">
-        <v>124.489985</v>
+        <v>136.9389835</v>
       </c>
       <c r="N12">
-        <v>18919.810015</v>
+        <v>18907.3610165</v>
       </c>
       <c r="O12">
-        <v>4881.31098387</v>
+        <v>4878.099142257</v>
       </c>
       <c r="P12">
-        <v>14038.49903113</v>
+        <v>14029.261874243</v>
       </c>
       <c r="Q12">
-        <v>14840.99903113</v>
+        <v>14831.761874243</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07993098264602172</v>
+        <v>0.08022307121795683</v>
       </c>
       <c r="T12">
-        <v>0.7882444029104323</v>
+        <v>0.794990097412398</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>152.9785709268099</v>
+        <v>139.0714281152817</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2430,22 +2430,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07550401938398159</v>
+        <v>0.07533789438654362</v>
       </c>
       <c r="C13">
-        <v>21974.23213745269</v>
+        <v>21737.60060330102</v>
       </c>
       <c r="D13">
-        <v>23826.67713745269</v>
+        <v>23837.54060330101</v>
       </c>
       <c r="E13">
-        <v>-2329.555</v>
+        <v>-2082.06</v>
       </c>
       <c r="F13">
-        <v>2722.445</v>
+        <v>2969.94</v>
       </c>
       <c r="G13">
         <v>870</v>
@@ -2466,28 +2466,28 @@
         <v>19044.3</v>
       </c>
       <c r="M13">
-        <v>136.9389835</v>
+        <v>149.387982</v>
       </c>
       <c r="N13">
-        <v>18907.3610165</v>
+        <v>18894.912018</v>
       </c>
       <c r="O13">
-        <v>4878.099142257</v>
+        <v>4874.887300644</v>
       </c>
       <c r="P13">
-        <v>14029.261874243</v>
+        <v>14020.024717356</v>
       </c>
       <c r="Q13">
-        <v>14831.761874243</v>
+        <v>14822.524717356</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08022307121795683</v>
+        <v>0.08052179816652684</v>
       </c>
       <c r="T13">
-        <v>0.794990097412398</v>
+        <v>0.801889103153045</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>139.0714281152817</v>
+        <v>127.4821424390082</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2512,22 +2512,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07533789438654362</v>
+        <v>0.07517176938910566</v>
       </c>
       <c r="C14">
-        <v>21737.60060330102</v>
+        <v>21500.97897978198</v>
       </c>
       <c r="D14">
-        <v>23837.54060330101</v>
+        <v>23848.41397978198</v>
       </c>
       <c r="E14">
-        <v>-2082.06</v>
+        <v>-1834.565</v>
       </c>
       <c r="F14">
-        <v>2969.94</v>
+        <v>3217.435</v>
       </c>
       <c r="G14">
         <v>870</v>
@@ -2548,28 +2548,28 @@
         <v>19044.3</v>
       </c>
       <c r="M14">
-        <v>149.387982</v>
+        <v>161.8369805</v>
       </c>
       <c r="N14">
-        <v>18894.912018</v>
+        <v>18882.4630195</v>
       </c>
       <c r="O14">
-        <v>4874.887300644</v>
+        <v>4871.675459031</v>
       </c>
       <c r="P14">
-        <v>14020.024717356</v>
+        <v>14010.787560469</v>
       </c>
       <c r="Q14">
-        <v>14822.524717356</v>
+        <v>14813.287560469</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08052179816652684</v>
+        <v>0.08082739240127088</v>
       </c>
       <c r="T14">
-        <v>0.801889103153045</v>
+        <v>0.80894670672681</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>127.4821424390082</v>
+        <v>117.6758237898538</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2594,22 +2594,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07517176938910566</v>
+        <v>0.07500564439166769</v>
       </c>
       <c r="C15">
-        <v>21500.97897978198</v>
+        <v>21264.36728046385</v>
       </c>
       <c r="D15">
-        <v>23848.41397978198</v>
+        <v>23859.29728046385</v>
       </c>
       <c r="E15">
-        <v>-1834.565</v>
+        <v>-1587.07</v>
       </c>
       <c r="F15">
-        <v>3217.435</v>
+        <v>3464.93</v>
       </c>
       <c r="G15">
         <v>870</v>
@@ -2630,28 +2630,28 @@
         <v>19044.3</v>
       </c>
       <c r="M15">
-        <v>161.8369805</v>
+        <v>174.285979</v>
       </c>
       <c r="N15">
-        <v>18882.4630195</v>
+        <v>18870.014021</v>
       </c>
       <c r="O15">
-        <v>4871.675459031</v>
+        <v>4868.463617418</v>
       </c>
       <c r="P15">
-        <v>14010.787560469</v>
+        <v>14001.550403582</v>
       </c>
       <c r="Q15">
-        <v>14813.287560469</v>
+        <v>14804.050403582</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08082739240127088</v>
+        <v>0.08114009347868337</v>
       </c>
       <c r="T15">
-        <v>0.80894670672681</v>
+        <v>0.8161684406162442</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>117.6758237898538</v>
+        <v>109.2704078048642</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2676,22 +2676,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07500564439166769</v>
+        <v>0.07483951939422973</v>
       </c>
       <c r="C16">
-        <v>21264.36728046385</v>
+        <v>21027.76551893963</v>
       </c>
       <c r="D16">
-        <v>23859.29728046385</v>
+        <v>23870.19051893963</v>
       </c>
       <c r="E16">
-        <v>-1587.07</v>
+        <v>-1339.574999999999</v>
       </c>
       <c r="F16">
-        <v>3464.93</v>
+        <v>3712.425000000001</v>
       </c>
       <c r="G16">
         <v>870</v>
@@ -2712,28 +2712,28 @@
         <v>19044.3</v>
       </c>
       <c r="M16">
-        <v>174.285979</v>
+        <v>186.7349775</v>
       </c>
       <c r="N16">
-        <v>18870.014021</v>
+        <v>18857.5650225</v>
       </c>
       <c r="O16">
-        <v>4868.463617418</v>
+        <v>4865.251775805</v>
       </c>
       <c r="P16">
-        <v>14001.550403582</v>
+        <v>13992.313246695</v>
       </c>
       <c r="Q16">
-        <v>14804.050403582</v>
+        <v>14794.813246695</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08114009347868337</v>
+        <v>0.08146015222850557</v>
       </c>
       <c r="T16">
-        <v>0.8161684406162442</v>
+        <v>0.8235600976560179</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>109.2704078048642</v>
+        <v>101.9857139512066</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2758,22 +2758,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07483951939422973</v>
+        <v>0.07467339439679176</v>
       </c>
       <c r="C17">
-        <v>21027.76551893963</v>
+        <v>20791.17370882721</v>
       </c>
       <c r="D17">
-        <v>23870.19051893963</v>
+        <v>23881.0937088272</v>
       </c>
       <c r="E17">
-        <v>-1339.575</v>
+        <v>-1092.08</v>
       </c>
       <c r="F17">
-        <v>3712.425</v>
+        <v>3959.92</v>
       </c>
       <c r="G17">
         <v>870</v>
@@ -2794,28 +2794,28 @@
         <v>19044.3</v>
       </c>
       <c r="M17">
-        <v>186.7349775</v>
+        <v>199.183976</v>
       </c>
       <c r="N17">
-        <v>18857.5650225</v>
+        <v>18845.116024</v>
       </c>
       <c r="O17">
-        <v>4865.251775805</v>
+        <v>4862.039934192</v>
       </c>
       <c r="P17">
-        <v>13992.313246695</v>
+        <v>13983.076089808</v>
       </c>
       <c r="Q17">
-        <v>14794.813246695</v>
+        <v>14785.576089808</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08146015222850557</v>
+        <v>0.0817878314247521</v>
       </c>
       <c r="T17">
-        <v>0.8235600976560179</v>
+        <v>0.8311277465300718</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>101.9857139512066</v>
+        <v>95.61160682925617</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2840,22 +2840,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07467339439679176</v>
+        <v>0.0745072693993538</v>
       </c>
       <c r="C18">
-        <v>20791.17370882721</v>
+        <v>20554.59186376931</v>
       </c>
       <c r="D18">
-        <v>23881.0937088272</v>
+        <v>23892.00686376931</v>
       </c>
       <c r="E18">
-        <v>-1092.08</v>
+        <v>-844.585</v>
       </c>
       <c r="F18">
-        <v>3959.92</v>
+        <v>4207.415</v>
       </c>
       <c r="G18">
         <v>870</v>
@@ -2876,28 +2876,28 @@
         <v>19044.3</v>
       </c>
       <c r="M18">
-        <v>199.183976</v>
+        <v>211.6329745</v>
       </c>
       <c r="N18">
-        <v>18845.116024</v>
+        <v>18832.6670255</v>
       </c>
       <c r="O18">
-        <v>4862.039934192</v>
+        <v>4858.828092579</v>
       </c>
       <c r="P18">
-        <v>13983.076089808</v>
+        <v>13973.838932921</v>
       </c>
       <c r="Q18">
-        <v>14785.576089808</v>
+        <v>14776.338932921</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0817878314247521</v>
+        <v>0.08212340650524555</v>
       </c>
       <c r="T18">
-        <v>0.8311277465300718</v>
+        <v>0.8388777483890429</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>95.61160682925617</v>
+        <v>89.98739466282935</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2922,22 +2922,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0745072693993538</v>
+        <v>0.07434114440191583</v>
       </c>
       <c r="C19">
-        <v>20554.59186376931</v>
+        <v>20318.01999743365</v>
       </c>
       <c r="D19">
-        <v>23892.00686376931</v>
+        <v>23902.92999743365</v>
       </c>
       <c r="E19">
-        <v>-844.585</v>
+        <v>-597.0899999999992</v>
       </c>
       <c r="F19">
-        <v>4207.415</v>
+        <v>4454.910000000001</v>
       </c>
       <c r="G19">
         <v>870</v>
@@ -2958,28 +2958,28 @@
         <v>19044.3</v>
       </c>
       <c r="M19">
-        <v>211.6329745</v>
+        <v>224.081973</v>
       </c>
       <c r="N19">
-        <v>18832.6670255</v>
+        <v>18820.218027</v>
       </c>
       <c r="O19">
-        <v>4858.828092579</v>
+        <v>4855.616250966</v>
       </c>
       <c r="P19">
-        <v>13973.838932921</v>
+        <v>13964.601776034</v>
       </c>
       <c r="Q19">
-        <v>14776.338932921</v>
+        <v>14767.101776034</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08212340650524555</v>
+        <v>0.0824671663437998</v>
       </c>
       <c r="T19">
-        <v>0.8388777483890429</v>
+        <v>0.8468167746835985</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>89.98739466282935</v>
+        <v>84.98809495933881</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3004,22 +3004,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07434114440191583</v>
+        <v>0.07417501940447789</v>
       </c>
       <c r="C20">
-        <v>20318.01999743365</v>
+        <v>20081.45812351294</v>
       </c>
       <c r="D20">
-        <v>23902.92999743365</v>
+        <v>23913.86312351294</v>
       </c>
       <c r="E20">
-        <v>-597.0900000000001</v>
+        <v>-349.5950000000003</v>
       </c>
       <c r="F20">
-        <v>4454.91</v>
+        <v>4702.405</v>
       </c>
       <c r="G20">
         <v>870</v>
@@ -3040,28 +3040,28 @@
         <v>19044.3</v>
       </c>
       <c r="M20">
-        <v>224.081973</v>
+        <v>236.5309715</v>
       </c>
       <c r="N20">
-        <v>18820.218027</v>
+        <v>18807.7690285</v>
       </c>
       <c r="O20">
-        <v>4855.616250966</v>
+        <v>4852.404409353</v>
       </c>
       <c r="P20">
-        <v>13964.601776034</v>
+        <v>13955.364619147</v>
       </c>
       <c r="Q20">
-        <v>14767.101776034</v>
+        <v>14757.864619147</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0824671663437998</v>
+        <v>0.08281941407960233</v>
       </c>
       <c r="T20">
-        <v>0.8468167746835985</v>
+        <v>0.8549518263187605</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>84.98809495933884</v>
+        <v>80.51503732989995</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3086,22 +3086,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07417501940447789</v>
+        <v>0.07400889440703992</v>
       </c>
       <c r="C21">
-        <v>20081.45812351294</v>
+        <v>19844.90625572496</v>
       </c>
       <c r="D21">
-        <v>23913.86312351294</v>
+        <v>23924.80625572497</v>
       </c>
       <c r="E21">
-        <v>-349.5950000000003</v>
+        <v>-102.0999999999995</v>
       </c>
       <c r="F21">
-        <v>4702.405</v>
+        <v>4949.900000000001</v>
       </c>
       <c r="G21">
         <v>870</v>
@@ -3122,28 +3122,28 @@
         <v>19044.3</v>
       </c>
       <c r="M21">
-        <v>236.5309715</v>
+        <v>248.97997</v>
       </c>
       <c r="N21">
-        <v>18807.7690285</v>
+        <v>18795.32003</v>
       </c>
       <c r="O21">
-        <v>4852.404409353</v>
+        <v>4849.19256774</v>
       </c>
       <c r="P21">
-        <v>13955.364619147</v>
+        <v>13946.12746226</v>
       </c>
       <c r="Q21">
-        <v>14757.864619147</v>
+        <v>14748.62746226</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08281941407960233</v>
+        <v>0.0831804680087999</v>
       </c>
       <c r="T21">
-        <v>0.8549518263187605</v>
+        <v>0.8632902542448015</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>80.51503732989995</v>
+        <v>76.48928546340494</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3168,22 +3168,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07400889440703992</v>
+        <v>0.07384276940960197</v>
       </c>
       <c r="C22">
-        <v>19844.90625572496</v>
+        <v>19608.3644078126</v>
       </c>
       <c r="D22">
-        <v>23924.80625572497</v>
+        <v>23935.7594078126</v>
       </c>
       <c r="E22">
-        <v>-102.0999999999995</v>
+        <v>145.3950000000004</v>
       </c>
       <c r="F22">
-        <v>4949.900000000001</v>
+        <v>5197.395</v>
       </c>
       <c r="G22">
         <v>870</v>
@@ -3204,28 +3204,28 @@
         <v>19044.3</v>
       </c>
       <c r="M22">
-        <v>248.97997</v>
+        <v>261.4289685</v>
       </c>
       <c r="N22">
-        <v>18795.32003</v>
+        <v>18782.8710315</v>
       </c>
       <c r="O22">
-        <v>4849.19256774</v>
+        <v>4845.980726127</v>
       </c>
       <c r="P22">
-        <v>13946.12746226</v>
+        <v>13936.890305373</v>
       </c>
       <c r="Q22">
-        <v>14748.62746226</v>
+        <v>14739.390305373</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0831804680087999</v>
+        <v>0.08355066254379995</v>
       </c>
       <c r="T22">
-        <v>0.8632902542448015</v>
+        <v>0.8718397816120083</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>76.48928546340494</v>
+        <v>72.84693853657613</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3250,22 +3250,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07384276940960197</v>
+        <v>0.073676644412164</v>
       </c>
       <c r="C23">
-        <v>19608.3644078126</v>
+        <v>19371.83259354393</v>
       </c>
       <c r="D23">
-        <v>23935.7594078126</v>
+        <v>23946.72259354393</v>
       </c>
       <c r="E23">
-        <v>145.3949999999995</v>
+        <v>392.8900000000003</v>
       </c>
       <c r="F23">
-        <v>5197.395</v>
+        <v>5444.89</v>
       </c>
       <c r="G23">
         <v>870</v>
@@ -3286,28 +3286,28 @@
         <v>19044.3</v>
       </c>
       <c r="M23">
-        <v>261.4289684999999</v>
+        <v>273.877967</v>
       </c>
       <c r="N23">
-        <v>18782.8710315</v>
+        <v>18770.422033</v>
       </c>
       <c r="O23">
-        <v>4845.980726127</v>
+        <v>4842.768884514</v>
       </c>
       <c r="P23">
-        <v>13936.890305373</v>
+        <v>13927.653148486</v>
       </c>
       <c r="Q23">
-        <v>14739.390305373</v>
+        <v>14730.153148486</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08355066254379995</v>
+        <v>0.0839303492463641</v>
       </c>
       <c r="T23">
-        <v>0.8718397816120081</v>
+        <v>0.880608527629656</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>72.84693853657615</v>
+        <v>69.53571405764086</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3332,22 +3332,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.073676644412164</v>
+        <v>0.07351051941472604</v>
       </c>
       <c r="C24">
-        <v>19371.83259354393</v>
+        <v>19135.31082671225</v>
       </c>
       <c r="D24">
-        <v>23946.72259354393</v>
+        <v>23957.69582671225</v>
       </c>
       <c r="E24">
-        <v>392.8900000000003</v>
+        <v>640.3850000000002</v>
       </c>
       <c r="F24">
-        <v>5444.89</v>
+        <v>5692.385</v>
       </c>
       <c r="G24">
         <v>870</v>
@@ -3368,28 +3368,28 @@
         <v>19044.3</v>
       </c>
       <c r="M24">
-        <v>273.877967</v>
+        <v>286.3269655</v>
       </c>
       <c r="N24">
-        <v>18770.422033</v>
+        <v>18757.9730345</v>
       </c>
       <c r="O24">
-        <v>4842.768884514</v>
+        <v>4839.557042900999</v>
       </c>
       <c r="P24">
-        <v>13927.653148486</v>
+        <v>13918.415991599</v>
       </c>
       <c r="Q24">
-        <v>14730.153148486</v>
+        <v>14720.915991599</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0839303492463641</v>
+        <v>0.08431989794120265</v>
       </c>
       <c r="T24">
-        <v>0.880608527629656</v>
+        <v>0.8896050332841259</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>69.53571405764086</v>
+        <v>66.51242214209127</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3414,22 +3414,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07351051941472604</v>
+        <v>0.07334439441728809</v>
       </c>
       <c r="C25">
-        <v>19135.31082671225</v>
+        <v>18898.79912113618</v>
       </c>
       <c r="D25">
-        <v>23957.69582671225</v>
+        <v>23968.67912113618</v>
       </c>
       <c r="E25">
-        <v>640.3850000000002</v>
+        <v>887.8800000000001</v>
       </c>
       <c r="F25">
-        <v>5692.385</v>
+        <v>5939.88</v>
       </c>
       <c r="G25">
         <v>870</v>
@@ -3450,28 +3450,28 @@
         <v>19044.3</v>
       </c>
       <c r="M25">
-        <v>286.3269655</v>
+        <v>298.775964</v>
       </c>
       <c r="N25">
-        <v>18757.9730345</v>
+        <v>18745.524036</v>
       </c>
       <c r="O25">
-        <v>4839.557042900999</v>
+        <v>4836.345201288</v>
       </c>
       <c r="P25">
-        <v>13918.415991599</v>
+        <v>13909.178834712</v>
       </c>
       <c r="Q25">
-        <v>14720.915991599</v>
+        <v>14711.678834712</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08431989794120265</v>
+        <v>0.08471969791748431</v>
       </c>
       <c r="T25">
-        <v>0.8896050332841259</v>
+        <v>0.8988382890873976</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>66.51242214209127</v>
+        <v>63.74107121950412</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3496,22 +3496,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07334439441728807</v>
+        <v>0.07317826941985012</v>
       </c>
       <c r="C26">
-        <v>18898.79912113618</v>
+        <v>18662.29749065967</v>
       </c>
       <c r="D26">
-        <v>23968.67912113618</v>
+        <v>23979.67249065967</v>
       </c>
       <c r="E26">
-        <v>887.8800000000001</v>
+        <v>1135.375</v>
       </c>
       <c r="F26">
-        <v>5939.88</v>
+        <v>6187.375</v>
       </c>
       <c r="G26">
         <v>870</v>
@@ -3532,28 +3532,28 @@
         <v>19044.3</v>
       </c>
       <c r="M26">
-        <v>298.775964</v>
+        <v>311.2249625</v>
       </c>
       <c r="N26">
-        <v>18745.524036</v>
+        <v>18733.0750375</v>
       </c>
       <c r="O26">
-        <v>4836.345201288</v>
+        <v>4833.133359675</v>
       </c>
       <c r="P26">
-        <v>13909.178834712</v>
+        <v>13899.941677825</v>
       </c>
       <c r="Q26">
-        <v>14711.678834712</v>
+        <v>14702.441677825</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08471969791748431</v>
+        <v>0.08513015922646683</v>
       </c>
       <c r="T26">
-        <v>0.8988382890873976</v>
+        <v>0.9083177650454233</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>63.74107121950412</v>
+        <v>61.19142837072395</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3578,22 +3578,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07317826941985012</v>
+        <v>0.07301214442241215</v>
       </c>
       <c r="C27">
-        <v>18662.29749065967</v>
+        <v>18425.80594915208</v>
       </c>
       <c r="D27">
-        <v>23979.67249065967</v>
+        <v>23990.67594915208</v>
       </c>
       <c r="E27">
-        <v>1135.375</v>
+        <v>1382.87</v>
       </c>
       <c r="F27">
-        <v>6187.375</v>
+        <v>6434.87</v>
       </c>
       <c r="G27">
         <v>870</v>
@@ -3614,28 +3614,28 @@
         <v>19044.3</v>
       </c>
       <c r="M27">
-        <v>311.2249625</v>
+        <v>323.673961</v>
       </c>
       <c r="N27">
-        <v>18733.0750375</v>
+        <v>18720.626039</v>
       </c>
       <c r="O27">
-        <v>4833.133359675</v>
+        <v>4829.921518061999</v>
       </c>
       <c r="P27">
-        <v>13899.941677825</v>
+        <v>13890.704520938</v>
       </c>
       <c r="Q27">
-        <v>14702.441677825</v>
+        <v>14693.204520938</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08513015922646683</v>
+        <v>0.08555171408434074</v>
       </c>
       <c r="T27">
-        <v>0.9083177650454233</v>
+        <v>0.9180534430563684</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>61.19142837072395</v>
+        <v>58.83791189492688</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3660,22 +3660,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07301214442241215</v>
+        <v>0.07284601942497419</v>
       </c>
       <c r="C28">
-        <v>18425.80594915208</v>
+        <v>18189.32451050824</v>
       </c>
       <c r="D28">
-        <v>23990.67594915208</v>
+        <v>24001.68951050824</v>
       </c>
       <c r="E28">
-        <v>1382.87</v>
+        <v>1630.365000000001</v>
       </c>
       <c r="F28">
-        <v>6434.87</v>
+        <v>6682.365000000001</v>
       </c>
       <c r="G28">
         <v>870</v>
@@ -3696,28 +3696,28 @@
         <v>19044.3</v>
       </c>
       <c r="M28">
-        <v>323.673961</v>
+        <v>336.1229595</v>
       </c>
       <c r="N28">
-        <v>18720.626039</v>
+        <v>18708.1770405</v>
       </c>
       <c r="O28">
-        <v>4829.921518061999</v>
+        <v>4826.709676449</v>
       </c>
       <c r="P28">
-        <v>13890.704520938</v>
+        <v>13881.467364051</v>
       </c>
       <c r="Q28">
-        <v>14693.204520938</v>
+        <v>14683.967364051</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08555171408434074</v>
+        <v>0.08598481839037561</v>
       </c>
       <c r="T28">
-        <v>0.9180534430563684</v>
+        <v>0.9280558519717231</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>58.83791189492688</v>
+        <v>56.65872997289254</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3742,22 +3742,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07284601942497419</v>
+        <v>0.07267989442753624</v>
       </c>
       <c r="C29">
-        <v>18189.32451050824</v>
+        <v>17952.8531886485</v>
       </c>
       <c r="D29">
-        <v>24001.68951050824</v>
+        <v>24012.7131886485</v>
       </c>
       <c r="E29">
-        <v>1630.365000000001</v>
+        <v>1877.860000000001</v>
       </c>
       <c r="F29">
-        <v>6682.365000000001</v>
+        <v>6929.860000000001</v>
       </c>
       <c r="G29">
         <v>870</v>
@@ -3778,28 +3778,28 @@
         <v>19044.3</v>
       </c>
       <c r="M29">
-        <v>336.1229595</v>
+        <v>348.571958</v>
       </c>
       <c r="N29">
-        <v>18708.1770405</v>
+        <v>18695.728042</v>
       </c>
       <c r="O29">
-        <v>4826.709676449</v>
+        <v>4823.497834836</v>
       </c>
       <c r="P29">
-        <v>13881.467364051</v>
+        <v>13872.230207164</v>
       </c>
       <c r="Q29">
-        <v>14683.967364051</v>
+        <v>14674.730207164</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08598481839037561</v>
+        <v>0.08642995337157811</v>
       </c>
       <c r="T29">
-        <v>0.9280558519717231</v>
+        <v>0.938336105579171</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>56.65872997289254</v>
+        <v>54.6352039024321</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3824,22 +3824,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07267989442753624</v>
+        <v>0.07251376943009827</v>
       </c>
       <c r="C30">
-        <v>17952.8531886485</v>
+        <v>17716.39199751884</v>
       </c>
       <c r="D30">
-        <v>24012.7131886485</v>
+        <v>24023.74699751884</v>
       </c>
       <c r="E30">
-        <v>1877.860000000001</v>
+        <v>2125.355</v>
       </c>
       <c r="F30">
-        <v>6929.860000000001</v>
+        <v>7177.355</v>
       </c>
       <c r="G30">
         <v>870</v>
@@ -3860,28 +3860,28 @@
         <v>19044.3</v>
       </c>
       <c r="M30">
-        <v>348.571958</v>
+        <v>361.0209565</v>
       </c>
       <c r="N30">
-        <v>18695.728042</v>
+        <v>18683.2790435</v>
       </c>
       <c r="O30">
-        <v>4823.497834836</v>
+        <v>4820.285993222999</v>
       </c>
       <c r="P30">
-        <v>13872.230207164</v>
+        <v>13862.993050277</v>
       </c>
       <c r="Q30">
-        <v>14674.730207164</v>
+        <v>14665.493050277</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08642995337157811</v>
+        <v>0.08688762736633558</v>
       </c>
       <c r="T30">
-        <v>0.938336105579171</v>
+        <v>0.9489059437952793</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>54.6352039024321</v>
+        <v>52.75123135407237</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3906,22 +3906,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07251376943009827</v>
+        <v>0.0723476444326603</v>
       </c>
       <c r="C31">
-        <v>17716.39199751884</v>
+        <v>17479.94095109082</v>
       </c>
       <c r="D31">
-        <v>24023.74699751884</v>
+        <v>24034.79095109082</v>
       </c>
       <c r="E31">
-        <v>2125.355</v>
+        <v>2372.849999999999</v>
       </c>
       <c r="F31">
-        <v>7177.355</v>
+        <v>7424.849999999999</v>
       </c>
       <c r="G31">
         <v>870</v>
@@ -3942,28 +3942,28 @@
         <v>19044.3</v>
       </c>
       <c r="M31">
-        <v>361.0209565</v>
+        <v>373.469955</v>
       </c>
       <c r="N31">
-        <v>18683.2790435</v>
+        <v>18670.830045</v>
       </c>
       <c r="O31">
-        <v>4820.285993222999</v>
+        <v>4817.07415161</v>
       </c>
       <c r="P31">
-        <v>13862.993050277</v>
+        <v>13853.75589339</v>
       </c>
       <c r="Q31">
-        <v>14665.493050277</v>
+        <v>14656.25589339</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08688762736633558</v>
+        <v>0.0873583777609433</v>
       </c>
       <c r="T31">
-        <v>0.9489059437952793</v>
+        <v>0.9597777773889907</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>52.75123135407238</v>
+        <v>50.9928569756033</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3988,22 +3988,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0723476444326603</v>
+        <v>0.07218151943522234</v>
       </c>
       <c r="C32">
-        <v>17479.94095109082</v>
+        <v>17243.50006336174</v>
       </c>
       <c r="D32">
-        <v>24034.79095109082</v>
+        <v>24045.84506336174</v>
       </c>
       <c r="E32">
-        <v>2372.849999999999</v>
+        <v>2620.345</v>
       </c>
       <c r="F32">
-        <v>7424.849999999999</v>
+        <v>7672.345</v>
       </c>
       <c r="G32">
         <v>870</v>
@@ -4024,28 +4024,28 @@
         <v>19044.3</v>
       </c>
       <c r="M32">
-        <v>373.469955</v>
+        <v>385.9189535</v>
       </c>
       <c r="N32">
-        <v>18670.830045</v>
+        <v>18658.3810465</v>
       </c>
       <c r="O32">
-        <v>4817.07415161</v>
+        <v>4813.862309997</v>
       </c>
       <c r="P32">
-        <v>13853.75589339</v>
+        <v>13844.518736503</v>
       </c>
       <c r="Q32">
-        <v>14656.25589339</v>
+        <v>14647.018736503</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0873583777609433</v>
+        <v>0.08784277309452514</v>
       </c>
       <c r="T32">
-        <v>0.9597777773889907</v>
+        <v>0.9709647365941142</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>50.9928569756033</v>
+        <v>49.34792610542254</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4070,22 +4070,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07218151943522234</v>
+        <v>0.07201539443778437</v>
       </c>
       <c r="C33">
-        <v>17243.50006336174</v>
+        <v>17007.06934835466</v>
       </c>
       <c r="D33">
-        <v>24045.84506336174</v>
+        <v>24056.90934835466</v>
       </c>
       <c r="E33">
-        <v>2620.345</v>
+        <v>2867.84</v>
       </c>
       <c r="F33">
-        <v>7672.345</v>
+        <v>7919.84</v>
       </c>
       <c r="G33">
         <v>870</v>
@@ -4106,28 +4106,28 @@
         <v>19044.3</v>
       </c>
       <c r="M33">
-        <v>385.9189535</v>
+        <v>398.367952</v>
       </c>
       <c r="N33">
-        <v>18658.3810465</v>
+        <v>18645.932048</v>
       </c>
       <c r="O33">
-        <v>4813.862309997</v>
+        <v>4810.650468383999</v>
       </c>
       <c r="P33">
-        <v>13844.518736503</v>
+        <v>13835.281579616</v>
       </c>
       <c r="Q33">
-        <v>14647.018736503</v>
+        <v>14637.781579616</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08784277309452514</v>
+        <v>0.08834141534968291</v>
       </c>
       <c r="T33">
-        <v>0.9709647365941142</v>
+        <v>0.9824807240111529</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>49.34792610542254</v>
+        <v>47.80580341462809</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4152,22 +4152,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07201539443778437</v>
+        <v>0.07184926944034642</v>
       </c>
       <c r="C34">
-        <v>17007.06934835466</v>
+        <v>16770.64882011846</v>
       </c>
       <c r="D34">
-        <v>24056.90934835466</v>
+        <v>24067.98382011846</v>
       </c>
       <c r="E34">
-        <v>2867.84</v>
+        <v>3115.335</v>
       </c>
       <c r="F34">
-        <v>7919.84</v>
+        <v>8167.335</v>
       </c>
       <c r="G34">
         <v>870</v>
@@ -4188,28 +4188,28 @@
         <v>19044.3</v>
       </c>
       <c r="M34">
-        <v>398.367952</v>
+        <v>410.8169505</v>
       </c>
       <c r="N34">
-        <v>18645.932048</v>
+        <v>18633.4830495</v>
       </c>
       <c r="O34">
-        <v>4810.650468383999</v>
+        <v>4807.438626771</v>
       </c>
       <c r="P34">
-        <v>13835.281579616</v>
+        <v>13826.044422729</v>
       </c>
       <c r="Q34">
-        <v>14637.781579616</v>
+        <v>14628.544422729</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08834141534968291</v>
+        <v>0.08885494244827824</v>
       </c>
       <c r="T34">
-        <v>0.9824807240111529</v>
+        <v>0.9943404722466107</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>47.80580341462809</v>
+        <v>46.35714270509391</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4234,22 +4234,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07184926944034642</v>
+        <v>0.07168314444290844</v>
       </c>
       <c r="C35">
-        <v>16770.64882011846</v>
+        <v>16534.23849272788</v>
       </c>
       <c r="D35">
-        <v>24067.98382011846</v>
+        <v>24079.06849272788</v>
       </c>
       <c r="E35">
-        <v>3115.335</v>
+        <v>3362.83</v>
       </c>
       <c r="F35">
-        <v>8167.335</v>
+        <v>8414.83</v>
       </c>
       <c r="G35">
         <v>870</v>
@@ -4270,28 +4270,28 @@
         <v>19044.3</v>
       </c>
       <c r="M35">
-        <v>410.8169505</v>
+        <v>423.265949</v>
       </c>
       <c r="N35">
-        <v>18633.4830495</v>
+        <v>18621.034051</v>
       </c>
       <c r="O35">
-        <v>4807.438626771</v>
+        <v>4804.226785158</v>
       </c>
       <c r="P35">
-        <v>13826.044422729</v>
+        <v>13816.807265842</v>
       </c>
       <c r="Q35">
-        <v>14628.544422729</v>
+        <v>14619.307265842</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08885494244827824</v>
+        <v>0.08938403097410372</v>
       </c>
       <c r="T35">
-        <v>0.9943404722466107</v>
+        <v>1.006559606792234</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>46.35714270509391</v>
+        <v>44.99369733141467</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4316,22 +4316,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07168314444290844</v>
+        <v>0.07151701944547049</v>
       </c>
       <c r="C36">
-        <v>16534.23849272788</v>
+        <v>16297.83838028364</v>
       </c>
       <c r="D36">
-        <v>24079.06849272788</v>
+        <v>24090.16338028364</v>
       </c>
       <c r="E36">
-        <v>3362.83</v>
+        <v>3610.325000000001</v>
       </c>
       <c r="F36">
-        <v>8414.83</v>
+        <v>8662.325000000001</v>
       </c>
       <c r="G36">
         <v>870</v>
@@ -4352,28 +4352,28 @@
         <v>19044.3</v>
       </c>
       <c r="M36">
-        <v>423.265949</v>
+        <v>435.7149475</v>
       </c>
       <c r="N36">
-        <v>18621.034051</v>
+        <v>18608.5850525</v>
       </c>
       <c r="O36">
-        <v>4804.226785158</v>
+        <v>4801.014943544999</v>
       </c>
       <c r="P36">
-        <v>13816.807265842</v>
+        <v>13807.570108955</v>
       </c>
       <c r="Q36">
-        <v>14619.307265842</v>
+        <v>14610.070108955</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08938403097410372</v>
+        <v>0.0899293991468777</v>
       </c>
       <c r="T36">
-        <v>1.006559606792234</v>
+        <v>1.019154714708492</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>44.99369733141467</v>
+        <v>43.70816312194568</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4398,22 +4398,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07151701944547049</v>
+        <v>0.07135089444803253</v>
       </c>
       <c r="C37">
-        <v>16297.83838028364</v>
+        <v>16061.44849691243</v>
       </c>
       <c r="D37">
-        <v>24090.16338028364</v>
+        <v>24101.26849691243</v>
       </c>
       <c r="E37">
-        <v>3610.325000000001</v>
+        <v>3857.820000000002</v>
       </c>
       <c r="F37">
-        <v>8662.325000000001</v>
+        <v>8909.820000000002</v>
       </c>
       <c r="G37">
         <v>870</v>
@@ -4434,28 +4434,28 @@
         <v>19044.3</v>
       </c>
       <c r="M37">
-        <v>435.7149475</v>
+        <v>448.1639460000001</v>
       </c>
       <c r="N37">
-        <v>18608.5850525</v>
+        <v>18596.136054</v>
       </c>
       <c r="O37">
-        <v>4801.014943544999</v>
+        <v>4797.803101932</v>
       </c>
       <c r="P37">
-        <v>13807.570108955</v>
+        <v>13798.332952068</v>
       </c>
       <c r="Q37">
-        <v>14610.070108955</v>
+        <v>14600.832952068</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0899293991468777</v>
+        <v>0.09049181007505083</v>
       </c>
       <c r="T37">
-        <v>1.019154714708492</v>
+        <v>1.032143419747133</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>43.70816312194568</v>
+        <v>42.4940474796694</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4480,22 +4480,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07135089444803253</v>
+        <v>0.07118476945059457</v>
       </c>
       <c r="C38">
-        <v>16061.44849691243</v>
+        <v>15825.06885676702</v>
       </c>
       <c r="D38">
-        <v>24101.26849691243</v>
+        <v>24112.38385676702</v>
       </c>
       <c r="E38">
-        <v>3857.82</v>
+        <v>4105.315000000001</v>
       </c>
       <c r="F38">
-        <v>8909.82</v>
+        <v>9157.315000000001</v>
       </c>
       <c r="G38">
         <v>870</v>
@@ -4516,28 +4516,28 @@
         <v>19044.3</v>
       </c>
       <c r="M38">
-        <v>448.163946</v>
+        <v>460.6129445</v>
       </c>
       <c r="N38">
-        <v>18596.136054</v>
+        <v>18583.6870555</v>
       </c>
       <c r="O38">
-        <v>4797.803101932</v>
+        <v>4794.591260319</v>
       </c>
       <c r="P38">
-        <v>13798.332952068</v>
+        <v>13789.095795181</v>
       </c>
       <c r="Q38">
-        <v>14600.832952068</v>
+        <v>14591.595795181</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09049181007505083</v>
+        <v>0.09107207531840408</v>
       </c>
       <c r="T38">
-        <v>1.032143419747133</v>
+        <v>1.04554446462827</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>42.49404747966942</v>
+        <v>41.34555970994862</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4562,22 +4562,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07118476945059457</v>
+        <v>0.0710186444531566</v>
       </c>
       <c r="C39">
-        <v>15825.06885676702</v>
+        <v>15588.69947402628</v>
       </c>
       <c r="D39">
-        <v>24112.38385676702</v>
+        <v>24123.50947402628</v>
       </c>
       <c r="E39">
-        <v>4105.315000000001</v>
+        <v>4352.809999999999</v>
       </c>
       <c r="F39">
-        <v>9157.315000000001</v>
+        <v>9404.809999999999</v>
       </c>
       <c r="G39">
         <v>870</v>
@@ -4598,28 +4598,28 @@
         <v>19044.3</v>
       </c>
       <c r="M39">
-        <v>460.6129445</v>
+        <v>473.0619429999999</v>
       </c>
       <c r="N39">
-        <v>18583.6870555</v>
+        <v>18571.238057</v>
       </c>
       <c r="O39">
-        <v>4794.591260319</v>
+        <v>4791.379418705999</v>
       </c>
       <c r="P39">
-        <v>13789.095795181</v>
+        <v>13779.858638294</v>
       </c>
       <c r="Q39">
-        <v>14591.595795181</v>
+        <v>14582.358638294</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09107207531840408</v>
+        <v>0.09167105879541387</v>
       </c>
       <c r="T39">
-        <v>1.04554446462827</v>
+        <v>1.059377801279767</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>41.34555970994862</v>
+        <v>40.25751866494998</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4644,22 +4644,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0710186444531566</v>
+        <v>0.07085251945571866</v>
       </c>
       <c r="C40">
-        <v>15588.69947402628</v>
+        <v>15352.34036289527</v>
       </c>
       <c r="D40">
-        <v>24123.50947402628</v>
+        <v>24134.64536289527</v>
       </c>
       <c r="E40">
-        <v>4352.809999999999</v>
+        <v>4600.305</v>
       </c>
       <c r="F40">
-        <v>9404.809999999999</v>
+        <v>9652.305</v>
       </c>
       <c r="G40">
         <v>870</v>
@@ -4680,28 +4680,28 @@
         <v>19044.3</v>
       </c>
       <c r="M40">
-        <v>473.0619429999999</v>
+        <v>485.5109415</v>
       </c>
       <c r="N40">
-        <v>18571.238057</v>
+        <v>18558.7890585</v>
       </c>
       <c r="O40">
-        <v>4791.379418705999</v>
+        <v>4788.167577093</v>
       </c>
       <c r="P40">
-        <v>13779.858638294</v>
+        <v>13770.621481407</v>
       </c>
       <c r="Q40">
-        <v>14582.358638294</v>
+        <v>14573.121481407</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09167105879541387</v>
+        <v>0.09228968107494862</v>
       </c>
       <c r="T40">
-        <v>1.059377801279767</v>
+        <v>1.073664689952624</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>40.25751866494998</v>
+        <v>39.22527459661792</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4726,22 +4726,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07085251945571866</v>
+        <v>0.07068639445828069</v>
       </c>
       <c r="C41">
-        <v>15352.34036289527</v>
+        <v>15115.9915376053</v>
       </c>
       <c r="D41">
-        <v>24134.64536289527</v>
+        <v>24145.79153760531</v>
       </c>
       <c r="E41">
-        <v>4600.305</v>
+        <v>4847.800000000001</v>
       </c>
       <c r="F41">
-        <v>9652.305</v>
+        <v>9899.800000000001</v>
       </c>
       <c r="G41">
         <v>870</v>
@@ -4762,28 +4762,28 @@
         <v>19044.3</v>
       </c>
       <c r="M41">
-        <v>485.5109415</v>
+        <v>497.95994</v>
       </c>
       <c r="N41">
-        <v>18558.7890585</v>
+        <v>18546.34006</v>
       </c>
       <c r="O41">
-        <v>4788.167577093</v>
+        <v>4784.95573548</v>
       </c>
       <c r="P41">
-        <v>13770.621481407</v>
+        <v>13761.38432452</v>
       </c>
       <c r="Q41">
-        <v>14573.121481407</v>
+        <v>14563.88432452</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09228968107494862</v>
+        <v>0.09292892409713449</v>
       </c>
       <c r="T41">
-        <v>1.073664689952624</v>
+        <v>1.08842780824791</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>39.22527459661792</v>
+        <v>38.24464273170247</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4808,22 +4808,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07068639445828069</v>
+        <v>0.07052026946084272</v>
       </c>
       <c r="C42">
-        <v>15115.9915376053</v>
+        <v>14879.65301241399</v>
       </c>
       <c r="D42">
-        <v>24145.79153760531</v>
+        <v>24156.94801241399</v>
       </c>
       <c r="E42">
-        <v>4847.800000000001</v>
+        <v>5095.295</v>
       </c>
       <c r="F42">
-        <v>9899.800000000001</v>
+        <v>10147.295</v>
       </c>
       <c r="G42">
         <v>870</v>
@@ -4844,28 +4844,28 @@
         <v>19044.3</v>
       </c>
       <c r="M42">
-        <v>497.95994</v>
+        <v>510.4089385</v>
       </c>
       <c r="N42">
-        <v>18546.34006</v>
+        <v>18533.8910615</v>
       </c>
       <c r="O42">
-        <v>4784.95573548</v>
+        <v>4781.743893867</v>
       </c>
       <c r="P42">
-        <v>13761.38432452</v>
+        <v>13752.147167633</v>
       </c>
       <c r="Q42">
-        <v>14563.88432452</v>
+        <v>14554.647167633</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09292892409713449</v>
+        <v>0.0935898363743097</v>
       </c>
       <c r="T42">
-        <v>1.08842780824791</v>
+        <v>1.103691371231171</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>38.24464273170247</v>
+        <v>37.31184656751461</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4890,22 +4890,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07052026946084272</v>
+        <v>0.07035414446340477</v>
       </c>
       <c r="C43">
-        <v>14879.65301241399</v>
+        <v>14643.32480160529</v>
       </c>
       <c r="D43">
-        <v>24156.94801241399</v>
+        <v>24168.11480160529</v>
       </c>
       <c r="E43">
-        <v>5095.295</v>
+        <v>5342.790000000001</v>
       </c>
       <c r="F43">
-        <v>10147.295</v>
+        <v>10394.79</v>
       </c>
       <c r="G43">
         <v>870</v>
@@ -4926,28 +4926,28 @@
         <v>19044.3</v>
       </c>
       <c r="M43">
-        <v>510.4089385</v>
+        <v>522.857937</v>
       </c>
       <c r="N43">
-        <v>18533.8910615</v>
+        <v>18521.442063</v>
       </c>
       <c r="O43">
-        <v>4781.743893867</v>
+        <v>4778.532052254</v>
       </c>
       <c r="P43">
-        <v>13752.147167633</v>
+        <v>13742.910010746</v>
       </c>
       <c r="Q43">
-        <v>14554.647167633</v>
+        <v>14545.410010746</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.0935898363743097</v>
+        <v>0.09427353873000821</v>
       </c>
       <c r="T43">
-        <v>1.103691371231171</v>
+        <v>1.119481263972476</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>37.31184656751461</v>
+        <v>36.42346926828807</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07035414446340477</v>
+        <v>0.07018801946596681</v>
       </c>
       <c r="C44">
-        <v>14643.32480160529</v>
+        <v>14407.00691948959</v>
       </c>
       <c r="D44">
-        <v>24168.11480160529</v>
+        <v>24179.29191948959</v>
       </c>
       <c r="E44">
-        <v>5342.789999999999</v>
+        <v>5590.285</v>
       </c>
       <c r="F44">
-        <v>10394.79</v>
+        <v>10642.285</v>
       </c>
       <c r="G44">
         <v>870</v>
@@ -5008,28 +5008,28 @@
         <v>19044.3</v>
       </c>
       <c r="M44">
-        <v>522.8579369999999</v>
+        <v>535.3069355</v>
       </c>
       <c r="N44">
-        <v>18521.442063</v>
+        <v>18508.9930645</v>
       </c>
       <c r="O44">
-        <v>4778.532052254</v>
+        <v>4775.320210641</v>
       </c>
       <c r="P44">
-        <v>13742.910010746</v>
+        <v>13733.672853859</v>
       </c>
       <c r="Q44">
-        <v>14545.410010746</v>
+        <v>14536.172853859</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09427353873000821</v>
+        <v>0.09498123064204703</v>
       </c>
       <c r="T44">
-        <v>1.119481263972476</v>
+        <v>1.135825188038038</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>36.42346926828807</v>
+        <v>35.57641184344416</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5054,22 +5054,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07018801946596681</v>
+        <v>0.07002189446852884</v>
       </c>
       <c r="C45">
-        <v>14407.00691948959</v>
+        <v>14170.69938040378</v>
       </c>
       <c r="D45">
-        <v>24179.29191948959</v>
+        <v>24190.47938040378</v>
       </c>
       <c r="E45">
-        <v>5590.285</v>
+        <v>5837.780000000001</v>
       </c>
       <c r="F45">
-        <v>10642.285</v>
+        <v>10889.78</v>
       </c>
       <c r="G45">
         <v>870</v>
@@ -5090,28 +5090,28 @@
         <v>19044.3</v>
       </c>
       <c r="M45">
-        <v>535.3069355</v>
+        <v>547.755934</v>
       </c>
       <c r="N45">
-        <v>18508.9930645</v>
+        <v>18496.544066</v>
       </c>
       <c r="O45">
-        <v>4775.320210641</v>
+        <v>4772.108369028</v>
       </c>
       <c r="P45">
-        <v>13733.672853859</v>
+        <v>13724.435696972</v>
       </c>
       <c r="Q45">
-        <v>14536.172853859</v>
+        <v>14526.935696972</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09498123064204703</v>
+        <v>0.09571419726523006</v>
       </c>
       <c r="T45">
-        <v>1.135825188038038</v>
+        <v>1.152752823677369</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>35.57641184344416</v>
+        <v>34.76785702882043</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5136,22 +5136,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07002189446852884</v>
+        <v>0.06985576947109087</v>
       </c>
       <c r="C46">
-        <v>14170.69938040378</v>
+        <v>13934.40219871128</v>
       </c>
       <c r="D46">
-        <v>24190.47938040378</v>
+        <v>24201.67719871128</v>
       </c>
       <c r="E46">
-        <v>5837.780000000001</v>
+        <v>6085.275</v>
       </c>
       <c r="F46">
-        <v>10889.78</v>
+        <v>11137.275</v>
       </c>
       <c r="G46">
         <v>870</v>
@@ -5172,28 +5172,28 @@
         <v>19044.3</v>
       </c>
       <c r="M46">
-        <v>547.755934</v>
+        <v>560.2049324999999</v>
       </c>
       <c r="N46">
-        <v>18496.544066</v>
+        <v>18484.0950675</v>
       </c>
       <c r="O46">
-        <v>4772.108369028</v>
+        <v>4768.896527415</v>
       </c>
       <c r="P46">
-        <v>13724.435696972</v>
+        <v>13715.198540085</v>
       </c>
       <c r="Q46">
-        <v>14526.935696972</v>
+        <v>14517.698540085</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09571419726523006</v>
+        <v>0.09647381722016524</v>
       </c>
       <c r="T46">
-        <v>1.152752823677369</v>
+        <v>1.170296009703585</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>34.76785702882043</v>
+        <v>33.99523798373554</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5218,22 +5218,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06985576947109087</v>
+        <v>0.06968964447365292</v>
       </c>
       <c r="C47">
-        <v>13934.40219871128</v>
+        <v>13698.11538880212</v>
       </c>
       <c r="D47">
-        <v>24201.67719871128</v>
+        <v>24212.88538880212</v>
       </c>
       <c r="E47">
-        <v>6085.275</v>
+        <v>6332.77</v>
       </c>
       <c r="F47">
-        <v>11137.275</v>
+        <v>11384.77</v>
       </c>
       <c r="G47">
         <v>870</v>
@@ -5254,28 +5254,28 @@
         <v>19044.3</v>
       </c>
       <c r="M47">
-        <v>560.2049324999999</v>
+        <v>572.6539309999999</v>
       </c>
       <c r="N47">
-        <v>18484.0950675</v>
+        <v>18471.646069</v>
       </c>
       <c r="O47">
-        <v>4768.896527415</v>
+        <v>4765.684685802</v>
       </c>
       <c r="P47">
-        <v>13715.198540085</v>
+        <v>13705.961383198</v>
       </c>
       <c r="Q47">
-        <v>14517.698540085</v>
+        <v>14508.461383198</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09647381722016524</v>
+        <v>0.0972615712475054</v>
       </c>
       <c r="T47">
-        <v>1.170296009703585</v>
+        <v>1.188488943360402</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>33.99523798373554</v>
+        <v>33.25621107104563</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5300,22 +5300,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06968964447365292</v>
+        <v>0.06952351947621495</v>
       </c>
       <c r="C48">
-        <v>13698.11538880212</v>
+        <v>13461.83896509301</v>
       </c>
       <c r="D48">
-        <v>24212.88538880212</v>
+        <v>24224.10396509301</v>
       </c>
       <c r="E48">
-        <v>6332.77</v>
+        <v>6580.265000000001</v>
       </c>
       <c r="F48">
-        <v>11384.77</v>
+        <v>11632.265</v>
       </c>
       <c r="G48">
         <v>870</v>
@@ -5336,28 +5336,28 @@
         <v>19044.3</v>
       </c>
       <c r="M48">
-        <v>572.6539309999999</v>
+        <v>585.1029295000001</v>
       </c>
       <c r="N48">
-        <v>18471.646069</v>
+        <v>18459.1970705</v>
       </c>
       <c r="O48">
-        <v>4765.684685802</v>
+        <v>4762.472844189</v>
       </c>
       <c r="P48">
-        <v>13705.961383198</v>
+        <v>13696.724226311</v>
       </c>
       <c r="Q48">
-        <v>14508.461383198</v>
+        <v>14499.224226311</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.0972615712475054</v>
+        <v>0.098079051841915</v>
       </c>
       <c r="T48">
-        <v>1.188488943360402</v>
+        <v>1.207368402815589</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>33.25621107104563</v>
+        <v>32.5486321120872</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5382,22 +5382,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06952351947621495</v>
+        <v>0.06935739447877699</v>
       </c>
       <c r="C49">
-        <v>13461.83896509301</v>
+        <v>13225.57294202736</v>
       </c>
       <c r="D49">
-        <v>24224.10396509301</v>
+        <v>24235.33294202736</v>
       </c>
       <c r="E49">
-        <v>6580.265000000001</v>
+        <v>6827.76</v>
       </c>
       <c r="F49">
-        <v>11632.265</v>
+        <v>11879.76</v>
       </c>
       <c r="G49">
         <v>870</v>
@@ -5418,28 +5418,28 @@
         <v>19044.3</v>
       </c>
       <c r="M49">
-        <v>585.1029295000001</v>
+        <v>597.551928</v>
       </c>
       <c r="N49">
-        <v>18459.1970705</v>
+        <v>18446.748072</v>
       </c>
       <c r="O49">
-        <v>4762.472844189</v>
+        <v>4759.261002576</v>
       </c>
       <c r="P49">
-        <v>13696.724226311</v>
+        <v>13687.487069424</v>
       </c>
       <c r="Q49">
-        <v>14499.224226311</v>
+        <v>14489.987069424</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.098079051841915</v>
+        <v>0.09892797399764806</v>
       </c>
       <c r="T49">
-        <v>1.207368402815589</v>
+        <v>1.226973995326745</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>32.5486321120872</v>
+        <v>31.87053560975206</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5464,22 +5464,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06935739447877698</v>
+        <v>0.06919126948133902</v>
       </c>
       <c r="C50">
-        <v>13225.57294202736</v>
+        <v>12989.31733407542</v>
       </c>
       <c r="D50">
-        <v>24235.33294202736</v>
+        <v>24246.57233407542</v>
       </c>
       <c r="E50">
-        <v>6827.76</v>
+        <v>7075.254999999999</v>
       </c>
       <c r="F50">
-        <v>11879.76</v>
+        <v>12127.255</v>
       </c>
       <c r="G50">
         <v>870</v>
@@ -5500,28 +5500,28 @@
         <v>19044.3</v>
       </c>
       <c r="M50">
-        <v>597.551928</v>
+        <v>610.0009264999999</v>
       </c>
       <c r="N50">
-        <v>18446.748072</v>
+        <v>18434.2990735</v>
       </c>
       <c r="O50">
-        <v>4759.261002576</v>
+        <v>4756.049160963</v>
       </c>
       <c r="P50">
-        <v>13687.487069424</v>
+        <v>13678.249912537</v>
       </c>
       <c r="Q50">
-        <v>14489.987069424</v>
+        <v>14480.749912537</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09892797399764805</v>
+        <v>0.09981018721831182</v>
       </c>
       <c r="T50">
-        <v>1.226973995326745</v>
+        <v>1.247348434603045</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>31.87053560975206</v>
+        <v>31.22011651567549</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5546,22 +5546,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06919126948133902</v>
+        <v>0.06902514448390107</v>
       </c>
       <c r="C51">
-        <v>12989.31733407542</v>
+        <v>12753.07215573425</v>
       </c>
       <c r="D51">
-        <v>24246.57233407542</v>
+        <v>24257.82215573425</v>
       </c>
       <c r="E51">
-        <v>7075.254999999999</v>
+        <v>7322.75</v>
       </c>
       <c r="F51">
-        <v>12127.255</v>
+        <v>12374.75</v>
       </c>
       <c r="G51">
         <v>870</v>
@@ -5582,28 +5582,28 @@
         <v>19044.3</v>
       </c>
       <c r="M51">
-        <v>610.0009264999999</v>
+        <v>622.449925</v>
       </c>
       <c r="N51">
-        <v>18434.2990735</v>
+        <v>18421.850075</v>
       </c>
       <c r="O51">
-        <v>4756.049160963</v>
+        <v>4752.83731935</v>
       </c>
       <c r="P51">
-        <v>13678.249912537</v>
+        <v>13669.01275565</v>
       </c>
       <c r="Q51">
-        <v>14480.749912537</v>
+        <v>14471.51275565</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09981018721831182</v>
+        <v>0.1007276889678021</v>
       </c>
       <c r="T51">
-        <v>1.247348434603045</v>
+        <v>1.268537851450396</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>31.22011651567549</v>
+        <v>30.59571418536198</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5628,22 +5628,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06902514448390107</v>
+        <v>0.0688590194864631</v>
       </c>
       <c r="C52">
-        <v>12753.07215573425</v>
+        <v>12516.83742152786</v>
       </c>
       <c r="D52">
-        <v>24257.82215573425</v>
+        <v>24269.08242152786</v>
       </c>
       <c r="E52">
-        <v>7322.75</v>
+        <v>7570.245000000001</v>
       </c>
       <c r="F52">
-        <v>12374.75</v>
+        <v>12622.245</v>
       </c>
       <c r="G52">
         <v>870</v>
@@ -5664,28 +5664,28 @@
         <v>19044.3</v>
       </c>
       <c r="M52">
-        <v>622.449925</v>
+        <v>634.8989235</v>
       </c>
       <c r="N52">
-        <v>18421.850075</v>
+        <v>18409.4010765</v>
       </c>
       <c r="O52">
-        <v>4752.83731935</v>
+        <v>4749.625477737</v>
       </c>
       <c r="P52">
-        <v>13669.01275565</v>
+        <v>13659.775598763</v>
       </c>
       <c r="Q52">
-        <v>14471.51275565</v>
+        <v>14462.275598763</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1007276889678021</v>
+        <v>0.101682639768292</v>
       </c>
       <c r="T52">
-        <v>1.268537851450396</v>
+        <v>1.290592142454782</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>30.59571418536198</v>
+        <v>29.99579822094311</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5710,22 +5710,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0688590194864631</v>
+        <v>0.06869289448902513</v>
       </c>
       <c r="C53">
-        <v>12516.83742152786</v>
+        <v>12280.61314600724</v>
       </c>
       <c r="D53">
-        <v>24269.08242152786</v>
+        <v>24280.35314600724</v>
       </c>
       <c r="E53">
-        <v>7570.245000000001</v>
+        <v>7817.74</v>
       </c>
       <c r="F53">
-        <v>12622.245</v>
+        <v>12869.74</v>
       </c>
       <c r="G53">
         <v>870</v>
@@ -5746,28 +5746,28 @@
         <v>19044.3</v>
       </c>
       <c r="M53">
-        <v>634.8989235</v>
+        <v>647.3479219999999</v>
       </c>
       <c r="N53">
-        <v>18409.4010765</v>
+        <v>18396.952078</v>
       </c>
       <c r="O53">
-        <v>4749.625477737</v>
+        <v>4746.413636124</v>
       </c>
       <c r="P53">
-        <v>13659.775598763</v>
+        <v>13650.538441876</v>
       </c>
       <c r="Q53">
-        <v>14462.275598763</v>
+        <v>14453.038441876</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.101682639768292</v>
+        <v>0.102677380185469</v>
       </c>
       <c r="T53">
-        <v>1.290592142454782</v>
+        <v>1.313565362251017</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>29.99579822094311</v>
+        <v>29.41895594746344</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5792,22 +5792,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06869289448902513</v>
+        <v>0.06852676949158718</v>
       </c>
       <c r="C54">
-        <v>12280.61314600724</v>
+        <v>12044.39934375038</v>
       </c>
       <c r="D54">
-        <v>24280.35314600724</v>
+        <v>24291.63434375038</v>
       </c>
       <c r="E54">
-        <v>7817.74</v>
+        <v>8065.235000000001</v>
       </c>
       <c r="F54">
-        <v>12869.74</v>
+        <v>13117.235</v>
       </c>
       <c r="G54">
         <v>870</v>
@@ -5828,28 +5828,28 @@
         <v>19044.3</v>
       </c>
       <c r="M54">
-        <v>647.3479219999999</v>
+        <v>659.7969204999999</v>
       </c>
       <c r="N54">
-        <v>18396.952078</v>
+        <v>18384.5030795</v>
       </c>
       <c r="O54">
-        <v>4746.413636124</v>
+        <v>4743.201794511</v>
       </c>
       <c r="P54">
-        <v>13650.538441876</v>
+        <v>13641.301284989</v>
       </c>
       <c r="Q54">
-        <v>14453.038441876</v>
+        <v>14443.801284989</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.102677380185469</v>
+        <v>0.1037144499821004</v>
       </c>
       <c r="T54">
-        <v>1.313565362251017</v>
+        <v>1.33751616586837</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>29.41895594746344</v>
+        <v>28.86388130694526</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5874,22 +5874,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06852676949158718</v>
+        <v>0.06836064449414922</v>
       </c>
       <c r="C55">
-        <v>12044.39934375038</v>
+        <v>11808.19602936243</v>
       </c>
       <c r="D55">
-        <v>24291.63434375038</v>
+        <v>24302.92602936243</v>
       </c>
       <c r="E55">
-        <v>8065.235000000001</v>
+        <v>8312.730000000001</v>
       </c>
       <c r="F55">
-        <v>13117.235</v>
+        <v>13364.73</v>
       </c>
       <c r="G55">
         <v>870</v>
@@ -5910,28 +5910,28 @@
         <v>19044.3</v>
       </c>
       <c r="M55">
-        <v>659.7969204999999</v>
+        <v>672.2459190000001</v>
       </c>
       <c r="N55">
-        <v>18384.5030795</v>
+        <v>18372.054081</v>
       </c>
       <c r="O55">
-        <v>4743.201794511</v>
+        <v>4739.989952898</v>
       </c>
       <c r="P55">
-        <v>13641.301284989</v>
+        <v>13632.064128102</v>
       </c>
       <c r="Q55">
-        <v>14443.801284989</v>
+        <v>14434.564128102</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1037144499821004</v>
+        <v>0.1047966097698896</v>
       </c>
       <c r="T55">
-        <v>1.33751616586837</v>
+        <v>1.362508308773432</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>28.86388130694526</v>
+        <v>28.32936498644627</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5956,22 +5956,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06836064449414922</v>
+        <v>0.06819451949671125</v>
       </c>
       <c r="C56">
-        <v>11808.19602936243</v>
+        <v>11572.00321747569</v>
       </c>
       <c r="D56">
-        <v>24302.92602936243</v>
+        <v>24314.22821747569</v>
       </c>
       <c r="E56">
-        <v>8312.730000000001</v>
+        <v>8560.225</v>
       </c>
       <c r="F56">
-        <v>13364.73</v>
+        <v>13612.225</v>
       </c>
       <c r="G56">
         <v>870</v>
@@ -5992,28 +5992,28 @@
         <v>19044.3</v>
       </c>
       <c r="M56">
-        <v>672.2459190000001</v>
+        <v>684.6949175</v>
       </c>
       <c r="N56">
-        <v>18372.054081</v>
+        <v>18359.6050825</v>
       </c>
       <c r="O56">
-        <v>4739.989952898</v>
+        <v>4736.778111285</v>
       </c>
       <c r="P56">
-        <v>13632.064128102</v>
+        <v>13622.826971215</v>
       </c>
       <c r="Q56">
-        <v>14434.564128102</v>
+        <v>14425.326971215</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1047966097698896</v>
+        <v>0.1059268655482472</v>
       </c>
       <c r="T56">
-        <v>1.362508308773432</v>
+        <v>1.388611213585387</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>28.32936498644627</v>
+        <v>27.81428562305634</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6038,22 +6038,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06819451949671125</v>
+        <v>0.0680283944992733</v>
       </c>
       <c r="C57">
-        <v>11572.00321747569</v>
+        <v>11335.82092274967</v>
       </c>
       <c r="D57">
-        <v>24314.22821747569</v>
+        <v>24325.54092274967</v>
       </c>
       <c r="E57">
-        <v>8560.225</v>
+        <v>8807.720000000001</v>
       </c>
       <c r="F57">
-        <v>13612.225</v>
+        <v>13859.72</v>
       </c>
       <c r="G57">
         <v>870</v>
@@ -6074,28 +6074,28 @@
         <v>19044.3</v>
       </c>
       <c r="M57">
-        <v>684.6949175</v>
+        <v>697.143916</v>
       </c>
       <c r="N57">
-        <v>18359.6050825</v>
+        <v>18347.156084</v>
       </c>
       <c r="O57">
-        <v>4736.778111285</v>
+        <v>4733.566269672</v>
       </c>
       <c r="P57">
-        <v>13622.826971215</v>
+        <v>13613.589814328</v>
       </c>
       <c r="Q57">
-        <v>14425.326971215</v>
+        <v>14416.089814328</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1059268655482472</v>
+        <v>0.1071084965892575</v>
       </c>
       <c r="T57">
-        <v>1.388611213585387</v>
+        <v>1.415900614070612</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>27.81428562305634</v>
+        <v>27.31760195121605</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6120,22 +6120,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0680283944992733</v>
+        <v>0.06786226950183533</v>
       </c>
       <c r="C58">
-        <v>11335.82092274967</v>
+        <v>11099.6491598712</v>
       </c>
       <c r="D58">
-        <v>24325.54092274967</v>
+        <v>24336.8641598712</v>
       </c>
       <c r="E58">
-        <v>8807.720000000001</v>
+        <v>9055.215000000002</v>
       </c>
       <c r="F58">
-        <v>13859.72</v>
+        <v>14107.215</v>
       </c>
       <c r="G58">
         <v>870</v>
@@ -6156,28 +6156,28 @@
         <v>19044.3</v>
       </c>
       <c r="M58">
-        <v>697.143916</v>
+        <v>709.5929145000001</v>
       </c>
       <c r="N58">
-        <v>18347.156084</v>
+        <v>18334.7070855</v>
       </c>
       <c r="O58">
-        <v>4733.566269672</v>
+        <v>4730.354428058999</v>
       </c>
       <c r="P58">
-        <v>13613.589814328</v>
+        <v>13604.352657441</v>
       </c>
       <c r="Q58">
-        <v>14416.089814328</v>
+        <v>14406.852657441</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1071084965892575</v>
+        <v>0.1083450872135706</v>
       </c>
       <c r="T58">
-        <v>1.415900614070612</v>
+        <v>1.444459288997011</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>27.31760195121605</v>
+        <v>26.83834577663331</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6202,22 +6202,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06786226950183533</v>
+        <v>0.06769614450439736</v>
       </c>
       <c r="C59">
-        <v>11099.6491598712</v>
+        <v>10863.48794355447</v>
       </c>
       <c r="D59">
-        <v>24336.8641598712</v>
+        <v>24348.19794355447</v>
       </c>
       <c r="E59">
-        <v>9055.215000000002</v>
+        <v>9302.710000000001</v>
       </c>
       <c r="F59">
-        <v>14107.215</v>
+        <v>14354.71</v>
       </c>
       <c r="G59">
         <v>870</v>
@@ -6238,28 +6238,28 @@
         <v>19044.3</v>
       </c>
       <c r="M59">
-        <v>709.5929145000001</v>
+        <v>722.041913</v>
       </c>
       <c r="N59">
-        <v>18334.7070855</v>
+        <v>18322.258087</v>
       </c>
       <c r="O59">
-        <v>4730.354428058999</v>
+        <v>4727.142586446</v>
       </c>
       <c r="P59">
-        <v>13604.352657441</v>
+        <v>13595.115500554</v>
       </c>
       <c r="Q59">
-        <v>14406.852657441</v>
+        <v>14397.615500554</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1083450872135706</v>
+        <v>0.109640563105708</v>
       </c>
       <c r="T59">
-        <v>1.444459288997011</v>
+        <v>1.474377900824666</v>
       </c>
       <c r="U59">
         <v>0.0503</v>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>26.83834577663331</v>
+        <v>26.37561567703619</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6284,22 +6284,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.06769614450439737</v>
+        <v>0.0675300195069594</v>
       </c>
       <c r="C60">
-        <v>10863.48794355447</v>
+        <v>10627.33728854107</v>
       </c>
       <c r="D60">
-        <v>24348.19794355447</v>
+        <v>24359.54228854107</v>
       </c>
       <c r="E60">
-        <v>9302.709999999999</v>
+        <v>9550.205</v>
       </c>
       <c r="F60">
-        <v>14354.71</v>
+        <v>14602.205</v>
       </c>
       <c r="G60">
         <v>870</v>
@@ -6320,28 +6320,28 @@
         <v>19044.3</v>
       </c>
       <c r="M60">
-        <v>722.0419129999999</v>
+        <v>734.4909114999999</v>
       </c>
       <c r="N60">
-        <v>18322.258087</v>
+        <v>18309.8090885</v>
       </c>
       <c r="O60">
-        <v>4727.142586446</v>
+        <v>4723.930744833</v>
       </c>
       <c r="P60">
-        <v>13595.115500554</v>
+        <v>13585.878343667</v>
       </c>
       <c r="Q60">
-        <v>14397.615500554</v>
+        <v>14388.378343667</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.109640563105708</v>
+        <v>0.1109992329438034</v>
       </c>
       <c r="T60">
-        <v>1.474377900824666</v>
+        <v>1.505755957131719</v>
       </c>
       <c r="U60">
         <v>0.0503</v>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>26.37561567703619</v>
+        <v>25.9285713435271</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6366,22 +6366,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0675300195069594</v>
+        <v>0.06736389450952143</v>
       </c>
       <c r="C61">
-        <v>10627.33728854107</v>
+        <v>10391.19720960011</v>
       </c>
       <c r="D61">
-        <v>24359.54228854107</v>
+        <v>24370.89720960011</v>
       </c>
       <c r="E61">
-        <v>9550.205</v>
+        <v>9797.699999999999</v>
       </c>
       <c r="F61">
-        <v>14602.205</v>
+        <v>14849.7</v>
       </c>
       <c r="G61">
         <v>870</v>
@@ -6402,28 +6402,28 @@
         <v>19044.3</v>
       </c>
       <c r="M61">
-        <v>734.4909114999999</v>
+        <v>746.9399099999999</v>
       </c>
       <c r="N61">
-        <v>18309.8090885</v>
+        <v>18297.36009</v>
       </c>
       <c r="O61">
-        <v>4723.930744833</v>
+        <v>4720.718903219999</v>
       </c>
       <c r="P61">
-        <v>13585.878343667</v>
+        <v>13576.64118678</v>
       </c>
       <c r="Q61">
-        <v>14388.378343667</v>
+        <v>14379.14118678</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1109992329438034</v>
+        <v>0.1124258362738036</v>
       </c>
       <c r="T61">
-        <v>1.505755957131719</v>
+        <v>1.538702916254125</v>
       </c>
       <c r="U61">
         <v>0.0503</v>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>25.9285713435271</v>
+        <v>25.49642848780165</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6448,22 +6448,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.06736389450952143</v>
+        <v>0.06719776951208348</v>
       </c>
       <c r="C62">
-        <v>10391.19720960011</v>
+        <v>10155.06772152821</v>
       </c>
       <c r="D62">
-        <v>24370.89720960011</v>
+        <v>24382.26272152821</v>
       </c>
       <c r="E62">
-        <v>9797.699999999999</v>
+        <v>10045.195</v>
       </c>
       <c r="F62">
-        <v>14849.7</v>
+        <v>15097.195</v>
       </c>
       <c r="G62">
         <v>870</v>
@@ -6484,28 +6484,28 @@
         <v>19044.3</v>
       </c>
       <c r="M62">
-        <v>746.9399099999999</v>
+        <v>759.3889085</v>
       </c>
       <c r="N62">
-        <v>18297.36009</v>
+        <v>18284.9110915</v>
       </c>
       <c r="O62">
-        <v>4720.718903219999</v>
+        <v>4717.507061607</v>
       </c>
       <c r="P62">
-        <v>13576.64118678</v>
+        <v>13567.404029893</v>
       </c>
       <c r="Q62">
-        <v>14379.14118678</v>
+        <v>14369.904029893</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1124258362738036</v>
+        <v>0.113925598748932</v>
       </c>
       <c r="T62">
-        <v>1.538702916254125</v>
+        <v>1.573339463023834</v>
       </c>
       <c r="U62">
         <v>0.0503</v>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>25.49642848780165</v>
+        <v>25.0784542502967</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6530,22 +6530,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.06719776951208348</v>
+        <v>0.06703164451464552</v>
       </c>
       <c r="C63">
-        <v>10155.06772152821</v>
+        <v>9918.948839149643</v>
       </c>
       <c r="D63">
-        <v>24382.26272152821</v>
+        <v>24393.63883914964</v>
       </c>
       <c r="E63">
-        <v>10045.195</v>
+        <v>10292.69</v>
       </c>
       <c r="F63">
-        <v>15097.195</v>
+        <v>15344.69</v>
       </c>
       <c r="G63">
         <v>870</v>
@@ -6566,28 +6566,28 @@
         <v>19044.3</v>
       </c>
       <c r="M63">
-        <v>759.3889085</v>
+        <v>771.837907</v>
       </c>
       <c r="N63">
-        <v>18284.9110915</v>
+        <v>18272.462093</v>
       </c>
       <c r="O63">
-        <v>4717.507061607</v>
+        <v>4714.295219994</v>
       </c>
       <c r="P63">
-        <v>13567.404029893</v>
+        <v>13558.166873006</v>
       </c>
       <c r="Q63">
-        <v>14369.904029893</v>
+        <v>14360.666873006</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.113925598748932</v>
+        <v>0.1155042960911724</v>
       </c>
       <c r="T63">
-        <v>1.573339463023834</v>
+        <v>1.609798985939318</v>
       </c>
       <c r="U63">
         <v>0.0503</v>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>25.0784542502967</v>
+        <v>24.67396305271127</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6612,22 +6612,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.06703164451464552</v>
+        <v>0.06686551951720757</v>
       </c>
       <c r="C64">
-        <v>9918.948839149643</v>
+        <v>9682.840577316338</v>
       </c>
       <c r="D64">
-        <v>24393.63883914964</v>
+        <v>24405.02557731634</v>
       </c>
       <c r="E64">
-        <v>10292.69</v>
+        <v>10540.185</v>
       </c>
       <c r="F64">
-        <v>15344.69</v>
+        <v>15592.185</v>
       </c>
       <c r="G64">
         <v>870</v>
@@ -6648,28 +6648,28 @@
         <v>19044.3</v>
       </c>
       <c r="M64">
-        <v>771.837907</v>
+        <v>784.2869055</v>
       </c>
       <c r="N64">
-        <v>18272.462093</v>
+        <v>18260.0130945</v>
       </c>
       <c r="O64">
-        <v>4714.295219994</v>
+        <v>4711.083378380999</v>
       </c>
       <c r="P64">
-        <v>13558.166873006</v>
+        <v>13548.929716119</v>
       </c>
       <c r="Q64">
-        <v>14360.666873006</v>
+        <v>14351.429716119</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1155042960911724</v>
+        <v>0.1171683284248853</v>
       </c>
       <c r="T64">
-        <v>1.609798985939318</v>
+        <v>1.648229293877259</v>
       </c>
       <c r="U64">
         <v>0.0503</v>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>24.67396305271127</v>
+        <v>24.28231284552538</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6694,22 +6694,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.06686551951720757</v>
+        <v>0.0666993945197696</v>
       </c>
       <c r="C65">
-        <v>9682.840577316338</v>
+        <v>9446.74295090797</v>
       </c>
       <c r="D65">
-        <v>24405.02557731634</v>
+        <v>24416.42295090797</v>
       </c>
       <c r="E65">
-        <v>10540.185</v>
+        <v>10787.68</v>
       </c>
       <c r="F65">
-        <v>15592.185</v>
+        <v>15839.68</v>
       </c>
       <c r="G65">
         <v>870</v>
@@ -6730,28 +6730,28 @@
         <v>19044.3</v>
       </c>
       <c r="M65">
-        <v>784.2869055</v>
+        <v>796.735904</v>
       </c>
       <c r="N65">
-        <v>18260.0130945</v>
+        <v>18247.564096</v>
       </c>
       <c r="O65">
-        <v>4711.083378380999</v>
+        <v>4707.871536768</v>
       </c>
       <c r="P65">
-        <v>13548.929716119</v>
+        <v>13539.692559232</v>
       </c>
       <c r="Q65">
-        <v>14351.429716119</v>
+        <v>14342.192559232</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1171683284248853</v>
+        <v>0.11892480699936</v>
       </c>
       <c r="T65">
-        <v>1.648229293877259</v>
+        <v>1.688794618922864</v>
       </c>
       <c r="U65">
         <v>0.0503</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>24.28231284552538</v>
+        <v>23.90290170731404</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6776,22 +6776,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0666993945197696</v>
+        <v>0.06653326952233164</v>
       </c>
       <c r="C66">
-        <v>9446.74295090797</v>
+        <v>9210.655974832041</v>
       </c>
       <c r="D66">
-        <v>24416.42295090797</v>
+        <v>24427.83097483204</v>
       </c>
       <c r="E66">
-        <v>10787.68</v>
+        <v>11035.175</v>
       </c>
       <c r="F66">
-        <v>15839.68</v>
+        <v>16087.175</v>
       </c>
       <c r="G66">
         <v>870</v>
@@ -6812,28 +6812,28 @@
         <v>19044.3</v>
       </c>
       <c r="M66">
-        <v>796.735904</v>
+        <v>809.1849025</v>
       </c>
       <c r="N66">
-        <v>18247.564096</v>
+        <v>18235.1150975</v>
       </c>
       <c r="O66">
-        <v>4707.871536768</v>
+        <v>4704.659695155</v>
       </c>
       <c r="P66">
-        <v>13539.692559232</v>
+        <v>13530.455402345</v>
       </c>
       <c r="Q66">
-        <v>14342.192559232</v>
+        <v>14332.955402345</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.11892480699936</v>
+        <v>0.1207816557780904</v>
       </c>
       <c r="T66">
-        <v>1.688794618922864</v>
+        <v>1.731677962542504</v>
       </c>
       <c r="U66">
         <v>0.0503</v>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>23.90290170731404</v>
+        <v>23.53516475797075</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6858,22 +6858,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.06653326952233164</v>
+        <v>0.06636714452489367</v>
       </c>
       <c r="C67">
-        <v>9210.655974832041</v>
+        <v>8974.5796640239</v>
       </c>
       <c r="D67">
-        <v>24427.83097483204</v>
+        <v>24439.2496640239</v>
       </c>
       <c r="E67">
-        <v>11035.175</v>
+        <v>11282.67</v>
       </c>
       <c r="F67">
-        <v>16087.175</v>
+        <v>16334.67</v>
       </c>
       <c r="G67">
         <v>870</v>
@@ -6894,28 +6894,28 @@
         <v>19044.3</v>
       </c>
       <c r="M67">
-        <v>809.1849025</v>
+        <v>821.6339009999999</v>
       </c>
       <c r="N67">
-        <v>18235.1150975</v>
+        <v>18222.666099</v>
       </c>
       <c r="O67">
-        <v>4704.659695155</v>
+        <v>4701.447853541999</v>
       </c>
       <c r="P67">
-        <v>13530.455402345</v>
+        <v>13521.218245458</v>
       </c>
       <c r="Q67">
-        <v>14332.955402345</v>
+        <v>14323.718245458</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1207816557780904</v>
+        <v>0.1227477309555697</v>
       </c>
       <c r="T67">
-        <v>1.731677962542504</v>
+        <v>1.777083855786828</v>
       </c>
       <c r="U67">
         <v>0.0503</v>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>23.53516475797075</v>
+        <v>23.17857135254695</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6940,22 +6940,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.06636714452489367</v>
+        <v>0.06620101952745572</v>
       </c>
       <c r="C68">
-        <v>8974.5796640239</v>
+        <v>8738.514033446856</v>
       </c>
       <c r="D68">
-        <v>24439.2496640239</v>
+        <v>24450.67903344686</v>
       </c>
       <c r="E68">
-        <v>11282.67</v>
+        <v>11530.165</v>
       </c>
       <c r="F68">
-        <v>16334.67</v>
+        <v>16582.165</v>
       </c>
       <c r="G68">
         <v>870</v>
@@ -6976,28 +6976,28 @@
         <v>19044.3</v>
       </c>
       <c r="M68">
-        <v>821.6339009999999</v>
+        <v>834.0828995000001</v>
       </c>
       <c r="N68">
-        <v>18222.666099</v>
+        <v>18210.2171005</v>
       </c>
       <c r="O68">
-        <v>4701.447853541999</v>
+        <v>4698.236011929</v>
       </c>
       <c r="P68">
-        <v>13521.218245458</v>
+        <v>13511.981088571</v>
       </c>
       <c r="Q68">
-        <v>14323.718245458</v>
+        <v>14314.481088571</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1227477309555697</v>
+        <v>0.1248329622044113</v>
       </c>
       <c r="T68">
-        <v>1.777083855786828</v>
+        <v>1.825241621348991</v>
       </c>
       <c r="U68">
         <v>0.0503</v>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>23.17857135254695</v>
+        <v>22.83262252638953</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7022,22 +7022,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.06620101952745572</v>
+        <v>0.06603489453001775</v>
       </c>
       <c r="C69">
-        <v>8738.514033446856</v>
+        <v>8502.459098092218</v>
       </c>
       <c r="D69">
-        <v>24450.67903344686</v>
+        <v>24462.11909809222</v>
       </c>
       <c r="E69">
-        <v>11530.165</v>
+        <v>11777.66</v>
       </c>
       <c r="F69">
-        <v>16582.165</v>
+        <v>16829.66</v>
       </c>
       <c r="G69">
         <v>870</v>
@@ -7058,28 +7058,28 @@
         <v>19044.3</v>
       </c>
       <c r="M69">
-        <v>834.0828995000001</v>
+        <v>846.531898</v>
       </c>
       <c r="N69">
-        <v>18210.2171005</v>
+        <v>18197.768102</v>
       </c>
       <c r="O69">
-        <v>4698.236011929</v>
+        <v>4695.024170316</v>
       </c>
       <c r="P69">
-        <v>13511.981088571</v>
+        <v>13502.743931684</v>
       </c>
       <c r="Q69">
-        <v>14314.481088571</v>
+        <v>14305.243931684</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1248329622044113</v>
+        <v>0.1270485204063055</v>
       </c>
       <c r="T69">
-        <v>1.825241621348991</v>
+        <v>1.876409247258788</v>
       </c>
       <c r="U69">
         <v>0.0503</v>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>22.83262252638953</v>
+        <v>22.49684866570734</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7104,22 +7104,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.06603489453001775</v>
+        <v>0.06586876953257979</v>
       </c>
       <c r="C70">
-        <v>8502.459098092218</v>
+        <v>8266.414872979349</v>
       </c>
       <c r="D70">
-        <v>24462.11909809222</v>
+        <v>24473.56987297935</v>
       </c>
       <c r="E70">
-        <v>11777.66</v>
+        <v>12025.155</v>
       </c>
       <c r="F70">
-        <v>16829.66</v>
+        <v>17077.155</v>
       </c>
       <c r="G70">
         <v>870</v>
@@ -7140,28 +7140,28 @@
         <v>19044.3</v>
       </c>
       <c r="M70">
-        <v>846.531898</v>
+        <v>858.9808965000001</v>
       </c>
       <c r="N70">
-        <v>18197.768102</v>
+        <v>18185.3191035</v>
       </c>
       <c r="O70">
-        <v>4695.024170316</v>
+        <v>4691.812328702999</v>
       </c>
       <c r="P70">
-        <v>13502.743931684</v>
+        <v>13493.506774797</v>
       </c>
       <c r="Q70">
-        <v>14305.243931684</v>
+        <v>14296.006774797</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1270485204063055</v>
+        <v>0.1294070178470316</v>
       </c>
       <c r="T70">
-        <v>1.876409247258788</v>
+        <v>1.930878010324056</v>
       </c>
       <c r="U70">
         <v>0.0503</v>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>22.49684866570734</v>
+        <v>22.17080738069708</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7186,22 +7186,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.06586876953257979</v>
+        <v>0.06570264453514182</v>
       </c>
       <c r="C71">
-        <v>8266.414872979349</v>
+        <v>8030.381373155768</v>
       </c>
       <c r="D71">
-        <v>24473.56987297935</v>
+        <v>24485.03137315577</v>
       </c>
       <c r="E71">
-        <v>12025.155</v>
+        <v>12272.65</v>
       </c>
       <c r="F71">
-        <v>17077.155</v>
+        <v>17324.65</v>
       </c>
       <c r="G71">
         <v>870</v>
@@ -7222,28 +7222,28 @@
         <v>19044.3</v>
       </c>
       <c r="M71">
-        <v>858.9808965000001</v>
+        <v>871.429895</v>
       </c>
       <c r="N71">
-        <v>18185.3191035</v>
+        <v>18172.870105</v>
       </c>
       <c r="O71">
-        <v>4691.812328702999</v>
+        <v>4688.60048709</v>
       </c>
       <c r="P71">
-        <v>13493.506774797</v>
+        <v>13484.26961791</v>
       </c>
       <c r="Q71">
-        <v>14296.006774797</v>
+        <v>14286.76961791</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1294070178470316</v>
+        <v>0.1319227484504728</v>
       </c>
       <c r="T71">
-        <v>1.930878010324056</v>
+        <v>1.988978024260342</v>
       </c>
       <c r="U71">
         <v>0.0503</v>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>22.17080738069708</v>
+        <v>21.85408156097284</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7268,22 +7268,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.06570264453514182</v>
+        <v>0.06553651953770387</v>
       </c>
       <c r="C72">
-        <v>8030.381373155768</v>
+        <v>7794.35861369719</v>
       </c>
       <c r="D72">
-        <v>24485.03137315577</v>
+        <v>24496.50361369719</v>
       </c>
       <c r="E72">
-        <v>12272.65</v>
+        <v>12520.145</v>
       </c>
       <c r="F72">
-        <v>17324.65</v>
+        <v>17572.145</v>
       </c>
       <c r="G72">
         <v>870</v>
@@ -7304,28 +7304,28 @@
         <v>19044.3</v>
       </c>
       <c r="M72">
-        <v>871.429895</v>
+        <v>883.8788935</v>
       </c>
       <c r="N72">
-        <v>18172.870105</v>
+        <v>18160.4211065</v>
       </c>
       <c r="O72">
-        <v>4688.60048709</v>
+        <v>4685.388645477</v>
       </c>
       <c r="P72">
-        <v>13484.26961791</v>
+        <v>13475.032461023</v>
       </c>
       <c r="Q72">
-        <v>14286.76961791</v>
+        <v>14277.532461023</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1319227484504728</v>
+        <v>0.1346119777162202</v>
       </c>
       <c r="T72">
-        <v>1.988978024260342</v>
+        <v>2.051084935709475</v>
       </c>
       <c r="U72">
         <v>0.0503</v>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>21.85408156097284</v>
+        <v>21.54627759532534</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7350,22 +7350,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.06553651953770387</v>
+        <v>0.06537039454026589</v>
       </c>
       <c r="C73">
-        <v>7794.35861369719</v>
+        <v>7558.346609707591</v>
       </c>
       <c r="D73">
-        <v>24496.50361369719</v>
+        <v>24507.98660970759</v>
       </c>
       <c r="E73">
-        <v>12520.145</v>
+        <v>12767.64</v>
       </c>
       <c r="F73">
-        <v>17572.145</v>
+        <v>17819.64</v>
       </c>
       <c r="G73">
         <v>870</v>
@@ -7386,28 +7386,28 @@
         <v>19044.3</v>
       </c>
       <c r="M73">
-        <v>883.8788935</v>
+        <v>896.3278919999999</v>
       </c>
       <c r="N73">
-        <v>18160.4211065</v>
+        <v>18147.972108</v>
       </c>
       <c r="O73">
-        <v>4685.388645477</v>
+        <v>4682.176803863999</v>
       </c>
       <c r="P73">
-        <v>13475.032461023</v>
+        <v>13465.795304136</v>
       </c>
       <c r="Q73">
-        <v>14277.532461023</v>
+        <v>14268.295304136</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1346119777162202</v>
+        <v>0.1374932947866639</v>
       </c>
       <c r="T73">
-        <v>2.051084935709475</v>
+        <v>2.11762805511926</v>
       </c>
       <c r="U73">
         <v>0.0503</v>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>21.54627759532534</v>
+        <v>21.24702373983471</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7432,22 +7432,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.06537039454026589</v>
+        <v>0.06520426954282794</v>
       </c>
       <c r="C74">
-        <v>7558.346609707591</v>
+        <v>7322.345376319288</v>
       </c>
       <c r="D74">
-        <v>24507.98660970759</v>
+        <v>24519.48037631929</v>
       </c>
       <c r="E74">
-        <v>12767.64</v>
+        <v>13015.135</v>
       </c>
       <c r="F74">
-        <v>17819.64</v>
+        <v>18067.135</v>
       </c>
       <c r="G74">
         <v>870</v>
@@ -7468,28 +7468,28 @@
         <v>19044.3</v>
       </c>
       <c r="M74">
-        <v>896.3278919999999</v>
+        <v>908.7768904999999</v>
       </c>
       <c r="N74">
-        <v>18147.972108</v>
+        <v>18135.5231095</v>
       </c>
       <c r="O74">
-        <v>4682.176803863999</v>
+        <v>4678.964962251</v>
       </c>
       <c r="P74">
-        <v>13465.795304136</v>
+        <v>13456.558147249</v>
       </c>
       <c r="Q74">
-        <v>14268.295304136</v>
+        <v>14259.058147249</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1374932947866639</v>
+        <v>0.1405880427512146</v>
       </c>
       <c r="T74">
-        <v>2.11762805511926</v>
+        <v>2.189100294485326</v>
       </c>
       <c r="U74">
         <v>0.0503</v>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>21.24702373983471</v>
+        <v>20.95596862011094</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7514,22 +7514,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.06520426954282794</v>
+        <v>0.06503814454538998</v>
       </c>
       <c r="C75">
-        <v>7322.345376319288</v>
+        <v>7086.354928692988</v>
       </c>
       <c r="D75">
-        <v>24519.48037631929</v>
+        <v>24530.98492869299</v>
       </c>
       <c r="E75">
-        <v>13015.135</v>
+        <v>13262.63</v>
       </c>
       <c r="F75">
-        <v>18067.135</v>
+        <v>18314.63</v>
       </c>
       <c r="G75">
         <v>870</v>
@@ -7550,28 +7550,28 @@
         <v>19044.3</v>
       </c>
       <c r="M75">
-        <v>908.7768904999999</v>
+        <v>921.2258890000001</v>
       </c>
       <c r="N75">
-        <v>18135.5231095</v>
+        <v>18123.074111</v>
       </c>
       <c r="O75">
-        <v>4678.964962251</v>
+        <v>4675.753120638</v>
       </c>
       <c r="P75">
-        <v>13456.558147249</v>
+        <v>13447.320990362</v>
       </c>
       <c r="Q75">
-        <v>14259.058147249</v>
+        <v>14249.820990362</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1405880427512146</v>
+        <v>0.1439208482514999</v>
       </c>
       <c r="T75">
-        <v>2.189100294485326</v>
+        <v>2.266070398418012</v>
       </c>
       <c r="U75">
         <v>0.0503</v>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>20.95596862011094</v>
+        <v>20.67277985497431</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7596,22 +7596,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.06503814454538998</v>
+        <v>0.06487201954795202</v>
       </c>
       <c r="C76">
-        <v>7086.354928692988</v>
+        <v>6850.375282017878</v>
       </c>
       <c r="D76">
-        <v>24530.98492869299</v>
+        <v>24542.50028201788</v>
       </c>
       <c r="E76">
-        <v>13262.63</v>
+        <v>13510.125</v>
       </c>
       <c r="F76">
-        <v>18314.63</v>
+        <v>18562.125</v>
       </c>
       <c r="G76">
         <v>870</v>
@@ -7632,28 +7632,28 @@
         <v>19044.3</v>
       </c>
       <c r="M76">
-        <v>921.2258890000001</v>
+        <v>933.6748875</v>
       </c>
       <c r="N76">
-        <v>18123.074111</v>
+        <v>18110.6251125</v>
       </c>
       <c r="O76">
-        <v>4675.753120638</v>
+        <v>4672.541279024999</v>
       </c>
       <c r="P76">
-        <v>13447.320990362</v>
+        <v>13438.083833475</v>
       </c>
       <c r="Q76">
-        <v>14249.820990362</v>
+        <v>14240.583833475</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1439208482514999</v>
+        <v>0.1475202781918081</v>
       </c>
       <c r="T76">
-        <v>2.266070398418012</v>
+        <v>2.349198110665314</v>
       </c>
       <c r="U76">
         <v>0.0503</v>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>20.67277985497431</v>
+        <v>20.39714279024132</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7678,22 +7678,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.06487201954795202</v>
+        <v>0.06470589455051406</v>
       </c>
       <c r="C77">
-        <v>6850.375282017878</v>
+        <v>6614.406451511677</v>
       </c>
       <c r="D77">
-        <v>24542.50028201788</v>
+        <v>24554.02645151168</v>
       </c>
       <c r="E77">
-        <v>13510.125</v>
+        <v>13757.62</v>
       </c>
       <c r="F77">
-        <v>18562.125</v>
+        <v>18809.62</v>
       </c>
       <c r="G77">
         <v>870</v>
@@ -7714,28 +7714,28 @@
         <v>19044.3</v>
       </c>
       <c r="M77">
-        <v>933.6748875</v>
+        <v>946.1238859999999</v>
       </c>
       <c r="N77">
-        <v>18110.6251125</v>
+        <v>18098.176114</v>
       </c>
       <c r="O77">
-        <v>4672.541279024999</v>
+        <v>4669.329437412</v>
       </c>
       <c r="P77">
-        <v>13438.083833475</v>
+        <v>13428.846676588</v>
       </c>
       <c r="Q77">
-        <v>14240.583833475</v>
+        <v>14231.346676588</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1475202781918081</v>
+        <v>0.1514196606271419</v>
       </c>
       <c r="T77">
-        <v>2.349198110665314</v>
+        <v>2.439253132266558</v>
       </c>
       <c r="U77">
         <v>0.0503</v>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>20.39714279024132</v>
+        <v>20.12875933247499</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7760,22 +7760,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.06470589455051406</v>
+        <v>0.0645397695530761</v>
       </c>
       <c r="C78">
-        <v>6614.406451511677</v>
+        <v>6378.448452420693</v>
       </c>
       <c r="D78">
-        <v>24554.02645151168</v>
+        <v>24565.56345242069</v>
       </c>
       <c r="E78">
-        <v>13757.62</v>
+        <v>14005.115</v>
       </c>
       <c r="F78">
-        <v>18809.62</v>
+        <v>19057.115</v>
       </c>
       <c r="G78">
         <v>870</v>
@@ -7796,28 +7796,28 @@
         <v>19044.3</v>
       </c>
       <c r="M78">
-        <v>946.1238859999999</v>
+        <v>958.5728845</v>
       </c>
       <c r="N78">
-        <v>18098.176114</v>
+        <v>18085.7271155</v>
       </c>
       <c r="O78">
-        <v>4669.329437412</v>
+        <v>4666.117595799</v>
       </c>
       <c r="P78">
-        <v>13428.846676588</v>
+        <v>13419.609519701</v>
       </c>
       <c r="Q78">
-        <v>14231.346676588</v>
+        <v>14222.109519701</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1514196606271419</v>
+        <v>0.155658119795983</v>
       </c>
       <c r="T78">
-        <v>2.439253132266558</v>
+        <v>2.537139025311387</v>
       </c>
       <c r="U78">
         <v>0.0503</v>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>20.12875933247499</v>
+        <v>19.86734687361167</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7842,22 +7842,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0645397695530761</v>
+        <v>0.06437364455563814</v>
       </c>
       <c r="C79">
-        <v>6378.448452420693</v>
+        <v>6142.501300019921</v>
       </c>
       <c r="D79">
-        <v>24565.56345242069</v>
+        <v>24577.11130001992</v>
       </c>
       <c r="E79">
-        <v>14005.115</v>
+        <v>14252.61</v>
       </c>
       <c r="F79">
-        <v>19057.115</v>
+        <v>19304.61</v>
       </c>
       <c r="G79">
         <v>870</v>
@@ -7878,28 +7878,28 @@
         <v>19044.3</v>
       </c>
       <c r="M79">
-        <v>958.5728845</v>
+        <v>971.021883</v>
       </c>
       <c r="N79">
-        <v>18085.7271155</v>
+        <v>18073.278117</v>
       </c>
       <c r="O79">
-        <v>4666.117595799</v>
+        <v>4662.905754185999</v>
       </c>
       <c r="P79">
-        <v>13419.609519701</v>
+        <v>13410.372362814</v>
       </c>
       <c r="Q79">
-        <v>14222.109519701</v>
+        <v>14212.872362814</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.155658119795983</v>
+        <v>0.1602818934347188</v>
       </c>
       <c r="T79">
-        <v>2.537139025311387</v>
+        <v>2.643923635905747</v>
       </c>
       <c r="U79">
         <v>0.0503</v>
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>19.86734687361167</v>
+        <v>19.61263729830896</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7924,22 +7924,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.06437364455563814</v>
+        <v>0.06420751955820017</v>
       </c>
       <c r="C80">
-        <v>6142.501300019921</v>
+        <v>5906.56500961307</v>
       </c>
       <c r="D80">
-        <v>24577.11130001992</v>
+        <v>24588.67000961307</v>
       </c>
       <c r="E80">
-        <v>14252.61</v>
+        <v>14500.105</v>
       </c>
       <c r="F80">
-        <v>19304.61</v>
+        <v>19552.105</v>
       </c>
       <c r="G80">
         <v>870</v>
@@ -7960,28 +7960,28 @@
         <v>19044.3</v>
       </c>
       <c r="M80">
-        <v>971.021883</v>
+        <v>983.4708814999999</v>
       </c>
       <c r="N80">
-        <v>18073.278117</v>
+        <v>18060.8291185</v>
       </c>
       <c r="O80">
-        <v>4662.905754185999</v>
+        <v>4659.693912573</v>
       </c>
       <c r="P80">
-        <v>13410.372362814</v>
+        <v>13401.135205927</v>
       </c>
       <c r="Q80">
-        <v>14212.872362814</v>
+        <v>14203.635205927</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1602818934347188</v>
+        <v>0.1653460264676199</v>
       </c>
       <c r="T80">
-        <v>2.643923635905747</v>
+        <v>2.760878209413855</v>
       </c>
       <c r="U80">
         <v>0.0503</v>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>19.61263729830896</v>
+        <v>19.3643760666848</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8006,22 +8006,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.06420751955820017</v>
+        <v>0.06404139456076222</v>
       </c>
       <c r="C81">
-        <v>5906.56500961307</v>
+        <v>5670.639596532666</v>
       </c>
       <c r="D81">
-        <v>24588.67000961307</v>
+        <v>24600.23959653267</v>
       </c>
       <c r="E81">
-        <v>14500.105</v>
+        <v>14747.6</v>
       </c>
       <c r="F81">
-        <v>19552.105</v>
+        <v>19799.6</v>
       </c>
       <c r="G81">
         <v>870</v>
@@ -8042,28 +8042,28 @@
         <v>19044.3</v>
       </c>
       <c r="M81">
-        <v>983.4708814999999</v>
+        <v>995.91988</v>
       </c>
       <c r="N81">
-        <v>18060.8291185</v>
+        <v>18048.38012</v>
       </c>
       <c r="O81">
-        <v>4659.693912573</v>
+        <v>4656.48207096</v>
       </c>
       <c r="P81">
-        <v>13401.135205927</v>
+        <v>13391.89804904</v>
       </c>
       <c r="Q81">
-        <v>14203.635205927</v>
+        <v>14194.39804904</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1653460264676199</v>
+        <v>0.1709165728038111</v>
       </c>
       <c r="T81">
-        <v>2.760878209413855</v>
+        <v>2.889528240272774</v>
       </c>
       <c r="U81">
         <v>0.0503</v>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>19.3643760666848</v>
+        <v>19.12232136585123</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8088,22 +8088,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.06404139456076222</v>
+        <v>0.06387526956332425</v>
       </c>
       <c r="C82">
-        <v>5670.639596532666</v>
+        <v>5434.725076140112</v>
       </c>
       <c r="D82">
-        <v>24600.23959653267</v>
+        <v>24611.82007614011</v>
       </c>
       <c r="E82">
-        <v>14747.6</v>
+        <v>14995.095</v>
       </c>
       <c r="F82">
-        <v>19799.6</v>
+        <v>20047.095</v>
       </c>
       <c r="G82">
         <v>870</v>
@@ -8124,28 +8124,28 @@
         <v>19044.3</v>
       </c>
       <c r="M82">
-        <v>995.91988</v>
+        <v>1008.3688785</v>
       </c>
       <c r="N82">
-        <v>18048.38012</v>
+        <v>18035.9311215</v>
       </c>
       <c r="O82">
-        <v>4656.48207096</v>
+        <v>4653.270229346999</v>
       </c>
       <c r="P82">
-        <v>13391.89804904</v>
+        <v>13382.660892153</v>
       </c>
       <c r="Q82">
-        <v>14194.39804904</v>
+        <v>14185.160892153</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1709165728038111</v>
+        <v>0.1770734924385487</v>
       </c>
       <c r="T82">
-        <v>2.889528240272774</v>
+        <v>3.031720379643158</v>
       </c>
       <c r="U82">
         <v>0.0503</v>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>19.12232136585123</v>
+        <v>18.88624332429751</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8170,22 +8170,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.06387526956332425</v>
+        <v>0.06370914456588628</v>
       </c>
       <c r="C83">
-        <v>5434.725076140112</v>
+        <v>5198.821463825734</v>
       </c>
       <c r="D83">
-        <v>24611.82007614011</v>
+        <v>24623.41146382573</v>
       </c>
       <c r="E83">
-        <v>14995.095</v>
+        <v>15242.59</v>
       </c>
       <c r="F83">
-        <v>20047.095</v>
+        <v>20294.59</v>
       </c>
       <c r="G83">
         <v>870</v>
@@ -8206,28 +8206,28 @@
         <v>19044.3</v>
       </c>
       <c r="M83">
-        <v>1008.3688785</v>
+        <v>1020.817877</v>
       </c>
       <c r="N83">
-        <v>18035.9311215</v>
+        <v>18023.482123</v>
       </c>
       <c r="O83">
-        <v>4653.270229346999</v>
+        <v>4650.058387734</v>
       </c>
       <c r="P83">
-        <v>13382.660892153</v>
+        <v>13373.423735266</v>
       </c>
       <c r="Q83">
-        <v>14185.160892153</v>
+        <v>14175.923735266</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1770734924385487</v>
+        <v>0.1839145142549239</v>
       </c>
       <c r="T83">
-        <v>3.031720379643158</v>
+        <v>3.189711645610251</v>
       </c>
       <c r="U83">
         <v>0.0503</v>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>18.88624332429751</v>
+        <v>18.6559232837573</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8252,22 +8252,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.06370914456588628</v>
+        <v>0.06354301956844832</v>
       </c>
       <c r="C84">
-        <v>5198.821463825734</v>
+        <v>4962.928775008862</v>
       </c>
       <c r="D84">
-        <v>24623.41146382573</v>
+        <v>24635.01377500887</v>
       </c>
       <c r="E84">
-        <v>15242.59</v>
+        <v>15490.085</v>
       </c>
       <c r="F84">
-        <v>20294.59</v>
+        <v>20542.085</v>
       </c>
       <c r="G84">
         <v>870</v>
@@ -8288,28 +8288,28 @@
         <v>19044.3</v>
       </c>
       <c r="M84">
-        <v>1020.817877</v>
+        <v>1033.2668755</v>
       </c>
       <c r="N84">
-        <v>18023.482123</v>
+        <v>18011.0331245</v>
       </c>
       <c r="O84">
-        <v>4650.058387734</v>
+        <v>4646.846546121</v>
       </c>
       <c r="P84">
-        <v>13373.423735266</v>
+        <v>13364.186578379</v>
       </c>
       <c r="Q84">
-        <v>14175.923735266</v>
+        <v>14166.686578379</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1839145142549239</v>
+        <v>0.1915603621673432</v>
       </c>
       <c r="T84">
-        <v>3.189711645610251</v>
+        <v>3.36629011933818</v>
       </c>
       <c r="U84">
         <v>0.0503</v>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>18.6559232837573</v>
+        <v>18.43115312371203</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8334,22 +8334,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.06354301956844832</v>
+        <v>0.06337689457101035</v>
       </c>
       <c r="C85">
-        <v>4962.928775008862</v>
+        <v>4727.04702513793</v>
       </c>
       <c r="D85">
-        <v>24635.01377500887</v>
+        <v>24646.62702513793</v>
       </c>
       <c r="E85">
-        <v>15490.085</v>
+        <v>15737.58</v>
       </c>
       <c r="F85">
-        <v>20542.085</v>
+        <v>20789.58</v>
       </c>
       <c r="G85">
         <v>870</v>
@@ -8370,28 +8370,28 @@
         <v>19044.3</v>
       </c>
       <c r="M85">
-        <v>1033.2668755</v>
+        <v>1045.715874</v>
       </c>
       <c r="N85">
-        <v>18011.0331245</v>
+        <v>17998.584126</v>
       </c>
       <c r="O85">
-        <v>4646.846546121</v>
+        <v>4643.634704507999</v>
       </c>
       <c r="P85">
-        <v>13364.186578379</v>
+        <v>13354.949421492</v>
       </c>
       <c r="Q85">
-        <v>14166.686578379</v>
+        <v>14157.449421492</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1915603621673432</v>
+        <v>0.2001619410688148</v>
       </c>
       <c r="T85">
-        <v>3.36629011933818</v>
+        <v>3.564940902282098</v>
       </c>
       <c r="U85">
         <v>0.0503</v>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>18.43115312371203</v>
+        <v>18.21173463414403</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8416,22 +8416,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.06337689457101037</v>
+        <v>0.06321076957357241</v>
       </c>
       <c r="C86">
-        <v>4727.047025137927</v>
+        <v>4491.176229690478</v>
       </c>
       <c r="D86">
-        <v>24646.62702513792</v>
+        <v>24658.25122969048</v>
       </c>
       <c r="E86">
-        <v>15737.58</v>
+        <v>15985.075</v>
       </c>
       <c r="F86">
-        <v>20789.58</v>
+        <v>21037.075</v>
       </c>
       <c r="G86">
         <v>870</v>
@@ -8452,28 +8452,28 @@
         <v>19044.3</v>
       </c>
       <c r="M86">
-        <v>1045.715874</v>
+        <v>1058.1648725</v>
       </c>
       <c r="N86">
-        <v>17998.584126</v>
+        <v>17986.1351275</v>
       </c>
       <c r="O86">
-        <v>4643.634704507999</v>
+        <v>4640.422862895</v>
       </c>
       <c r="P86">
-        <v>13354.949421492</v>
+        <v>13345.712264605</v>
       </c>
       <c r="Q86">
-        <v>14157.449421492</v>
+        <v>14148.212264605</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2001619410688148</v>
+        <v>0.2099103971571493</v>
       </c>
       <c r="T86">
-        <v>3.564940902282097</v>
+        <v>3.790078456285205</v>
       </c>
       <c r="U86">
         <v>0.0503</v>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>18.21173463414404</v>
+        <v>17.99747893256587</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8498,22 +8498,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.06321076957357241</v>
+        <v>0.06304464457613444</v>
       </c>
       <c r="C87">
-        <v>4491.176229690478</v>
+        <v>4255.3164041733</v>
       </c>
       <c r="D87">
-        <v>24658.25122969048</v>
+        <v>24669.8864041733</v>
       </c>
       <c r="E87">
-        <v>15985.075</v>
+        <v>16232.57</v>
       </c>
       <c r="F87">
-        <v>21037.075</v>
+        <v>21284.57</v>
       </c>
       <c r="G87">
         <v>870</v>
@@ -8534,28 +8534,28 @@
         <v>19044.3</v>
       </c>
       <c r="M87">
-        <v>1058.1648725</v>
+        <v>1070.613871</v>
       </c>
       <c r="N87">
-        <v>17986.1351275</v>
+        <v>17973.686129</v>
       </c>
       <c r="O87">
-        <v>4640.422862895</v>
+        <v>4637.211021282</v>
       </c>
       <c r="P87">
-        <v>13345.712264605</v>
+        <v>13336.475107718</v>
       </c>
       <c r="Q87">
-        <v>14148.212264605</v>
+        <v>14138.975107718</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2099103971571493</v>
+        <v>0.2210514898295317</v>
       </c>
       <c r="T87">
-        <v>3.790078456285205</v>
+        <v>4.047378518003042</v>
       </c>
       <c r="U87">
         <v>0.0503</v>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>17.99747893256587</v>
+        <v>17.78820592172208</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8580,22 +8580,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.06304464457613444</v>
+        <v>0.06287851957869647</v>
       </c>
       <c r="C88">
-        <v>4255.3164041733</v>
+        <v>4019.467564122435</v>
       </c>
       <c r="D88">
-        <v>24669.8864041733</v>
+        <v>24681.53256412243</v>
       </c>
       <c r="E88">
-        <v>16232.57</v>
+        <v>16480.065</v>
       </c>
       <c r="F88">
-        <v>21284.57</v>
+        <v>21532.065</v>
       </c>
       <c r="G88">
         <v>870</v>
@@ -8616,28 +8616,28 @@
         <v>19044.3</v>
       </c>
       <c r="M88">
-        <v>1070.613871</v>
+        <v>1083.0628695</v>
       </c>
       <c r="N88">
-        <v>17973.686129</v>
+        <v>17961.2371305</v>
       </c>
       <c r="O88">
-        <v>4637.211021282</v>
+        <v>4633.999179668999</v>
       </c>
       <c r="P88">
-        <v>13336.475107718</v>
+        <v>13327.237950831</v>
       </c>
       <c r="Q88">
-        <v>14138.975107718</v>
+        <v>14129.737950831</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2210514898295317</v>
+        <v>0.2339065967592036</v>
       </c>
       <c r="T88">
-        <v>4.047378518003042</v>
+        <v>4.344263204600547</v>
       </c>
       <c r="U88">
         <v>0.0503</v>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>17.78820592172208</v>
+        <v>17.58374378469079</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8662,22 +8662,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.06287851957869647</v>
+        <v>0.06271239458125852</v>
       </c>
       <c r="C89">
-        <v>4019.467564122435</v>
+        <v>3783.629725103288</v>
       </c>
       <c r="D89">
-        <v>24681.53256412243</v>
+        <v>24693.18972510329</v>
       </c>
       <c r="E89">
-        <v>16480.065</v>
+        <v>16727.56</v>
       </c>
       <c r="F89">
-        <v>21532.065</v>
+        <v>21779.56</v>
       </c>
       <c r="G89">
         <v>870</v>
@@ -8698,28 +8698,28 @@
         <v>19044.3</v>
       </c>
       <c r="M89">
-        <v>1083.0628695</v>
+        <v>1095.511868</v>
       </c>
       <c r="N89">
-        <v>17961.2371305</v>
+        <v>17948.788132</v>
       </c>
       <c r="O89">
-        <v>4633.999179668999</v>
+        <v>4630.787338055999</v>
       </c>
       <c r="P89">
-        <v>13327.237950831</v>
+        <v>13318.000793944</v>
       </c>
       <c r="Q89">
-        <v>14129.737950831</v>
+        <v>14120.500793944</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2339065967592036</v>
+        <v>0.2489042215104877</v>
       </c>
       <c r="T89">
-        <v>4.344263204600547</v>
+        <v>4.690628672297637</v>
       </c>
       <c r="U89">
         <v>0.0503</v>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>17.58374378469079</v>
+        <v>17.38392851441021</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8744,22 +8744,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.06271239458125852</v>
+        <v>0.06254626958382055</v>
       </c>
       <c r="C90">
-        <v>3783.629725103288</v>
+        <v>3547.802902710686</v>
       </c>
       <c r="D90">
-        <v>24693.18972510329</v>
+        <v>24704.85790271069</v>
       </c>
       <c r="E90">
-        <v>16727.56</v>
+        <v>16975.055</v>
       </c>
       <c r="F90">
-        <v>21779.56</v>
+        <v>22027.055</v>
       </c>
       <c r="G90">
         <v>870</v>
@@ -8780,28 +8780,28 @@
         <v>19044.3</v>
       </c>
       <c r="M90">
-        <v>1095.511868</v>
+        <v>1107.9608665</v>
       </c>
       <c r="N90">
-        <v>17948.788132</v>
+        <v>17936.3391335</v>
       </c>
       <c r="O90">
-        <v>4630.787338055999</v>
+        <v>4627.575496443</v>
       </c>
       <c r="P90">
-        <v>13318.000793944</v>
+        <v>13308.763637057</v>
       </c>
       <c r="Q90">
-        <v>14120.500793944</v>
+        <v>14111.263637057</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2489042215104877</v>
+        <v>0.2666286871256414</v>
       </c>
       <c r="T90">
-        <v>4.690628672297637</v>
+        <v>5.099969679576016</v>
       </c>
       <c r="U90">
         <v>0.0503</v>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>17.38392851441021</v>
+        <v>17.18860347492246</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8826,22 +8826,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.06254626958382055</v>
+        <v>0.06238014458638258</v>
       </c>
       <c r="C91">
-        <v>3547.802902710686</v>
+        <v>3311.98711256895</v>
       </c>
       <c r="D91">
-        <v>24704.85790271069</v>
+        <v>24716.53711256895</v>
       </c>
       <c r="E91">
-        <v>16975.055</v>
+        <v>17222.55</v>
       </c>
       <c r="F91">
-        <v>22027.055</v>
+        <v>22274.55</v>
       </c>
       <c r="G91">
         <v>870</v>
@@ -8862,28 +8862,28 @@
         <v>19044.3</v>
       </c>
       <c r="M91">
-        <v>1107.9608665</v>
+        <v>1120.409865</v>
       </c>
       <c r="N91">
-        <v>17936.3391335</v>
+        <v>17923.890135</v>
       </c>
       <c r="O91">
-        <v>4627.575496443</v>
+        <v>4624.363654829999</v>
       </c>
       <c r="P91">
-        <v>13308.763637057</v>
+        <v>13299.52648017</v>
       </c>
       <c r="Q91">
-        <v>14111.263637057</v>
+        <v>14102.02648017</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2666286871256414</v>
+        <v>0.2878980458638259</v>
       </c>
       <c r="T91">
-        <v>5.099969679576016</v>
+        <v>5.591178888310069</v>
       </c>
       <c r="U91">
         <v>0.0503</v>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>17.18860347492246</v>
+        <v>16.99761899186777</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8908,22 +8908,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.06238014458638258</v>
+        <v>0.06221401958894463</v>
       </c>
       <c r="C92">
-        <v>3311.98711256895</v>
+        <v>3076.182370331946</v>
       </c>
       <c r="D92">
-        <v>24716.53711256895</v>
+        <v>24728.22737033195</v>
       </c>
       <c r="E92">
-        <v>17222.55</v>
+        <v>17470.045</v>
       </c>
       <c r="F92">
-        <v>22274.55</v>
+        <v>22522.045</v>
       </c>
       <c r="G92">
         <v>870</v>
@@ -8944,28 +8944,28 @@
         <v>19044.3</v>
       </c>
       <c r="M92">
-        <v>1120.409865</v>
+        <v>1132.8588635</v>
       </c>
       <c r="N92">
-        <v>17923.890135</v>
+        <v>17911.4411365</v>
       </c>
       <c r="O92">
-        <v>4624.363654829999</v>
+        <v>4621.151813216999</v>
       </c>
       <c r="P92">
-        <v>13299.52648017</v>
+        <v>13290.289323283</v>
       </c>
       <c r="Q92">
-        <v>14102.02648017</v>
+        <v>14092.789323283</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2878980458638259</v>
+        <v>0.3138939287660515</v>
       </c>
       <c r="T92">
-        <v>5.591178888310069</v>
+        <v>6.191545698985025</v>
       </c>
       <c r="U92">
         <v>0.0503</v>
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>16.99761899186777</v>
+        <v>16.81083196997911</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8990,22 +8990,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.06221401958894463</v>
+        <v>0.06204789459150667</v>
       </c>
       <c r="C93">
-        <v>3076.182370331946</v>
+        <v>2840.388691683187</v>
       </c>
       <c r="D93">
-        <v>24728.22737033195</v>
+        <v>24739.92869168319</v>
       </c>
       <c r="E93">
-        <v>17470.045</v>
+        <v>17717.54</v>
       </c>
       <c r="F93">
-        <v>22522.045</v>
+        <v>22769.54</v>
       </c>
       <c r="G93">
         <v>870</v>
@@ -9026,28 +9026,28 @@
         <v>19044.3</v>
       </c>
       <c r="M93">
-        <v>1132.8588635</v>
+        <v>1145.307862</v>
       </c>
       <c r="N93">
-        <v>17911.4411365</v>
+        <v>17898.992138</v>
       </c>
       <c r="O93">
-        <v>4621.151813216999</v>
+        <v>4617.939971604</v>
       </c>
       <c r="P93">
-        <v>13290.289323283</v>
+        <v>13281.052166396</v>
       </c>
       <c r="Q93">
-        <v>14092.789323283</v>
+        <v>14083.552166396</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3138939287660515</v>
+        <v>0.3463887823938335</v>
       </c>
       <c r="T93">
-        <v>6.191545698985025</v>
+        <v>6.94200421232872</v>
       </c>
       <c r="U93">
         <v>0.0503</v>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>16.81083196997911</v>
+        <v>16.62810553552281</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9072,22 +9072,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.06204789459150667</v>
+        <v>0.06188176959406871</v>
       </c>
       <c r="C94">
-        <v>2840.388691683187</v>
+        <v>2604.606092335871</v>
       </c>
       <c r="D94">
-        <v>24739.92869168319</v>
+        <v>24751.64109233587</v>
       </c>
       <c r="E94">
-        <v>17717.54</v>
+        <v>17965.035</v>
       </c>
       <c r="F94">
-        <v>22769.54</v>
+        <v>23017.035</v>
       </c>
       <c r="G94">
         <v>870</v>
@@ -9108,28 +9108,28 @@
         <v>19044.3</v>
       </c>
       <c r="M94">
-        <v>1145.307862</v>
+        <v>1157.7568605</v>
       </c>
       <c r="N94">
-        <v>17898.992138</v>
+        <v>17886.5431395</v>
       </c>
       <c r="O94">
-        <v>4617.939971604</v>
+        <v>4614.728129990999</v>
       </c>
       <c r="P94">
-        <v>13281.052166396</v>
+        <v>13271.815009509</v>
       </c>
       <c r="Q94">
-        <v>14083.552166396</v>
+        <v>14074.315009509</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3463887823938335</v>
+        <v>0.3881678799152675</v>
       </c>
       <c r="T94">
-        <v>6.94200421232872</v>
+        <v>7.906879443770613</v>
       </c>
       <c r="U94">
         <v>0.0503</v>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>16.62810553552281</v>
+        <v>16.44930870180752</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9154,22 +9154,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.06188176959406871</v>
+        <v>0.06171564459663074</v>
       </c>
       <c r="C95">
-        <v>2604.606092335871</v>
+        <v>2368.834588032962</v>
       </c>
       <c r="D95">
-        <v>24751.64109233587</v>
+        <v>24763.36458803296</v>
       </c>
       <c r="E95">
-        <v>17965.035</v>
+        <v>18212.53</v>
       </c>
       <c r="F95">
-        <v>23017.035</v>
+        <v>23264.53</v>
       </c>
       <c r="G95">
         <v>870</v>
@@ -9190,28 +9190,28 @@
         <v>19044.3</v>
       </c>
       <c r="M95">
-        <v>1157.7568605</v>
+        <v>1170.205859</v>
       </c>
       <c r="N95">
-        <v>17886.5431395</v>
+        <v>17874.094141</v>
       </c>
       <c r="O95">
-        <v>4614.728129990999</v>
+        <v>4611.516288377999</v>
       </c>
       <c r="P95">
-        <v>13271.815009509</v>
+        <v>13262.577852622</v>
       </c>
       <c r="Q95">
-        <v>14074.315009509</v>
+        <v>14065.077852622</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3881678799152675</v>
+        <v>0.4438733432771795</v>
       </c>
       <c r="T95">
-        <v>7.906879443770613</v>
+        <v>9.193379752359805</v>
       </c>
       <c r="U95">
         <v>0.0503</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>16.44930870180752</v>
+        <v>16.2743160560436</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9236,22 +9236,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.06171564459663074</v>
+        <v>0.06154951959919278</v>
       </c>
       <c r="C96">
-        <v>2368.834588032962</v>
+        <v>2133.074194547298</v>
       </c>
       <c r="D96">
-        <v>24763.36458803296</v>
+        <v>24775.0991945473</v>
       </c>
       <c r="E96">
-        <v>18212.53</v>
+        <v>18460.025</v>
       </c>
       <c r="F96">
-        <v>23264.53</v>
+        <v>23512.025</v>
       </c>
       <c r="G96">
         <v>870</v>
@@ -9272,28 +9272,28 @@
         <v>19044.3</v>
       </c>
       <c r="M96">
-        <v>1170.205859</v>
+        <v>1182.6548575</v>
       </c>
       <c r="N96">
-        <v>17874.094141</v>
+        <v>17861.6451425</v>
       </c>
       <c r="O96">
-        <v>4611.516288377999</v>
+        <v>4608.304446765</v>
       </c>
       <c r="P96">
-        <v>13262.577852622</v>
+        <v>13253.340695735</v>
       </c>
       <c r="Q96">
-        <v>14065.077852622</v>
+        <v>14055.840695735</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4438733432771795</v>
+        <v>0.5218609919838563</v>
       </c>
       <c r="T96">
-        <v>9.193379752359805</v>
+        <v>10.99448018438467</v>
       </c>
       <c r="U96">
         <v>0.0503</v>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>16.2743160560436</v>
+        <v>16.10300746597999</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9318,22 +9318,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.06154951959919278</v>
+        <v>0.06138339460175481</v>
       </c>
       <c r="C97">
-        <v>2133.074194547298</v>
+        <v>1897.324927681584</v>
       </c>
       <c r="D97">
-        <v>24775.0991945473</v>
+        <v>24786.84492768158</v>
       </c>
       <c r="E97">
-        <v>18460.025</v>
+        <v>18707.52</v>
       </c>
       <c r="F97">
-        <v>23512.025</v>
+        <v>23759.52</v>
       </c>
       <c r="G97">
         <v>870</v>
@@ -9354,28 +9354,28 @@
         <v>19044.3</v>
       </c>
       <c r="M97">
-        <v>1182.6548575</v>
+        <v>1195.103856</v>
       </c>
       <c r="N97">
-        <v>17861.6451425</v>
+        <v>17849.196144</v>
       </c>
       <c r="O97">
-        <v>4608.304446765</v>
+        <v>4605.092605151999</v>
       </c>
       <c r="P97">
-        <v>13253.340695735</v>
+        <v>13244.103538848</v>
       </c>
       <c r="Q97">
-        <v>14055.840695735</v>
+        <v>14046.603538848</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5218609919838563</v>
+        <v>0.6388424650438715</v>
       </c>
       <c r="T97">
-        <v>10.99448018438467</v>
+        <v>13.69613083242198</v>
       </c>
       <c r="U97">
         <v>0.0503</v>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>16.10300746597999</v>
+        <v>15.93526780487603</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9400,22 +9400,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.06138339460175482</v>
+        <v>0.06121726960431687</v>
       </c>
       <c r="C98">
-        <v>1897.324927681584</v>
+        <v>1661.586803268532</v>
       </c>
       <c r="D98">
-        <v>24786.84492768158</v>
+        <v>24798.60180326853</v>
       </c>
       <c r="E98">
-        <v>18707.52</v>
+        <v>18955.015</v>
       </c>
       <c r="F98">
-        <v>23759.52</v>
+        <v>24007.015</v>
       </c>
       <c r="G98">
         <v>870</v>
@@ -9436,28 +9436,28 @@
         <v>19044.3</v>
       </c>
       <c r="M98">
-        <v>1195.103856</v>
+        <v>1207.5528545</v>
       </c>
       <c r="N98">
-        <v>17849.196144</v>
+        <v>17836.7471455</v>
       </c>
       <c r="O98">
-        <v>4605.092605151999</v>
+        <v>4601.880763538999</v>
       </c>
       <c r="P98">
-        <v>13244.103538848</v>
+        <v>13234.866381961</v>
       </c>
       <c r="Q98">
-        <v>14046.603538848</v>
+        <v>14037.366381961</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.63884246504387</v>
+        <v>0.8338115868105613</v>
       </c>
       <c r="T98">
-        <v>13.69613083242194</v>
+        <v>18.1988819124841</v>
       </c>
       <c r="U98">
         <v>0.0503</v>
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>15.93526780487603</v>
+        <v>15.77098669348555</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9482,22 +9482,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.06121726960431687</v>
+        <v>0.0610511446068789</v>
       </c>
       <c r="C99">
-        <v>1661.586803268532</v>
+        <v>1425.859837170905</v>
       </c>
       <c r="D99">
-        <v>24798.60180326853</v>
+        <v>24810.3698371709</v>
       </c>
       <c r="E99">
-        <v>18955.015</v>
+        <v>19202.51</v>
       </c>
       <c r="F99">
-        <v>24007.015</v>
+        <v>24254.51</v>
       </c>
       <c r="G99">
         <v>870</v>
@@ -9518,28 +9518,28 @@
         <v>19044.3</v>
       </c>
       <c r="M99">
-        <v>1207.5528545</v>
+        <v>1220.001853</v>
       </c>
       <c r="N99">
-        <v>17836.7471455</v>
+        <v>17824.298147</v>
       </c>
       <c r="O99">
-        <v>4601.880763538999</v>
+        <v>4598.668921926001</v>
       </c>
       <c r="P99">
-        <v>13234.866381961</v>
+        <v>13225.629225074</v>
       </c>
       <c r="Q99">
-        <v>14037.366381961</v>
+        <v>14028.129225074</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8338115868105613</v>
+        <v>1.223749830343944</v>
       </c>
       <c r="T99">
-        <v>18.1988819124841</v>
+        <v>27.20438407260841</v>
       </c>
       <c r="U99">
         <v>0.0503</v>
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>15.77098669348555</v>
+        <v>15.61005825783775</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9564,22 +9564,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.0610511446068789</v>
+        <v>0.06088501960944094</v>
       </c>
       <c r="C100">
-        <v>1425.859837170905</v>
+        <v>1190.14404528158</v>
       </c>
       <c r="D100">
-        <v>24810.3698371709</v>
+        <v>24822.14904528158</v>
       </c>
       <c r="E100">
-        <v>19202.51</v>
+        <v>19450.005</v>
       </c>
       <c r="F100">
-        <v>24254.51</v>
+        <v>24502.005</v>
       </c>
       <c r="G100">
         <v>870</v>
@@ -9600,28 +9600,28 @@
         <v>19044.3</v>
       </c>
       <c r="M100">
-        <v>1220.001853</v>
+        <v>1232.4508515</v>
       </c>
       <c r="N100">
-        <v>17824.298147</v>
+        <v>17811.8491485</v>
       </c>
       <c r="O100">
-        <v>4598.668921926001</v>
+        <v>4595.457080312999</v>
       </c>
       <c r="P100">
-        <v>13225.629225074</v>
+        <v>13216.392068187</v>
       </c>
       <c r="Q100">
-        <v>14028.129225074</v>
+        <v>14018.892068187</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.223749830343944</v>
+        <v>2.393564560944092</v>
       </c>
       <c r="T100">
-        <v>27.20438407260841</v>
+        <v>54.22089055298134</v>
       </c>
       <c r="U100">
         <v>0.0503</v>
@@ -9638,91 +9638,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>15.61005825783775</v>
+        <v>15.45238090169797</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.06088501960944094</v>
-      </c>
-      <c r="C101">
-        <v>1190.14404528158</v>
-      </c>
-      <c r="D101">
-        <v>24822.14904528158</v>
-      </c>
-      <c r="E101">
-        <v>19450.005</v>
-      </c>
-      <c r="F101">
-        <v>24502.005</v>
-      </c>
-      <c r="G101">
-        <v>870</v>
-      </c>
-      <c r="H101">
-        <v>19697.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>19846.8</v>
-      </c>
-      <c r="K101">
-        <v>802.5</v>
-      </c>
-      <c r="L101">
-        <v>19044.3</v>
-      </c>
-      <c r="M101">
-        <v>1232.4508515</v>
-      </c>
-      <c r="N101">
-        <v>17811.8491485</v>
-      </c>
-      <c r="O101">
-        <v>4595.457080312999</v>
-      </c>
-      <c r="P101">
-        <v>13216.392068187</v>
-      </c>
-      <c r="Q101">
-        <v>14018.892068187</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.393564560944092</v>
-      </c>
-      <c r="T101">
-        <v>54.22089055298134</v>
-      </c>
-      <c r="U101">
-        <v>0.0503</v>
-      </c>
-      <c r="V101">
-        <v>0.258</v>
-      </c>
-      <c r="W101">
-        <v>0.0373226</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Aaa/AAA</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>15.45238090169797</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
